--- a/data-sources/技能养成相关.xlsx
+++ b/data-sources/技能养成相关.xlsx
@@ -5,11 +5,11 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\策划\1.表格目录\XLS表格\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\古荒遗迹2策划\1.表格目录\XLS表格\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255" activeTab="2"/>
+    <workbookView windowWidth="28800" windowHeight="12255" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="SkillActive" sheetId="1" r:id="rId1"/>
@@ -613,7 +613,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4649" uniqueCount="2237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4633" uniqueCount="2237">
   <si>
     <t>技能</t>
   </si>
@@ -14636,8 +14636,8 @@
       <c r="D4" s="14">
         <v>1</v>
       </c>
-      <c r="E4" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C4,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E4" s="14" t="str" cm="1">
+        <f t="array" ref="E4">_xlfn.XLOOKUP(C4,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>专注斩</v>
       </c>
       <c r="F4">
@@ -14669,8 +14669,8 @@
       <c r="D5" s="14">
         <v>2</v>
       </c>
-      <c r="E5" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C5,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E5" s="14" t="str" cm="1">
+        <f t="array" ref="E5">_xlfn.XLOOKUP(C5,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>专注斩</v>
       </c>
       <c r="F5">
@@ -14702,8 +14702,8 @@
       <c r="D6" s="14">
         <v>3</v>
       </c>
-      <c r="E6" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C6,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E6" s="14" t="str" cm="1">
+        <f t="array" ref="E6">_xlfn.XLOOKUP(C6,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>专注斩</v>
       </c>
       <c r="F6">
@@ -14735,8 +14735,8 @@
       <c r="D7" s="14">
         <v>4</v>
       </c>
-      <c r="E7" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C7,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E7" s="14" t="str" cm="1">
+        <f t="array" ref="E7">_xlfn.XLOOKUP(C7,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>专注斩</v>
       </c>
       <c r="F7">
@@ -14768,8 +14768,8 @@
       <c r="D8" s="14">
         <v>5</v>
       </c>
-      <c r="E8" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C8,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E8" s="14" t="str" cm="1">
+        <f t="array" ref="E8">_xlfn.XLOOKUP(C8,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>专注斩</v>
       </c>
       <c r="F8">
@@ -14801,8 +14801,8 @@
       <c r="D9" s="14">
         <v>6</v>
       </c>
-      <c r="E9" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C9,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E9" s="14" t="str" cm="1">
+        <f t="array" ref="E9">_xlfn.XLOOKUP(C9,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>专注斩</v>
       </c>
       <c r="F9">
@@ -14834,8 +14834,8 @@
       <c r="D10" s="14">
         <v>7</v>
       </c>
-      <c r="E10" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C10,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E10" s="14" t="str" cm="1">
+        <f t="array" ref="E10">_xlfn.XLOOKUP(C10,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>专注斩</v>
       </c>
       <c r="F10">
@@ -14867,8 +14867,8 @@
       <c r="D11" s="14">
         <v>8</v>
       </c>
-      <c r="E11" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C11,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E11" s="14" t="str" cm="1">
+        <f t="array" ref="E11">_xlfn.XLOOKUP(C11,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>专注斩</v>
       </c>
       <c r="F11">
@@ -14900,8 +14900,8 @@
       <c r="D12" s="14">
         <v>9</v>
       </c>
-      <c r="E12" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C12,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E12" s="14" t="str" cm="1">
+        <f t="array" ref="E12">_xlfn.XLOOKUP(C12,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>专注斩</v>
       </c>
       <c r="F12">
@@ -14933,8 +14933,8 @@
       <c r="D13" s="14">
         <v>10</v>
       </c>
-      <c r="E13" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C13,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E13" s="14" t="str" cm="1">
+        <f t="array" ref="E13">_xlfn.XLOOKUP(C13,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>专注斩</v>
       </c>
       <c r="F13">
@@ -14966,8 +14966,8 @@
       <c r="D14" s="14">
         <v>11</v>
       </c>
-      <c r="E14" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C14,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E14" s="14" t="str" cm="1">
+        <f t="array" ref="E14">_xlfn.XLOOKUP(C14,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>专注斩</v>
       </c>
       <c r="F14">
@@ -14999,8 +14999,8 @@
       <c r="D15" s="14">
         <v>12</v>
       </c>
-      <c r="E15" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C15,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E15" s="14" t="str" cm="1">
+        <f t="array" ref="E15">_xlfn.XLOOKUP(C15,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>专注斩</v>
       </c>
       <c r="F15">
@@ -15032,8 +15032,8 @@
       <c r="D16" s="14">
         <v>13</v>
       </c>
-      <c r="E16" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C16,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E16" s="14" t="str" cm="1">
+        <f t="array" ref="E16">_xlfn.XLOOKUP(C16,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>专注斩</v>
       </c>
       <c r="F16">
@@ -15065,8 +15065,8 @@
       <c r="D17" s="14">
         <v>14</v>
       </c>
-      <c r="E17" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C17,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E17" s="14" t="str" cm="1">
+        <f t="array" ref="E17">_xlfn.XLOOKUP(C17,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>专注斩</v>
       </c>
       <c r="F17">
@@ -15098,8 +15098,8 @@
       <c r="D18" s="14">
         <v>15</v>
       </c>
-      <c r="E18" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C18,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E18" s="14" t="str" cm="1">
+        <f t="array" ref="E18">_xlfn.XLOOKUP(C18,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>专注斩</v>
       </c>
       <c r="F18">
@@ -15131,8 +15131,8 @@
       <c r="D19" s="14">
         <v>16</v>
       </c>
-      <c r="E19" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C19,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E19" s="14" t="str" cm="1">
+        <f t="array" ref="E19">_xlfn.XLOOKUP(C19,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>专注斩</v>
       </c>
       <c r="F19">
@@ -15165,8 +15165,8 @@
         <f t="shared" ref="D20:D83" si="4">D4</f>
         <v>1</v>
       </c>
-      <c r="E20" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C20,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E20" s="14" t="str" cm="1">
+        <f t="array" ref="E20">_xlfn.XLOOKUP(C20,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>旋风斩</v>
       </c>
       <c r="F20">
@@ -15199,8 +15199,8 @@
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="E21" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C21,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E21" s="14" t="str" cm="1">
+        <f t="array" ref="E21">_xlfn.XLOOKUP(C21,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>旋风斩</v>
       </c>
       <c r="F21">
@@ -15233,8 +15233,8 @@
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
-      <c r="E22" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C22,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E22" s="14" t="str" cm="1">
+        <f t="array" ref="E22">_xlfn.XLOOKUP(C22,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>旋风斩</v>
       </c>
       <c r="F22">
@@ -15267,8 +15267,8 @@
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
-      <c r="E23" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C23,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E23" s="14" t="str" cm="1">
+        <f t="array" ref="E23">_xlfn.XLOOKUP(C23,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>旋风斩</v>
       </c>
       <c r="F23">
@@ -15301,8 +15301,8 @@
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="E24" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C24,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E24" s="14" t="str" cm="1">
+        <f t="array" ref="E24">_xlfn.XLOOKUP(C24,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>旋风斩</v>
       </c>
       <c r="F24">
@@ -15335,8 +15335,8 @@
         <f t="shared" si="4"/>
         <v>6</v>
       </c>
-      <c r="E25" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C25,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E25" s="14" t="str" cm="1">
+        <f t="array" ref="E25">_xlfn.XLOOKUP(C25,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>旋风斩</v>
       </c>
       <c r="F25">
@@ -15369,8 +15369,8 @@
         <f t="shared" si="4"/>
         <v>7</v>
       </c>
-      <c r="E26" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C26,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E26" s="14" t="str" cm="1">
+        <f t="array" ref="E26">_xlfn.XLOOKUP(C26,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>旋风斩</v>
       </c>
       <c r="F26">
@@ -15403,8 +15403,8 @@
         <f t="shared" si="4"/>
         <v>8</v>
       </c>
-      <c r="E27" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C27,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E27" s="14" t="str" cm="1">
+        <f t="array" ref="E27">_xlfn.XLOOKUP(C27,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>旋风斩</v>
       </c>
       <c r="F27">
@@ -15437,8 +15437,8 @@
         <f t="shared" si="4"/>
         <v>9</v>
       </c>
-      <c r="E28" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C28,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E28" s="14" t="str" cm="1">
+        <f t="array" ref="E28">_xlfn.XLOOKUP(C28,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>旋风斩</v>
       </c>
       <c r="F28">
@@ -15471,8 +15471,8 @@
         <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="E29" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C29,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E29" s="14" t="str" cm="1">
+        <f t="array" ref="E29">_xlfn.XLOOKUP(C29,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>旋风斩</v>
       </c>
       <c r="F29">
@@ -15505,8 +15505,8 @@
         <f t="shared" si="4"/>
         <v>11</v>
       </c>
-      <c r="E30" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C30,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E30" s="14" t="str" cm="1">
+        <f t="array" ref="E30">_xlfn.XLOOKUP(C30,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>旋风斩</v>
       </c>
       <c r="F30">
@@ -15539,8 +15539,8 @@
         <f t="shared" si="4"/>
         <v>12</v>
       </c>
-      <c r="E31" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C31,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E31" s="14" t="str" cm="1">
+        <f t="array" ref="E31">_xlfn.XLOOKUP(C31,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>旋风斩</v>
       </c>
       <c r="F31">
@@ -15573,8 +15573,8 @@
         <f t="shared" si="4"/>
         <v>13</v>
       </c>
-      <c r="E32" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C32,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E32" s="14" t="str" cm="1">
+        <f t="array" ref="E32">_xlfn.XLOOKUP(C32,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>旋风斩</v>
       </c>
       <c r="F32">
@@ -15607,8 +15607,8 @@
         <f t="shared" si="4"/>
         <v>14</v>
       </c>
-      <c r="E33" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C33,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E33" s="14" t="str" cm="1">
+        <f t="array" ref="E33">_xlfn.XLOOKUP(C33,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>旋风斩</v>
       </c>
       <c r="F33">
@@ -15641,8 +15641,8 @@
         <f t="shared" si="4"/>
         <v>15</v>
       </c>
-      <c r="E34" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C34,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E34" s="14" t="str" cm="1">
+        <f t="array" ref="E34">_xlfn.XLOOKUP(C34,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>旋风斩</v>
       </c>
       <c r="F34">
@@ -15675,8 +15675,8 @@
         <f t="shared" si="4"/>
         <v>16</v>
       </c>
-      <c r="E35" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C35,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E35" s="14" t="str" cm="1">
+        <f t="array" ref="E35">_xlfn.XLOOKUP(C35,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>旋风斩</v>
       </c>
       <c r="F35">
@@ -15709,8 +15709,8 @@
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="E36" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C36,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E36" s="14" t="str" cm="1">
+        <f t="array" ref="E36">_xlfn.XLOOKUP(C36,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>月光斩</v>
       </c>
       <c r="F36">
@@ -15743,8 +15743,8 @@
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="E37" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C37,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E37" s="14" t="str" cm="1">
+        <f t="array" ref="E37">_xlfn.XLOOKUP(C37,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>月光斩</v>
       </c>
       <c r="F37">
@@ -15777,8 +15777,8 @@
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
-      <c r="E38" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C38,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E38" s="14" t="str" cm="1">
+        <f t="array" ref="E38">_xlfn.XLOOKUP(C38,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>月光斩</v>
       </c>
       <c r="F38">
@@ -15811,8 +15811,8 @@
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
-      <c r="E39" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C39,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E39" s="14" t="str" cm="1">
+        <f t="array" ref="E39">_xlfn.XLOOKUP(C39,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>月光斩</v>
       </c>
       <c r="F39">
@@ -15845,8 +15845,8 @@
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="E40" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C40,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E40" s="14" t="str" cm="1">
+        <f t="array" ref="E40">_xlfn.XLOOKUP(C40,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>月光斩</v>
       </c>
       <c r="F40">
@@ -15879,8 +15879,8 @@
         <f t="shared" si="4"/>
         <v>6</v>
       </c>
-      <c r="E41" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C41,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E41" s="14" t="str" cm="1">
+        <f t="array" ref="E41">_xlfn.XLOOKUP(C41,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>月光斩</v>
       </c>
       <c r="F41">
@@ -15913,8 +15913,8 @@
         <f t="shared" si="4"/>
         <v>7</v>
       </c>
-      <c r="E42" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C42,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E42" s="14" t="str" cm="1">
+        <f t="array" ref="E42">_xlfn.XLOOKUP(C42,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>月光斩</v>
       </c>
       <c r="F42">
@@ -15947,8 +15947,8 @@
         <f t="shared" si="4"/>
         <v>8</v>
       </c>
-      <c r="E43" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C43,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E43" s="14" t="str" cm="1">
+        <f t="array" ref="E43">_xlfn.XLOOKUP(C43,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>月光斩</v>
       </c>
       <c r="F43">
@@ -15981,8 +15981,8 @@
         <f t="shared" si="4"/>
         <v>9</v>
       </c>
-      <c r="E44" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C44,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E44" s="14" t="str" cm="1">
+        <f t="array" ref="E44">_xlfn.XLOOKUP(C44,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>月光斩</v>
       </c>
       <c r="F44">
@@ -16015,8 +16015,8 @@
         <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="E45" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C45,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E45" s="14" t="str" cm="1">
+        <f t="array" ref="E45">_xlfn.XLOOKUP(C45,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>月光斩</v>
       </c>
       <c r="F45">
@@ -16049,8 +16049,8 @@
         <f t="shared" si="4"/>
         <v>11</v>
       </c>
-      <c r="E46" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C46,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E46" s="14" t="str" cm="1">
+        <f t="array" ref="E46">_xlfn.XLOOKUP(C46,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>月光斩</v>
       </c>
       <c r="F46">
@@ -16083,8 +16083,8 @@
         <f t="shared" si="4"/>
         <v>12</v>
       </c>
-      <c r="E47" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C47,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E47" s="14" t="str" cm="1">
+        <f t="array" ref="E47">_xlfn.XLOOKUP(C47,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>月光斩</v>
       </c>
       <c r="F47">
@@ -16117,8 +16117,8 @@
         <f t="shared" si="4"/>
         <v>13</v>
       </c>
-      <c r="E48" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C48,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E48" s="14" t="str" cm="1">
+        <f t="array" ref="E48">_xlfn.XLOOKUP(C48,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>月光斩</v>
       </c>
       <c r="F48">
@@ -16151,8 +16151,8 @@
         <f t="shared" si="4"/>
         <v>14</v>
       </c>
-      <c r="E49" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C49,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E49" s="14" t="str" cm="1">
+        <f t="array" ref="E49">_xlfn.XLOOKUP(C49,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>月光斩</v>
       </c>
       <c r="F49">
@@ -16185,8 +16185,8 @@
         <f t="shared" si="4"/>
         <v>15</v>
       </c>
-      <c r="E50" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C50,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E50" s="14" t="str" cm="1">
+        <f t="array" ref="E50">_xlfn.XLOOKUP(C50,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>月光斩</v>
       </c>
       <c r="F50">
@@ -16219,8 +16219,8 @@
         <f t="shared" si="4"/>
         <v>16</v>
       </c>
-      <c r="E51" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C51,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E51" s="14" t="str" cm="1">
+        <f t="array" ref="E51">_xlfn.XLOOKUP(C51,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>月光斩</v>
       </c>
       <c r="F51">
@@ -16253,8 +16253,8 @@
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="E52" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C52,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E52" s="14" t="str" cm="1">
+        <f t="array" ref="E52">_xlfn.XLOOKUP(C52,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>混沌刺击</v>
       </c>
       <c r="F52">
@@ -16287,8 +16287,8 @@
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="E53" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C53,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E53" s="14" t="str" cm="1">
+        <f t="array" ref="E53">_xlfn.XLOOKUP(C53,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>混沌刺击</v>
       </c>
       <c r="F53">
@@ -16321,8 +16321,8 @@
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
-      <c r="E54" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C54,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E54" s="14" t="str" cm="1">
+        <f t="array" ref="E54">_xlfn.XLOOKUP(C54,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>混沌刺击</v>
       </c>
       <c r="F54">
@@ -16355,8 +16355,8 @@
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
-      <c r="E55" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C55,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E55" s="14" t="str" cm="1">
+        <f t="array" ref="E55">_xlfn.XLOOKUP(C55,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>混沌刺击</v>
       </c>
       <c r="F55">
@@ -16389,8 +16389,8 @@
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="E56" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C56,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E56" s="14" t="str" cm="1">
+        <f t="array" ref="E56">_xlfn.XLOOKUP(C56,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>混沌刺击</v>
       </c>
       <c r="F56">
@@ -16423,8 +16423,8 @@
         <f t="shared" si="4"/>
         <v>6</v>
       </c>
-      <c r="E57" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C57,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E57" s="14" t="str" cm="1">
+        <f t="array" ref="E57">_xlfn.XLOOKUP(C57,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>混沌刺击</v>
       </c>
       <c r="F57">
@@ -16457,8 +16457,8 @@
         <f t="shared" si="4"/>
         <v>7</v>
       </c>
-      <c r="E58" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C58,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E58" s="14" t="str" cm="1">
+        <f t="array" ref="E58">_xlfn.XLOOKUP(C58,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>混沌刺击</v>
       </c>
       <c r="F58">
@@ -16491,8 +16491,8 @@
         <f t="shared" si="4"/>
         <v>8</v>
       </c>
-      <c r="E59" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C59,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E59" s="14" t="str" cm="1">
+        <f t="array" ref="E59">_xlfn.XLOOKUP(C59,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>混沌刺击</v>
       </c>
       <c r="F59">
@@ -16525,8 +16525,8 @@
         <f t="shared" si="4"/>
         <v>9</v>
       </c>
-      <c r="E60" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C60,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E60" s="14" t="str" cm="1">
+        <f t="array" ref="E60">_xlfn.XLOOKUP(C60,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>混沌刺击</v>
       </c>
       <c r="F60">
@@ -16559,8 +16559,8 @@
         <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="E61" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C61,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E61" s="14" t="str" cm="1">
+        <f t="array" ref="E61">_xlfn.XLOOKUP(C61,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>混沌刺击</v>
       </c>
       <c r="F61">
@@ -16593,8 +16593,8 @@
         <f t="shared" si="4"/>
         <v>11</v>
       </c>
-      <c r="E62" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C62,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E62" s="14" t="str" cm="1">
+        <f t="array" ref="E62">_xlfn.XLOOKUP(C62,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>混沌刺击</v>
       </c>
       <c r="F62">
@@ -16627,8 +16627,8 @@
         <f t="shared" si="4"/>
         <v>12</v>
       </c>
-      <c r="E63" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C63,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E63" s="14" t="str" cm="1">
+        <f t="array" ref="E63">_xlfn.XLOOKUP(C63,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>混沌刺击</v>
       </c>
       <c r="F63">
@@ -16661,8 +16661,8 @@
         <f t="shared" si="4"/>
         <v>13</v>
       </c>
-      <c r="E64" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C64,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E64" s="14" t="str" cm="1">
+        <f t="array" ref="E64">_xlfn.XLOOKUP(C64,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>混沌刺击</v>
       </c>
       <c r="F64">
@@ -16695,8 +16695,8 @@
         <f t="shared" si="4"/>
         <v>14</v>
       </c>
-      <c r="E65" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C65,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E65" s="14" t="str" cm="1">
+        <f t="array" ref="E65">_xlfn.XLOOKUP(C65,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>混沌刺击</v>
       </c>
       <c r="F65">
@@ -16729,8 +16729,8 @@
         <f t="shared" si="4"/>
         <v>15</v>
       </c>
-      <c r="E66" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C66,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E66" s="14" t="str" cm="1">
+        <f t="array" ref="E66">_xlfn.XLOOKUP(C66,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>混沌刺击</v>
       </c>
       <c r="F66">
@@ -16763,8 +16763,8 @@
         <f t="shared" si="4"/>
         <v>16</v>
       </c>
-      <c r="E67" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C67,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E67" s="14" t="str" cm="1">
+        <f t="array" ref="E67">_xlfn.XLOOKUP(C67,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>混沌刺击</v>
       </c>
       <c r="F67">
@@ -16797,8 +16797,8 @@
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="E68" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C68,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E68" s="14" t="str" cm="1">
+        <f t="array" ref="E68">_xlfn.XLOOKUP(C68,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>冥地喷涌</v>
       </c>
       <c r="F68">
@@ -16830,8 +16830,8 @@
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="E69" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C69,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E69" s="14" t="str" cm="1">
+        <f t="array" ref="E69">_xlfn.XLOOKUP(C69,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>冥地喷涌</v>
       </c>
       <c r="F69">
@@ -16863,8 +16863,8 @@
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
-      <c r="E70" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C70,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E70" s="14" t="str" cm="1">
+        <f t="array" ref="E70">_xlfn.XLOOKUP(C70,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>冥地喷涌</v>
       </c>
       <c r="F70">
@@ -16896,8 +16896,8 @@
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
-      <c r="E71" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C71,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E71" s="14" t="str" cm="1">
+        <f t="array" ref="E71">_xlfn.XLOOKUP(C71,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>冥地喷涌</v>
       </c>
       <c r="F71">
@@ -16929,8 +16929,8 @@
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="E72" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C72,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E72" s="14" t="str" cm="1">
+        <f t="array" ref="E72">_xlfn.XLOOKUP(C72,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>冥地喷涌</v>
       </c>
       <c r="F72">
@@ -16962,8 +16962,8 @@
         <f t="shared" si="4"/>
         <v>6</v>
       </c>
-      <c r="E73" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C73,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E73" s="14" t="str" cm="1">
+        <f t="array" ref="E73">_xlfn.XLOOKUP(C73,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>冥地喷涌</v>
       </c>
       <c r="F73">
@@ -16995,8 +16995,8 @@
         <f t="shared" si="4"/>
         <v>7</v>
       </c>
-      <c r="E74" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C74,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E74" s="14" t="str" cm="1">
+        <f t="array" ref="E74">_xlfn.XLOOKUP(C74,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>冥地喷涌</v>
       </c>
       <c r="F74">
@@ -17028,8 +17028,8 @@
         <f t="shared" si="4"/>
         <v>8</v>
       </c>
-      <c r="E75" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C75,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E75" s="14" t="str" cm="1">
+        <f t="array" ref="E75">_xlfn.XLOOKUP(C75,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>冥地喷涌</v>
       </c>
       <c r="F75">
@@ -17061,8 +17061,8 @@
         <f t="shared" si="4"/>
         <v>9</v>
       </c>
-      <c r="E76" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C76,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E76" s="14" t="str" cm="1">
+        <f t="array" ref="E76">_xlfn.XLOOKUP(C76,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>冥地喷涌</v>
       </c>
       <c r="F76">
@@ -17094,8 +17094,8 @@
         <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="E77" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C77,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E77" s="14" t="str" cm="1">
+        <f t="array" ref="E77">_xlfn.XLOOKUP(C77,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>冥地喷涌</v>
       </c>
       <c r="F77">
@@ -17127,8 +17127,8 @@
         <f t="shared" si="4"/>
         <v>11</v>
       </c>
-      <c r="E78" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C78,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E78" s="14" t="str" cm="1">
+        <f t="array" ref="E78">_xlfn.XLOOKUP(C78,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>冥地喷涌</v>
       </c>
       <c r="F78">
@@ -17160,8 +17160,8 @@
         <f t="shared" si="4"/>
         <v>12</v>
       </c>
-      <c r="E79" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C79,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E79" s="14" t="str" cm="1">
+        <f t="array" ref="E79">_xlfn.XLOOKUP(C79,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>冥地喷涌</v>
       </c>
       <c r="F79">
@@ -17193,8 +17193,8 @@
         <f t="shared" si="4"/>
         <v>13</v>
       </c>
-      <c r="E80" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C80,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E80" s="14" t="str" cm="1">
+        <f t="array" ref="E80">_xlfn.XLOOKUP(C80,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>冥地喷涌</v>
       </c>
       <c r="F80">
@@ -17226,8 +17226,8 @@
         <f t="shared" si="4"/>
         <v>14</v>
       </c>
-      <c r="E81" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C81,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E81" s="14" t="str" cm="1">
+        <f t="array" ref="E81">_xlfn.XLOOKUP(C81,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>冥地喷涌</v>
       </c>
       <c r="F81">
@@ -17259,8 +17259,8 @@
         <f t="shared" si="4"/>
         <v>15</v>
       </c>
-      <c r="E82" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C82,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E82" s="14" t="str" cm="1">
+        <f t="array" ref="E82">_xlfn.XLOOKUP(C82,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>冥地喷涌</v>
       </c>
       <c r="F82">
@@ -17292,8 +17292,8 @@
         <f t="shared" si="4"/>
         <v>16</v>
       </c>
-      <c r="E83" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C83,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E83" s="14" t="str" cm="1">
+        <f t="array" ref="E83">_xlfn.XLOOKUP(C83,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>冥地喷涌</v>
       </c>
       <c r="F83">
@@ -17325,8 +17325,8 @@
         <f t="shared" ref="D84:D100" si="8">D68</f>
         <v>1</v>
       </c>
-      <c r="E84" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C84,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E84" s="14" t="str" cm="1">
+        <f t="array" ref="E84">_xlfn.XLOOKUP(C84,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>冰霜新星</v>
       </c>
       <c r="F84">
@@ -17358,8 +17358,8 @@
         <f t="shared" si="8"/>
         <v>2</v>
       </c>
-      <c r="E85" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C85,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E85" s="14" t="str" cm="1">
+        <f t="array" ref="E85">_xlfn.XLOOKUP(C85,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>冰霜新星</v>
       </c>
       <c r="F85">
@@ -17391,8 +17391,8 @@
         <f t="shared" si="8"/>
         <v>3</v>
       </c>
-      <c r="E86" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C86,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E86" s="14" t="str" cm="1">
+        <f t="array" ref="E86">_xlfn.XLOOKUP(C86,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>冰霜新星</v>
       </c>
       <c r="F86">
@@ -17424,8 +17424,8 @@
         <f t="shared" si="8"/>
         <v>4</v>
       </c>
-      <c r="E87" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C87,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E87" s="14" t="str" cm="1">
+        <f t="array" ref="E87">_xlfn.XLOOKUP(C87,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>冰霜新星</v>
       </c>
       <c r="F87">
@@ -17457,8 +17457,8 @@
         <f t="shared" si="8"/>
         <v>5</v>
       </c>
-      <c r="E88" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C88,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E88" s="14" t="str" cm="1">
+        <f t="array" ref="E88">_xlfn.XLOOKUP(C88,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>冰霜新星</v>
       </c>
       <c r="F88">
@@ -17490,8 +17490,8 @@
         <f t="shared" si="8"/>
         <v>6</v>
       </c>
-      <c r="E89" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C89,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E89" s="14" t="str" cm="1">
+        <f t="array" ref="E89">_xlfn.XLOOKUP(C89,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>冰霜新星</v>
       </c>
       <c r="F89">
@@ -17523,8 +17523,8 @@
         <f t="shared" si="8"/>
         <v>7</v>
       </c>
-      <c r="E90" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C90,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E90" s="14" t="str" cm="1">
+        <f t="array" ref="E90">_xlfn.XLOOKUP(C90,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>冰霜新星</v>
       </c>
       <c r="F90">
@@ -17556,8 +17556,8 @@
         <f t="shared" si="8"/>
         <v>8</v>
       </c>
-      <c r="E91" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C91,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E91" s="14" t="str" cm="1">
+        <f t="array" ref="E91">_xlfn.XLOOKUP(C91,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>冰霜新星</v>
       </c>
       <c r="F91">
@@ -17589,8 +17589,8 @@
         <f t="shared" si="8"/>
         <v>9</v>
       </c>
-      <c r="E92" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C92,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E92" s="14" t="str" cm="1">
+        <f t="array" ref="E92">_xlfn.XLOOKUP(C92,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>冰霜新星</v>
       </c>
       <c r="F92">
@@ -17622,8 +17622,8 @@
         <f t="shared" si="8"/>
         <v>10</v>
       </c>
-      <c r="E93" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C93,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E93" s="14" t="str" cm="1">
+        <f t="array" ref="E93">_xlfn.XLOOKUP(C93,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>冰霜新星</v>
       </c>
       <c r="F93">
@@ -17655,8 +17655,8 @@
         <f t="shared" si="8"/>
         <v>11</v>
       </c>
-      <c r="E94" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C94,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E94" s="14" t="str" cm="1">
+        <f t="array" ref="E94">_xlfn.XLOOKUP(C94,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>冰霜新星</v>
       </c>
       <c r="F94">
@@ -17688,8 +17688,8 @@
         <f t="shared" si="8"/>
         <v>12</v>
       </c>
-      <c r="E95" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C95,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E95" s="14" t="str" cm="1">
+        <f t="array" ref="E95">_xlfn.XLOOKUP(C95,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>冰霜新星</v>
       </c>
       <c r="F95">
@@ -17721,8 +17721,8 @@
         <f t="shared" si="8"/>
         <v>13</v>
       </c>
-      <c r="E96" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C96,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E96" s="14" t="str" cm="1">
+        <f t="array" ref="E96">_xlfn.XLOOKUP(C96,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>冰霜新星</v>
       </c>
       <c r="F96">
@@ -17754,8 +17754,8 @@
         <f t="shared" si="8"/>
         <v>14</v>
       </c>
-      <c r="E97" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C97,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E97" s="14" t="str" cm="1">
+        <f t="array" ref="E97">_xlfn.XLOOKUP(C97,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>冰霜新星</v>
       </c>
       <c r="F97">
@@ -17787,8 +17787,8 @@
         <f t="shared" si="8"/>
         <v>15</v>
       </c>
-      <c r="E98" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C98,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E98" s="14" t="str" cm="1">
+        <f t="array" ref="E98">_xlfn.XLOOKUP(C98,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>冰霜新星</v>
       </c>
       <c r="F98">
@@ -17820,8 +17820,8 @@
         <f t="shared" si="8"/>
         <v>16</v>
       </c>
-      <c r="E99" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C99,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E99" s="14" t="str" cm="1">
+        <f t="array" ref="E99">_xlfn.XLOOKUP(C99,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>冰霜新星</v>
       </c>
       <c r="F99">
@@ -17853,8 +17853,8 @@
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="E100" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C100,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E100" s="14" t="str" cm="1">
+        <f t="array" ref="E100">_xlfn.XLOOKUP(C100,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>移形换影</v>
       </c>
       <c r="F100">
@@ -17885,8 +17885,8 @@
       <c r="D101" s="14">
         <v>2</v>
       </c>
-      <c r="E101" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C101,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E101" s="14" t="str" cm="1">
+        <f t="array" ref="E101">_xlfn.XLOOKUP(C101,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>移形换影</v>
       </c>
       <c r="F101">
@@ -17917,8 +17917,8 @@
         <f t="shared" ref="D102:D115" si="13">D86</f>
         <v>3</v>
       </c>
-      <c r="E102" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C102,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E102" s="14" t="str" cm="1">
+        <f t="array" ref="E102">_xlfn.XLOOKUP(C102,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>移形换影</v>
       </c>
       <c r="F102">
@@ -17949,8 +17949,8 @@
         <f t="shared" si="13"/>
         <v>4</v>
       </c>
-      <c r="E103" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C103,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E103" s="14" t="str" cm="1">
+        <f t="array" ref="E103">_xlfn.XLOOKUP(C103,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>移形换影</v>
       </c>
       <c r="F103">
@@ -17981,8 +17981,8 @@
         <f t="shared" si="13"/>
         <v>5</v>
       </c>
-      <c r="E104" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C104,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E104" s="14" t="str" cm="1">
+        <f t="array" ref="E104">_xlfn.XLOOKUP(C104,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>移形换影</v>
       </c>
       <c r="F104">
@@ -18013,8 +18013,8 @@
         <f t="shared" si="13"/>
         <v>6</v>
       </c>
-      <c r="E105" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C105,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E105" s="14" t="str" cm="1">
+        <f t="array" ref="E105">_xlfn.XLOOKUP(C105,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>移形换影</v>
       </c>
       <c r="F105">
@@ -18045,8 +18045,8 @@
         <f t="shared" si="13"/>
         <v>7</v>
       </c>
-      <c r="E106" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C106,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E106" s="14" t="str" cm="1">
+        <f t="array" ref="E106">_xlfn.XLOOKUP(C106,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>移形换影</v>
       </c>
       <c r="F106">
@@ -18077,8 +18077,8 @@
         <f t="shared" si="13"/>
         <v>8</v>
       </c>
-      <c r="E107" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C107,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E107" s="14" t="str" cm="1">
+        <f t="array" ref="E107">_xlfn.XLOOKUP(C107,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>移形换影</v>
       </c>
       <c r="F107">
@@ -18109,8 +18109,8 @@
         <f t="shared" si="13"/>
         <v>9</v>
       </c>
-      <c r="E108" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C108,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E108" s="14" t="str" cm="1">
+        <f t="array" ref="E108">_xlfn.XLOOKUP(C108,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>移形换影</v>
       </c>
       <c r="F108">
@@ -18141,8 +18141,8 @@
         <f t="shared" si="13"/>
         <v>10</v>
       </c>
-      <c r="E109" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C109,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E109" s="14" t="str" cm="1">
+        <f t="array" ref="E109">_xlfn.XLOOKUP(C109,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>移形换影</v>
       </c>
       <c r="F109">
@@ -18173,8 +18173,8 @@
         <f t="shared" si="13"/>
         <v>11</v>
       </c>
-      <c r="E110" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C110,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E110" s="14" t="str" cm="1">
+        <f t="array" ref="E110">_xlfn.XLOOKUP(C110,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>移形换影</v>
       </c>
       <c r="F110">
@@ -18205,8 +18205,8 @@
         <f t="shared" si="13"/>
         <v>12</v>
       </c>
-      <c r="E111" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C111,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E111" s="14" t="str" cm="1">
+        <f t="array" ref="E111">_xlfn.XLOOKUP(C111,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>移形换影</v>
       </c>
       <c r="F111">
@@ -18237,8 +18237,8 @@
         <f t="shared" si="13"/>
         <v>13</v>
       </c>
-      <c r="E112" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C112,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E112" s="14" t="str" cm="1">
+        <f t="array" ref="E112">_xlfn.XLOOKUP(C112,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>移形换影</v>
       </c>
       <c r="F112">
@@ -18269,8 +18269,8 @@
         <f t="shared" si="13"/>
         <v>14</v>
       </c>
-      <c r="E113" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C113,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E113" s="14" t="str" cm="1">
+        <f t="array" ref="E113">_xlfn.XLOOKUP(C113,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>移形换影</v>
       </c>
       <c r="F113">
@@ -18301,8 +18301,8 @@
         <f t="shared" si="13"/>
         <v>15</v>
       </c>
-      <c r="E114" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C114,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E114" s="14" t="str" cm="1">
+        <f t="array" ref="E114">_xlfn.XLOOKUP(C114,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>移形换影</v>
       </c>
       <c r="F114">
@@ -18333,8 +18333,8 @@
         <f t="shared" si="13"/>
         <v>16</v>
       </c>
-      <c r="E115" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C115,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E115" s="14" t="str" cm="1">
+        <f t="array" ref="E115">_xlfn.XLOOKUP(C115,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>移形换影</v>
       </c>
       <c r="F115">
@@ -18365,8 +18365,8 @@
         <f t="shared" ref="D116:D163" si="14">D100</f>
         <v>1</v>
       </c>
-      <c r="E116" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C116,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E116" s="14" t="str" cm="1">
+        <f t="array" ref="E116">_xlfn.XLOOKUP(C116,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>法术旋龙</v>
       </c>
       <c r="F116">
@@ -18399,8 +18399,8 @@
         <f t="shared" si="14"/>
         <v>2</v>
       </c>
-      <c r="E117" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C117,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E117" s="14" t="str" cm="1">
+        <f t="array" ref="E117">_xlfn.XLOOKUP(C117,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>法术旋龙</v>
       </c>
       <c r="F117">
@@ -18433,8 +18433,8 @@
         <f t="shared" si="14"/>
         <v>3</v>
       </c>
-      <c r="E118" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C118,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E118" s="14" t="str" cm="1">
+        <f t="array" ref="E118">_xlfn.XLOOKUP(C118,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>法术旋龙</v>
       </c>
       <c r="F118">
@@ -18467,8 +18467,8 @@
         <f t="shared" si="14"/>
         <v>4</v>
       </c>
-      <c r="E119" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C119,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E119" s="14" t="str" cm="1">
+        <f t="array" ref="E119">_xlfn.XLOOKUP(C119,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>法术旋龙</v>
       </c>
       <c r="F119">
@@ -18501,8 +18501,8 @@
         <f t="shared" si="14"/>
         <v>5</v>
       </c>
-      <c r="E120" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C120,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E120" s="14" t="str" cm="1">
+        <f t="array" ref="E120">_xlfn.XLOOKUP(C120,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>法术旋龙</v>
       </c>
       <c r="F120">
@@ -18535,8 +18535,8 @@
         <f t="shared" si="14"/>
         <v>6</v>
       </c>
-      <c r="E121" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C121,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E121" s="14" t="str" cm="1">
+        <f t="array" ref="E121">_xlfn.XLOOKUP(C121,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>法术旋龙</v>
       </c>
       <c r="F121">
@@ -18569,8 +18569,8 @@
         <f t="shared" si="14"/>
         <v>7</v>
       </c>
-      <c r="E122" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C122,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E122" s="14" t="str" cm="1">
+        <f t="array" ref="E122">_xlfn.XLOOKUP(C122,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>法术旋龙</v>
       </c>
       <c r="F122">
@@ -18603,8 +18603,8 @@
         <f t="shared" si="14"/>
         <v>8</v>
       </c>
-      <c r="E123" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C123,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E123" s="14" t="str" cm="1">
+        <f t="array" ref="E123">_xlfn.XLOOKUP(C123,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>法术旋龙</v>
       </c>
       <c r="F123">
@@ -18637,8 +18637,8 @@
         <f t="shared" si="14"/>
         <v>9</v>
       </c>
-      <c r="E124" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C124,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E124" s="14" t="str" cm="1">
+        <f t="array" ref="E124">_xlfn.XLOOKUP(C124,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>法术旋龙</v>
       </c>
       <c r="F124">
@@ -18671,8 +18671,8 @@
         <f t="shared" si="14"/>
         <v>10</v>
       </c>
-      <c r="E125" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C125,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E125" s="14" t="str" cm="1">
+        <f t="array" ref="E125">_xlfn.XLOOKUP(C125,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>法术旋龙</v>
       </c>
       <c r="F125">
@@ -18705,8 +18705,8 @@
         <f t="shared" si="14"/>
         <v>11</v>
       </c>
-      <c r="E126" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C126,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E126" s="14" t="str" cm="1">
+        <f t="array" ref="E126">_xlfn.XLOOKUP(C126,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>法术旋龙</v>
       </c>
       <c r="F126">
@@ -18739,8 +18739,8 @@
         <f t="shared" si="14"/>
         <v>12</v>
       </c>
-      <c r="E127" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C127,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E127" s="14" t="str" cm="1">
+        <f t="array" ref="E127">_xlfn.XLOOKUP(C127,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>法术旋龙</v>
       </c>
       <c r="F127">
@@ -18773,8 +18773,8 @@
         <f t="shared" si="14"/>
         <v>13</v>
       </c>
-      <c r="E128" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C128,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E128" s="14" t="str" cm="1">
+        <f t="array" ref="E128">_xlfn.XLOOKUP(C128,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>法术旋龙</v>
       </c>
       <c r="F128">
@@ -18807,8 +18807,8 @@
         <f t="shared" si="14"/>
         <v>14</v>
       </c>
-      <c r="E129" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C129,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E129" s="14" t="str" cm="1">
+        <f t="array" ref="E129">_xlfn.XLOOKUP(C129,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>法术旋龙</v>
       </c>
       <c r="F129">
@@ -18841,8 +18841,8 @@
         <f t="shared" si="14"/>
         <v>15</v>
       </c>
-      <c r="E130" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C130,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E130" s="14" t="str" cm="1">
+        <f t="array" ref="E130">_xlfn.XLOOKUP(C130,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>法术旋龙</v>
       </c>
       <c r="F130">
@@ -18875,8 +18875,8 @@
         <f t="shared" si="14"/>
         <v>16</v>
       </c>
-      <c r="E131" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C131,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E131" s="14" t="str" cm="1">
+        <f t="array" ref="E131">_xlfn.XLOOKUP(C131,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>法术旋龙</v>
       </c>
       <c r="F131">
@@ -18909,8 +18909,8 @@
         <f t="shared" si="14"/>
         <v>1</v>
       </c>
-      <c r="E132" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C132,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E132" s="14" t="str" cm="1">
+        <f t="array" ref="E132">_xlfn.XLOOKUP(C132,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>火球术</v>
       </c>
       <c r="F132">
@@ -18943,8 +18943,8 @@
         <f t="shared" si="14"/>
         <v>2</v>
       </c>
-      <c r="E133" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C133,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E133" s="14" t="str" cm="1">
+        <f t="array" ref="E133">_xlfn.XLOOKUP(C133,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>火球术</v>
       </c>
       <c r="F133">
@@ -18977,8 +18977,8 @@
         <f t="shared" si="14"/>
         <v>3</v>
       </c>
-      <c r="E134" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C134,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E134" s="14" t="str" cm="1">
+        <f t="array" ref="E134">_xlfn.XLOOKUP(C134,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>火球术</v>
       </c>
       <c r="F134">
@@ -19011,8 +19011,8 @@
         <f t="shared" si="14"/>
         <v>4</v>
       </c>
-      <c r="E135" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C135,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E135" s="14" t="str" cm="1">
+        <f t="array" ref="E135">_xlfn.XLOOKUP(C135,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>火球术</v>
       </c>
       <c r="F135">
@@ -19045,8 +19045,8 @@
         <f t="shared" si="14"/>
         <v>5</v>
       </c>
-      <c r="E136" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C136,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E136" s="14" t="str" cm="1">
+        <f t="array" ref="E136">_xlfn.XLOOKUP(C136,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>火球术</v>
       </c>
       <c r="F136">
@@ -19079,8 +19079,8 @@
         <f t="shared" si="14"/>
         <v>6</v>
       </c>
-      <c r="E137" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C137,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E137" s="14" t="str" cm="1">
+        <f t="array" ref="E137">_xlfn.XLOOKUP(C137,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>火球术</v>
       </c>
       <c r="F137">
@@ -19113,8 +19113,8 @@
         <f t="shared" si="14"/>
         <v>7</v>
       </c>
-      <c r="E138" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C138,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E138" s="14" t="str" cm="1">
+        <f t="array" ref="E138">_xlfn.XLOOKUP(C138,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>火球术</v>
       </c>
       <c r="F138">
@@ -19147,8 +19147,8 @@
         <f t="shared" si="14"/>
         <v>8</v>
       </c>
-      <c r="E139" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C139,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E139" s="14" t="str" cm="1">
+        <f t="array" ref="E139">_xlfn.XLOOKUP(C139,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>火球术</v>
       </c>
       <c r="F139">
@@ -19181,8 +19181,8 @@
         <f t="shared" si="14"/>
         <v>9</v>
       </c>
-      <c r="E140" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C140,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E140" s="14" t="str" cm="1">
+        <f t="array" ref="E140">_xlfn.XLOOKUP(C140,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>火球术</v>
       </c>
       <c r="F140">
@@ -19215,8 +19215,8 @@
         <f t="shared" si="14"/>
         <v>10</v>
       </c>
-      <c r="E141" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C141,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E141" s="14" t="str" cm="1">
+        <f t="array" ref="E141">_xlfn.XLOOKUP(C141,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>火球术</v>
       </c>
       <c r="F141">
@@ -19249,8 +19249,8 @@
         <f t="shared" si="14"/>
         <v>11</v>
       </c>
-      <c r="E142" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C142,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E142" s="14" t="str" cm="1">
+        <f t="array" ref="E142">_xlfn.XLOOKUP(C142,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>火球术</v>
       </c>
       <c r="F142">
@@ -19283,8 +19283,8 @@
         <f t="shared" si="14"/>
         <v>12</v>
       </c>
-      <c r="E143" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C143,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E143" s="14" t="str" cm="1">
+        <f t="array" ref="E143">_xlfn.XLOOKUP(C143,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>火球术</v>
       </c>
       <c r="F143">
@@ -19317,8 +19317,8 @@
         <f t="shared" si="14"/>
         <v>13</v>
       </c>
-      <c r="E144" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C144,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E144" s="14" t="str" cm="1">
+        <f t="array" ref="E144">_xlfn.XLOOKUP(C144,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>火球术</v>
       </c>
       <c r="F144">
@@ -19351,8 +19351,8 @@
         <f t="shared" si="14"/>
         <v>14</v>
       </c>
-      <c r="E145" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C145,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E145" s="14" t="str" cm="1">
+        <f t="array" ref="E145">_xlfn.XLOOKUP(C145,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>火球术</v>
       </c>
       <c r="F145">
@@ -19385,8 +19385,8 @@
         <f t="shared" si="14"/>
         <v>15</v>
       </c>
-      <c r="E146" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C146,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E146" s="14" t="str" cm="1">
+        <f t="array" ref="E146">_xlfn.XLOOKUP(C146,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>火球术</v>
       </c>
       <c r="F146">
@@ -19419,8 +19419,8 @@
         <f t="shared" si="14"/>
         <v>16</v>
       </c>
-      <c r="E147" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C147,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E147" s="14" t="str" cm="1">
+        <f t="array" ref="E147">_xlfn.XLOOKUP(C147,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>火球术</v>
       </c>
       <c r="F147">
@@ -19453,8 +19453,8 @@
         <f t="shared" si="14"/>
         <v>1</v>
       </c>
-      <c r="E148" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C148,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E148" s="14" t="str" cm="1">
+        <f t="array" ref="E148">_xlfn.XLOOKUP(C148,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>混沌陨星</v>
       </c>
       <c r="F148">
@@ -19487,8 +19487,8 @@
         <f t="shared" si="14"/>
         <v>2</v>
       </c>
-      <c r="E149" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C149,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E149" s="14" t="str" cm="1">
+        <f t="array" ref="E149">_xlfn.XLOOKUP(C149,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>混沌陨星</v>
       </c>
       <c r="F149">
@@ -19521,8 +19521,8 @@
         <f t="shared" si="14"/>
         <v>3</v>
       </c>
-      <c r="E150" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C150,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E150" s="14" t="str" cm="1">
+        <f t="array" ref="E150">_xlfn.XLOOKUP(C150,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>混沌陨星</v>
       </c>
       <c r="F150">
@@ -19555,8 +19555,8 @@
         <f t="shared" si="14"/>
         <v>4</v>
       </c>
-      <c r="E151" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C151,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E151" s="14" t="str" cm="1">
+        <f t="array" ref="E151">_xlfn.XLOOKUP(C151,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>混沌陨星</v>
       </c>
       <c r="F151">
@@ -19589,8 +19589,8 @@
         <f t="shared" si="14"/>
         <v>5</v>
       </c>
-      <c r="E152" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C152,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E152" s="14" t="str" cm="1">
+        <f t="array" ref="E152">_xlfn.XLOOKUP(C152,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>混沌陨星</v>
       </c>
       <c r="F152">
@@ -19623,8 +19623,8 @@
         <f t="shared" si="14"/>
         <v>6</v>
       </c>
-      <c r="E153" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C153,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E153" s="14" t="str" cm="1">
+        <f t="array" ref="E153">_xlfn.XLOOKUP(C153,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>混沌陨星</v>
       </c>
       <c r="F153">
@@ -19657,8 +19657,8 @@
         <f t="shared" si="14"/>
         <v>7</v>
       </c>
-      <c r="E154" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C154,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E154" s="14" t="str" cm="1">
+        <f t="array" ref="E154">_xlfn.XLOOKUP(C154,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>混沌陨星</v>
       </c>
       <c r="F154">
@@ -19691,8 +19691,8 @@
         <f t="shared" si="14"/>
         <v>8</v>
       </c>
-      <c r="E155" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C155,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E155" s="14" t="str" cm="1">
+        <f t="array" ref="E155">_xlfn.XLOOKUP(C155,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>混沌陨星</v>
       </c>
       <c r="F155">
@@ -19725,8 +19725,8 @@
         <f t="shared" si="14"/>
         <v>9</v>
       </c>
-      <c r="E156" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C156,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E156" s="14" t="str" cm="1">
+        <f t="array" ref="E156">_xlfn.XLOOKUP(C156,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>混沌陨星</v>
       </c>
       <c r="F156">
@@ -19759,8 +19759,8 @@
         <f t="shared" si="14"/>
         <v>10</v>
       </c>
-      <c r="E157" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C157,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E157" s="14" t="str" cm="1">
+        <f t="array" ref="E157">_xlfn.XLOOKUP(C157,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>混沌陨星</v>
       </c>
       <c r="F157">
@@ -19793,8 +19793,8 @@
         <f t="shared" si="14"/>
         <v>11</v>
       </c>
-      <c r="E158" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C158,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E158" s="14" t="str" cm="1">
+        <f t="array" ref="E158">_xlfn.XLOOKUP(C158,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>混沌陨星</v>
       </c>
       <c r="F158">
@@ -19827,8 +19827,8 @@
         <f t="shared" si="14"/>
         <v>12</v>
       </c>
-      <c r="E159" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C159,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E159" s="14" t="str" cm="1">
+        <f t="array" ref="E159">_xlfn.XLOOKUP(C159,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>混沌陨星</v>
       </c>
       <c r="F159">
@@ -19861,8 +19861,8 @@
         <f t="shared" si="14"/>
         <v>13</v>
       </c>
-      <c r="E160" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C160,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E160" s="14" t="str" cm="1">
+        <f t="array" ref="E160">_xlfn.XLOOKUP(C160,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>混沌陨星</v>
       </c>
       <c r="F160">
@@ -19895,8 +19895,8 @@
         <f t="shared" si="14"/>
         <v>14</v>
       </c>
-      <c r="E161" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C161,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E161" s="14" t="str" cm="1">
+        <f t="array" ref="E161">_xlfn.XLOOKUP(C161,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>混沌陨星</v>
       </c>
       <c r="F161">
@@ -19929,8 +19929,8 @@
         <f t="shared" si="14"/>
         <v>15</v>
       </c>
-      <c r="E162" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C162,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E162" s="14" t="str" cm="1">
+        <f t="array" ref="E162">_xlfn.XLOOKUP(C162,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>混沌陨星</v>
       </c>
       <c r="F162">
@@ -19963,8 +19963,8 @@
         <f t="shared" si="14"/>
         <v>16</v>
       </c>
-      <c r="E163" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C163,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E163" s="14" t="str" cm="1">
+        <f t="array" ref="E163">_xlfn.XLOOKUP(C163,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>混沌陨星</v>
       </c>
       <c r="F163">
@@ -19996,8 +19996,8 @@
       <c r="D164" s="14">
         <v>1</v>
       </c>
-      <c r="E164" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C164,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E164" s="14" t="str" cm="1">
+        <f t="array" ref="E164">_xlfn.XLOOKUP(C164,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>闪电之捷</v>
       </c>
       <c r="F164">
@@ -20029,8 +20029,8 @@
       <c r="D165" s="14">
         <v>2</v>
       </c>
-      <c r="E165" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C165,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E165" s="14" t="str" cm="1">
+        <f t="array" ref="E165">_xlfn.XLOOKUP(C165,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>闪电之捷</v>
       </c>
       <c r="F165">
@@ -20062,8 +20062,8 @@
       <c r="D166" s="14">
         <v>3</v>
       </c>
-      <c r="E166" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C166,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E166" s="14" t="str" cm="1">
+        <f t="array" ref="E166">_xlfn.XLOOKUP(C166,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>闪电之捷</v>
       </c>
       <c r="F166">
@@ -20096,8 +20096,8 @@
         <f t="shared" ref="D167:D179" si="21">D23</f>
         <v>4</v>
       </c>
-      <c r="E167" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C167,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E167" s="14" t="str" cm="1">
+        <f t="array" ref="E167">_xlfn.XLOOKUP(C167,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>闪电之捷</v>
       </c>
       <c r="F167">
@@ -20130,8 +20130,8 @@
         <f t="shared" si="21"/>
         <v>5</v>
       </c>
-      <c r="E168" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C168,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E168" s="14" t="str" cm="1">
+        <f t="array" ref="E168">_xlfn.XLOOKUP(C168,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>闪电之捷</v>
       </c>
       <c r="F168">
@@ -20164,8 +20164,8 @@
         <f t="shared" si="21"/>
         <v>6</v>
       </c>
-      <c r="E169" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C169,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E169" s="14" t="str" cm="1">
+        <f t="array" ref="E169">_xlfn.XLOOKUP(C169,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>闪电之捷</v>
       </c>
       <c r="F169">
@@ -20198,8 +20198,8 @@
         <f t="shared" si="21"/>
         <v>7</v>
       </c>
-      <c r="E170" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C170,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E170" s="14" t="str" cm="1">
+        <f t="array" ref="E170">_xlfn.XLOOKUP(C170,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>闪电之捷</v>
       </c>
       <c r="F170">
@@ -20232,8 +20232,8 @@
         <f t="shared" si="21"/>
         <v>8</v>
       </c>
-      <c r="E171" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C171,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E171" s="14" t="str" cm="1">
+        <f t="array" ref="E171">_xlfn.XLOOKUP(C171,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>闪电之捷</v>
       </c>
       <c r="F171">
@@ -20266,8 +20266,8 @@
         <f t="shared" si="21"/>
         <v>9</v>
       </c>
-      <c r="E172" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C172,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E172" s="14" t="str" cm="1">
+        <f t="array" ref="E172">_xlfn.XLOOKUP(C172,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>闪电之捷</v>
       </c>
       <c r="F172">
@@ -20300,8 +20300,8 @@
         <f t="shared" si="21"/>
         <v>10</v>
       </c>
-      <c r="E173" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C173,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E173" s="14" t="str" cm="1">
+        <f t="array" ref="E173">_xlfn.XLOOKUP(C173,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>闪电之捷</v>
       </c>
       <c r="F173">
@@ -20334,8 +20334,8 @@
         <f t="shared" si="21"/>
         <v>11</v>
       </c>
-      <c r="E174" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C174,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E174" s="14" t="str" cm="1">
+        <f t="array" ref="E174">_xlfn.XLOOKUP(C174,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>闪电之捷</v>
       </c>
       <c r="F174">
@@ -20368,8 +20368,8 @@
         <f t="shared" si="21"/>
         <v>12</v>
       </c>
-      <c r="E175" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C175,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E175" s="14" t="str" cm="1">
+        <f t="array" ref="E175">_xlfn.XLOOKUP(C175,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>闪电之捷</v>
       </c>
       <c r="F175">
@@ -20402,8 +20402,8 @@
         <f t="shared" si="21"/>
         <v>13</v>
       </c>
-      <c r="E176" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C176,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E176" s="14" t="str" cm="1">
+        <f t="array" ref="E176">_xlfn.XLOOKUP(C176,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>闪电之捷</v>
       </c>
       <c r="F176">
@@ -20436,8 +20436,8 @@
         <f t="shared" si="21"/>
         <v>14</v>
       </c>
-      <c r="E177" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C177,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E177" s="14" t="str" cm="1">
+        <f t="array" ref="E177">_xlfn.XLOOKUP(C177,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>闪电之捷</v>
       </c>
       <c r="F177">
@@ -20470,8 +20470,8 @@
         <f t="shared" si="21"/>
         <v>15</v>
       </c>
-      <c r="E178" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C178,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E178" s="14" t="str" cm="1">
+        <f t="array" ref="E178">_xlfn.XLOOKUP(C178,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>闪电之捷</v>
       </c>
       <c r="F178">
@@ -20504,8 +20504,8 @@
         <f t="shared" si="21"/>
         <v>16</v>
       </c>
-      <c r="E179" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C179,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E179" s="14" t="str" cm="1">
+        <f t="array" ref="E179">_xlfn.XLOOKUP(C179,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>闪电之捷</v>
       </c>
       <c r="F179">
@@ -20538,8 +20538,8 @@
         <f>D164</f>
         <v>1</v>
       </c>
-      <c r="E180" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C180,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E180" s="14" t="str" cm="1">
+        <f t="array" ref="E180">_xlfn.XLOOKUP(C180,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>拔刀斩</v>
       </c>
       <c r="F180">
@@ -20571,8 +20571,8 @@
       <c r="D181" s="14">
         <v>2</v>
       </c>
-      <c r="E181" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C181,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E181" s="14" t="str" cm="1">
+        <f t="array" ref="E181">_xlfn.XLOOKUP(C181,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>拔刀斩</v>
       </c>
       <c r="F181">
@@ -20605,8 +20605,8 @@
         <f>D166</f>
         <v>3</v>
       </c>
-      <c r="E182" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C182,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E182" s="14" t="str" cm="1">
+        <f t="array" ref="E182">_xlfn.XLOOKUP(C182,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>拔刀斩</v>
       </c>
       <c r="F182">
@@ -20638,8 +20638,8 @@
       <c r="D183" s="14">
         <v>4</v>
       </c>
-      <c r="E183" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C183,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E183" s="14" t="str" cm="1">
+        <f t="array" ref="E183">_xlfn.XLOOKUP(C183,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>拔刀斩</v>
       </c>
       <c r="F183">
@@ -20672,8 +20672,8 @@
         <f t="shared" ref="D184:D192" si="24">D168</f>
         <v>5</v>
       </c>
-      <c r="E184" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C184,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E184" s="14" t="str" cm="1">
+        <f t="array" ref="E184">_xlfn.XLOOKUP(C184,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>拔刀斩</v>
       </c>
       <c r="F184">
@@ -20706,8 +20706,8 @@
         <f t="shared" si="24"/>
         <v>6</v>
       </c>
-      <c r="E185" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C185,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E185" s="14" t="str" cm="1">
+        <f t="array" ref="E185">_xlfn.XLOOKUP(C185,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>拔刀斩</v>
       </c>
       <c r="F185">
@@ -20740,8 +20740,8 @@
         <f t="shared" si="24"/>
         <v>7</v>
       </c>
-      <c r="E186" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C186,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E186" s="14" t="str" cm="1">
+        <f t="array" ref="E186">_xlfn.XLOOKUP(C186,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>拔刀斩</v>
       </c>
       <c r="F186">
@@ -20774,8 +20774,8 @@
         <f t="shared" si="24"/>
         <v>8</v>
       </c>
-      <c r="E187" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C187,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E187" s="14" t="str" cm="1">
+        <f t="array" ref="E187">_xlfn.XLOOKUP(C187,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>拔刀斩</v>
       </c>
       <c r="F187">
@@ -20808,8 +20808,8 @@
         <f t="shared" si="24"/>
         <v>9</v>
       </c>
-      <c r="E188" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C188,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E188" s="14" t="str" cm="1">
+        <f t="array" ref="E188">_xlfn.XLOOKUP(C188,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>拔刀斩</v>
       </c>
       <c r="F188">
@@ -20842,8 +20842,8 @@
         <f t="shared" si="24"/>
         <v>10</v>
       </c>
-      <c r="E189" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C189,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E189" s="14" t="str" cm="1">
+        <f t="array" ref="E189">_xlfn.XLOOKUP(C189,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>拔刀斩</v>
       </c>
       <c r="F189">
@@ -20876,8 +20876,8 @@
         <f t="shared" si="24"/>
         <v>11</v>
       </c>
-      <c r="E190" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C190,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E190" s="14" t="str" cm="1">
+        <f t="array" ref="E190">_xlfn.XLOOKUP(C190,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>拔刀斩</v>
       </c>
       <c r="F190">
@@ -20910,8 +20910,8 @@
         <f t="shared" si="24"/>
         <v>12</v>
       </c>
-      <c r="E191" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C191,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E191" s="14" t="str" cm="1">
+        <f t="array" ref="E191">_xlfn.XLOOKUP(C191,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>拔刀斩</v>
       </c>
       <c r="F191">
@@ -20944,8 +20944,8 @@
         <f t="shared" si="24"/>
         <v>13</v>
       </c>
-      <c r="E192" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C192,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E192" s="14" t="str" cm="1">
+        <f t="array" ref="E192">_xlfn.XLOOKUP(C192,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>拔刀斩</v>
       </c>
       <c r="F192">
@@ -20978,8 +20978,8 @@
         <f t="shared" ref="D193:D208" si="26">D177</f>
         <v>14</v>
       </c>
-      <c r="E193" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C193,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E193" s="14" t="str" cm="1">
+        <f t="array" ref="E193">_xlfn.XLOOKUP(C193,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>拔刀斩</v>
       </c>
       <c r="F193">
@@ -21012,8 +21012,8 @@
         <f t="shared" si="26"/>
         <v>15</v>
       </c>
-      <c r="E194" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C194,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E194" s="14" t="str" cm="1">
+        <f t="array" ref="E194">_xlfn.XLOOKUP(C194,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>拔刀斩</v>
       </c>
       <c r="F194">
@@ -21046,8 +21046,8 @@
         <f t="shared" si="26"/>
         <v>16</v>
       </c>
-      <c r="E195" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C195,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E195" s="14" t="str" cm="1">
+        <f t="array" ref="E195">_xlfn.XLOOKUP(C195,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>拔刀斩</v>
       </c>
       <c r="F195">
@@ -21080,8 +21080,8 @@
         <f t="shared" si="26"/>
         <v>1</v>
       </c>
-      <c r="E196" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C196,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E196" s="14" t="str" cm="1">
+        <f t="array" ref="E196">_xlfn.XLOOKUP(C196,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>气刃纵斩</v>
       </c>
       <c r="F196">
@@ -21114,8 +21114,8 @@
         <f t="shared" si="26"/>
         <v>2</v>
       </c>
-      <c r="E197" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C197,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E197" s="14" t="str" cm="1">
+        <f t="array" ref="E197">_xlfn.XLOOKUP(C197,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>气刃纵斩</v>
       </c>
       <c r="F197">
@@ -21148,8 +21148,8 @@
         <f t="shared" si="26"/>
         <v>3</v>
       </c>
-      <c r="E198" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C198,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E198" s="14" t="str" cm="1">
+        <f t="array" ref="E198">_xlfn.XLOOKUP(C198,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>气刃纵斩</v>
       </c>
       <c r="F198">
@@ -21182,8 +21182,8 @@
         <f t="shared" si="26"/>
         <v>4</v>
       </c>
-      <c r="E199" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C199,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E199" s="14" t="str" cm="1">
+        <f t="array" ref="E199">_xlfn.XLOOKUP(C199,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>气刃纵斩</v>
       </c>
       <c r="F199">
@@ -21216,8 +21216,8 @@
         <f t="shared" si="26"/>
         <v>5</v>
       </c>
-      <c r="E200" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C200,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E200" s="14" t="str" cm="1">
+        <f t="array" ref="E200">_xlfn.XLOOKUP(C200,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>气刃纵斩</v>
       </c>
       <c r="F200">
@@ -21250,8 +21250,8 @@
         <f t="shared" si="26"/>
         <v>6</v>
       </c>
-      <c r="E201" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C201,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E201" s="14" t="str" cm="1">
+        <f t="array" ref="E201">_xlfn.XLOOKUP(C201,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>气刃纵斩</v>
       </c>
       <c r="F201">
@@ -21284,8 +21284,8 @@
         <f t="shared" si="26"/>
         <v>7</v>
       </c>
-      <c r="E202" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C202,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E202" s="14" t="str" cm="1">
+        <f t="array" ref="E202">_xlfn.XLOOKUP(C202,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>气刃纵斩</v>
       </c>
       <c r="F202">
@@ -21318,8 +21318,8 @@
         <f t="shared" si="26"/>
         <v>8</v>
       </c>
-      <c r="E203" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C203,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E203" s="14" t="str" cm="1">
+        <f t="array" ref="E203">_xlfn.XLOOKUP(C203,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>气刃纵斩</v>
       </c>
       <c r="F203">
@@ -21352,8 +21352,8 @@
         <f t="shared" si="26"/>
         <v>9</v>
       </c>
-      <c r="E204" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C204,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E204" s="14" t="str" cm="1">
+        <f t="array" ref="E204">_xlfn.XLOOKUP(C204,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>气刃纵斩</v>
       </c>
       <c r="F204">
@@ -21386,8 +21386,8 @@
         <f t="shared" si="26"/>
         <v>10</v>
       </c>
-      <c r="E205" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C205,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E205" s="14" t="str" cm="1">
+        <f t="array" ref="E205">_xlfn.XLOOKUP(C205,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>气刃纵斩</v>
       </c>
       <c r="F205">
@@ -21420,8 +21420,8 @@
         <f t="shared" si="26"/>
         <v>11</v>
       </c>
-      <c r="E206" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C206,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E206" s="14" t="str" cm="1">
+        <f t="array" ref="E206">_xlfn.XLOOKUP(C206,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>气刃纵斩</v>
       </c>
       <c r="F206">
@@ -21454,8 +21454,8 @@
         <f t="shared" si="26"/>
         <v>12</v>
       </c>
-      <c r="E207" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C207,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E207" s="14" t="str" cm="1">
+        <f t="array" ref="E207">_xlfn.XLOOKUP(C207,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>气刃纵斩</v>
       </c>
       <c r="F207">
@@ -21488,8 +21488,8 @@
         <f t="shared" si="26"/>
         <v>13</v>
       </c>
-      <c r="E208" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C208,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E208" s="14" t="str" cm="1">
+        <f t="array" ref="E208">_xlfn.XLOOKUP(C208,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>气刃纵斩</v>
       </c>
       <c r="F208">
@@ -21522,8 +21522,8 @@
         <f t="shared" ref="D209:D215" si="30">D193</f>
         <v>14</v>
       </c>
-      <c r="E209" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C209,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E209" s="14" t="str" cm="1">
+        <f t="array" ref="E209">_xlfn.XLOOKUP(C209,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>气刃纵斩</v>
       </c>
       <c r="F209">
@@ -21556,8 +21556,8 @@
         <f t="shared" si="30"/>
         <v>15</v>
       </c>
-      <c r="E210" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C210,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E210" s="14" t="str" cm="1">
+        <f t="array" ref="E210">_xlfn.XLOOKUP(C210,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>气刃纵斩</v>
       </c>
       <c r="F210">
@@ -21590,8 +21590,8 @@
         <f t="shared" si="30"/>
         <v>16</v>
       </c>
-      <c r="E211" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C211,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E211" s="14" t="str" cm="1">
+        <f t="array" ref="E211">_xlfn.XLOOKUP(C211,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>气刃纵斩</v>
       </c>
       <c r="F211">
@@ -21624,8 +21624,8 @@
         <f t="shared" si="30"/>
         <v>1</v>
       </c>
-      <c r="E212" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C212,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E212" s="14" t="str" cm="1">
+        <f t="array" ref="E212">_xlfn.XLOOKUP(C212,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>回旋龙卷</v>
       </c>
       <c r="F212">
@@ -21658,8 +21658,8 @@
         <f t="shared" si="30"/>
         <v>2</v>
       </c>
-      <c r="E213" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C213,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E213" s="14" t="str" cm="1">
+        <f t="array" ref="E213">_xlfn.XLOOKUP(C213,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>回旋龙卷</v>
       </c>
       <c r="F213">
@@ -21692,8 +21692,8 @@
         <f t="shared" si="30"/>
         <v>3</v>
       </c>
-      <c r="E214" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C214,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E214" s="14" t="str" cm="1">
+        <f t="array" ref="E214">_xlfn.XLOOKUP(C214,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>回旋龙卷</v>
       </c>
       <c r="F214">
@@ -21726,8 +21726,8 @@
         <f t="shared" si="30"/>
         <v>4</v>
       </c>
-      <c r="E215" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C215,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E215" s="14" t="str" cm="1">
+        <f t="array" ref="E215">_xlfn.XLOOKUP(C215,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>回旋龙卷</v>
       </c>
       <c r="F215">
@@ -21760,8 +21760,8 @@
         <f t="shared" ref="D216:D243" si="33">D200</f>
         <v>5</v>
       </c>
-      <c r="E216" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C216,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E216" s="14" t="str" cm="1">
+        <f t="array" ref="E216">_xlfn.XLOOKUP(C216,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>回旋龙卷</v>
       </c>
       <c r="F216">
@@ -21794,8 +21794,8 @@
         <f t="shared" si="33"/>
         <v>6</v>
       </c>
-      <c r="E217" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C217,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E217" s="14" t="str" cm="1">
+        <f t="array" ref="E217">_xlfn.XLOOKUP(C217,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>回旋龙卷</v>
       </c>
       <c r="F217">
@@ -21828,8 +21828,8 @@
         <f t="shared" si="33"/>
         <v>7</v>
       </c>
-      <c r="E218" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C218,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E218" s="14" t="str" cm="1">
+        <f t="array" ref="E218">_xlfn.XLOOKUP(C218,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>回旋龙卷</v>
       </c>
       <c r="F218">
@@ -21862,8 +21862,8 @@
         <f t="shared" si="33"/>
         <v>8</v>
       </c>
-      <c r="E219" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C219,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E219" s="14" t="str" cm="1">
+        <f t="array" ref="E219">_xlfn.XLOOKUP(C219,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>回旋龙卷</v>
       </c>
       <c r="F219">
@@ -21896,8 +21896,8 @@
         <f t="shared" si="33"/>
         <v>9</v>
       </c>
-      <c r="E220" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C220,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E220" s="14" t="str" cm="1">
+        <f t="array" ref="E220">_xlfn.XLOOKUP(C220,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>回旋龙卷</v>
       </c>
       <c r="F220">
@@ -21930,8 +21930,8 @@
         <f t="shared" si="33"/>
         <v>10</v>
       </c>
-      <c r="E221" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C221,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E221" s="14" t="str" cm="1">
+        <f t="array" ref="E221">_xlfn.XLOOKUP(C221,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>回旋龙卷</v>
       </c>
       <c r="F221">
@@ -21964,8 +21964,8 @@
         <f t="shared" si="33"/>
         <v>11</v>
       </c>
-      <c r="E222" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C222,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E222" s="14" t="str" cm="1">
+        <f t="array" ref="E222">_xlfn.XLOOKUP(C222,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>回旋龙卷</v>
       </c>
       <c r="F222">
@@ -21998,8 +21998,8 @@
         <f t="shared" si="33"/>
         <v>12</v>
       </c>
-      <c r="E223" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C223,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E223" s="14" t="str" cm="1">
+        <f t="array" ref="E223">_xlfn.XLOOKUP(C223,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>回旋龙卷</v>
       </c>
       <c r="F223">
@@ -22032,8 +22032,8 @@
         <f t="shared" si="33"/>
         <v>13</v>
       </c>
-      <c r="E224" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C224,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E224" s="14" t="str" cm="1">
+        <f t="array" ref="E224">_xlfn.XLOOKUP(C224,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>回旋龙卷</v>
       </c>
       <c r="F224">
@@ -22066,8 +22066,8 @@
         <f t="shared" si="33"/>
         <v>14</v>
       </c>
-      <c r="E225" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C225,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E225" s="14" t="str" cm="1">
+        <f t="array" ref="E225">_xlfn.XLOOKUP(C225,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>回旋龙卷</v>
       </c>
       <c r="F225">
@@ -22100,8 +22100,8 @@
         <f t="shared" si="33"/>
         <v>15</v>
       </c>
-      <c r="E226" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C226,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E226" s="14" t="str" cm="1">
+        <f t="array" ref="E226">_xlfn.XLOOKUP(C226,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>回旋龙卷</v>
       </c>
       <c r="F226">
@@ -22134,8 +22134,8 @@
         <f t="shared" si="33"/>
         <v>16</v>
       </c>
-      <c r="E227" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C227,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E227" s="14" t="str" cm="1">
+        <f t="array" ref="E227">_xlfn.XLOOKUP(C227,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>回旋龙卷</v>
       </c>
       <c r="F227">
@@ -22168,8 +22168,8 @@
         <f t="shared" si="33"/>
         <v>1</v>
       </c>
-      <c r="E228" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C228,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E228" s="14" t="str" cm="1">
+        <f t="array" ref="E228">_xlfn.XLOOKUP(C228,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>魔力满溢</v>
       </c>
       <c r="F228">
@@ -22202,8 +22202,8 @@
         <f t="shared" si="33"/>
         <v>2</v>
       </c>
-      <c r="E229" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C229,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E229" s="14" t="str" cm="1">
+        <f t="array" ref="E229">_xlfn.XLOOKUP(C229,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>魔力满溢</v>
       </c>
       <c r="F229">
@@ -22236,8 +22236,8 @@
         <f t="shared" si="33"/>
         <v>3</v>
       </c>
-      <c r="E230" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C230,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E230" s="14" t="str" cm="1">
+        <f t="array" ref="E230">_xlfn.XLOOKUP(C230,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>魔力满溢</v>
       </c>
       <c r="F230">
@@ -22270,8 +22270,8 @@
         <f t="shared" si="33"/>
         <v>4</v>
       </c>
-      <c r="E231" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C231,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E231" s="14" t="str" cm="1">
+        <f t="array" ref="E231">_xlfn.XLOOKUP(C231,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>魔力满溢</v>
       </c>
       <c r="F231">
@@ -22304,8 +22304,8 @@
         <f t="shared" si="33"/>
         <v>5</v>
       </c>
-      <c r="E232" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C232,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E232" s="14" t="str" cm="1">
+        <f t="array" ref="E232">_xlfn.XLOOKUP(C232,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>魔力满溢</v>
       </c>
       <c r="F232">
@@ -22338,8 +22338,8 @@
         <f t="shared" si="33"/>
         <v>6</v>
       </c>
-      <c r="E233" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C233,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E233" s="14" t="str" cm="1">
+        <f t="array" ref="E233">_xlfn.XLOOKUP(C233,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>魔力满溢</v>
       </c>
       <c r="F233">
@@ -22372,8 +22372,8 @@
         <f t="shared" si="33"/>
         <v>7</v>
       </c>
-      <c r="E234" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C234,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E234" s="14" t="str" cm="1">
+        <f t="array" ref="E234">_xlfn.XLOOKUP(C234,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>魔力满溢</v>
       </c>
       <c r="F234">
@@ -22406,8 +22406,8 @@
         <f t="shared" si="33"/>
         <v>8</v>
       </c>
-      <c r="E235" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C235,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E235" s="14" t="str" cm="1">
+        <f t="array" ref="E235">_xlfn.XLOOKUP(C235,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>魔力满溢</v>
       </c>
       <c r="F235">
@@ -22440,8 +22440,8 @@
         <f t="shared" si="33"/>
         <v>9</v>
       </c>
-      <c r="E236" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C236,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E236" s="14" t="str" cm="1">
+        <f t="array" ref="E236">_xlfn.XLOOKUP(C236,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>魔力满溢</v>
       </c>
       <c r="F236">
@@ -22474,8 +22474,8 @@
         <f t="shared" si="33"/>
         <v>10</v>
       </c>
-      <c r="E237" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C237,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E237" s="14" t="str" cm="1">
+        <f t="array" ref="E237">_xlfn.XLOOKUP(C237,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>魔力满溢</v>
       </c>
       <c r="F237">
@@ -22508,8 +22508,8 @@
         <f t="shared" si="33"/>
         <v>11</v>
       </c>
-      <c r="E238" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C238,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E238" s="14" t="str" cm="1">
+        <f t="array" ref="E238">_xlfn.XLOOKUP(C238,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>魔力满溢</v>
       </c>
       <c r="F238">
@@ -22542,8 +22542,8 @@
         <f t="shared" si="33"/>
         <v>12</v>
       </c>
-      <c r="E239" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C239,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E239" s="14" t="str" cm="1">
+        <f t="array" ref="E239">_xlfn.XLOOKUP(C239,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>魔力满溢</v>
       </c>
       <c r="F239">
@@ -22576,8 +22576,8 @@
         <f t="shared" si="33"/>
         <v>13</v>
       </c>
-      <c r="E240" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C240,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E240" s="14" t="str" cm="1">
+        <f t="array" ref="E240">_xlfn.XLOOKUP(C240,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>魔力满溢</v>
       </c>
       <c r="F240">
@@ -22610,8 +22610,8 @@
         <f t="shared" si="33"/>
         <v>14</v>
       </c>
-      <c r="E241" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C241,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E241" s="14" t="str" cm="1">
+        <f t="array" ref="E241">_xlfn.XLOOKUP(C241,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>魔力满溢</v>
       </c>
       <c r="F241">
@@ -22644,8 +22644,8 @@
         <f t="shared" si="33"/>
         <v>15</v>
       </c>
-      <c r="E242" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C242,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E242" s="14" t="str" cm="1">
+        <f t="array" ref="E242">_xlfn.XLOOKUP(C242,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>魔力满溢</v>
       </c>
       <c r="F242">
@@ -22678,8 +22678,8 @@
         <f t="shared" si="33"/>
         <v>16</v>
       </c>
-      <c r="E243" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C243,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E243" s="14" t="str" cm="1">
+        <f t="array" ref="E243">_xlfn.XLOOKUP(C243,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>魔力满溢</v>
       </c>
       <c r="F243">
@@ -22711,8 +22711,8 @@
       <c r="D244" s="14">
         <v>1</v>
       </c>
-      <c r="E244" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C244,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E244" s="14" t="str" cm="1">
+        <f t="array" ref="E244">_xlfn.XLOOKUP(C244,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>灰烬之捷</v>
       </c>
       <c r="F244">
@@ -22744,8 +22744,8 @@
       <c r="D245" s="14">
         <v>2</v>
       </c>
-      <c r="E245" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C245,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E245" s="14" t="str" cm="1">
+        <f t="array" ref="E245">_xlfn.XLOOKUP(C245,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>灰烬之捷</v>
       </c>
       <c r="F245">
@@ -22777,8 +22777,8 @@
       <c r="D246" s="14">
         <v>3</v>
       </c>
-      <c r="E246" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C246,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E246" s="14" t="str" cm="1">
+        <f t="array" ref="E246">_xlfn.XLOOKUP(C246,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>灰烬之捷</v>
       </c>
       <c r="F246">
@@ -22810,8 +22810,8 @@
       <c r="D247" s="14">
         <v>4</v>
       </c>
-      <c r="E247" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C247,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E247" s="14" t="str" cm="1">
+        <f t="array" ref="E247">_xlfn.XLOOKUP(C247,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>灰烬之捷</v>
       </c>
       <c r="F247">
@@ -22843,8 +22843,8 @@
       <c r="D248" s="14">
         <v>5</v>
       </c>
-      <c r="E248" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C248,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E248" s="14" t="str" cm="1">
+        <f t="array" ref="E248">_xlfn.XLOOKUP(C248,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>灰烬之捷</v>
       </c>
       <c r="F248">
@@ -22876,8 +22876,8 @@
       <c r="D249" s="14">
         <v>6</v>
       </c>
-      <c r="E249" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C249,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E249" s="14" t="str" cm="1">
+        <f t="array" ref="E249">_xlfn.XLOOKUP(C249,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>灰烬之捷</v>
       </c>
       <c r="F249">
@@ -22909,8 +22909,8 @@
       <c r="D250" s="14">
         <v>7</v>
       </c>
-      <c r="E250" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C250,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E250" s="14" t="str" cm="1">
+        <f t="array" ref="E250">_xlfn.XLOOKUP(C250,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>灰烬之捷</v>
       </c>
       <c r="F250">
@@ -22942,8 +22942,8 @@
       <c r="D251" s="14">
         <v>8</v>
       </c>
-      <c r="E251" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C251,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E251" s="14" t="str" cm="1">
+        <f t="array" ref="E251">_xlfn.XLOOKUP(C251,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>灰烬之捷</v>
       </c>
       <c r="F251">
@@ -22976,8 +22976,8 @@
         <f t="shared" ref="D252:D259" si="42">D172</f>
         <v>9</v>
       </c>
-      <c r="E252" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C252,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E252" s="14" t="str" cm="1">
+        <f t="array" ref="E252">_xlfn.XLOOKUP(C252,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>灰烬之捷</v>
       </c>
       <c r="F252">
@@ -23010,8 +23010,8 @@
         <f t="shared" si="42"/>
         <v>10</v>
       </c>
-      <c r="E253" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C253,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E253" s="14" t="str" cm="1">
+        <f t="array" ref="E253">_xlfn.XLOOKUP(C253,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>灰烬之捷</v>
       </c>
       <c r="F253">
@@ -23044,8 +23044,8 @@
         <f t="shared" si="42"/>
         <v>11</v>
       </c>
-      <c r="E254" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C254,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E254" s="14" t="str" cm="1">
+        <f t="array" ref="E254">_xlfn.XLOOKUP(C254,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>灰烬之捷</v>
       </c>
       <c r="F254">
@@ -23078,8 +23078,8 @@
         <f t="shared" si="42"/>
         <v>12</v>
       </c>
-      <c r="E255" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C255,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E255" s="14" t="str" cm="1">
+        <f t="array" ref="E255">_xlfn.XLOOKUP(C255,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>灰烬之捷</v>
       </c>
       <c r="F255">
@@ -23112,8 +23112,8 @@
         <f t="shared" si="42"/>
         <v>13</v>
       </c>
-      <c r="E256" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C256,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E256" s="14" t="str" cm="1">
+        <f t="array" ref="E256">_xlfn.XLOOKUP(C256,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>灰烬之捷</v>
       </c>
       <c r="F256">
@@ -23146,8 +23146,8 @@
         <f t="shared" si="42"/>
         <v>14</v>
       </c>
-      <c r="E257" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C257,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E257" s="14" t="str" cm="1">
+        <f t="array" ref="E257">_xlfn.XLOOKUP(C257,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>灰烬之捷</v>
       </c>
       <c r="F257">
@@ -23180,8 +23180,8 @@
         <f t="shared" si="42"/>
         <v>15</v>
       </c>
-      <c r="E258" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C258,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E258" s="14" t="str" cm="1">
+        <f t="array" ref="E258">_xlfn.XLOOKUP(C258,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>灰烬之捷</v>
       </c>
       <c r="F258">
@@ -23214,8 +23214,8 @@
         <f t="shared" si="42"/>
         <v>16</v>
       </c>
-      <c r="E259" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C259,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E259" s="14" t="str" cm="1">
+        <f t="array" ref="E259">_xlfn.XLOOKUP(C259,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>灰烬之捷</v>
       </c>
       <c r="F259">
@@ -23248,8 +23248,8 @@
         <f t="shared" ref="D260:D267" si="44">D244</f>
         <v>1</v>
       </c>
-      <c r="E260" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C260,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E260" s="14" t="str" cm="1">
+        <f t="array" ref="E260">_xlfn.XLOOKUP(C260,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>月神赐福</v>
       </c>
       <c r="F260">
@@ -23282,8 +23282,8 @@
         <f t="shared" si="44"/>
         <v>2</v>
       </c>
-      <c r="E261" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C261,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E261" s="14" t="str" cm="1">
+        <f t="array" ref="E261">_xlfn.XLOOKUP(C261,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>月神赐福</v>
       </c>
       <c r="F261">
@@ -23316,8 +23316,8 @@
         <f t="shared" si="44"/>
         <v>3</v>
       </c>
-      <c r="E262" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C262,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E262" s="14" t="str" cm="1">
+        <f t="array" ref="E262">_xlfn.XLOOKUP(C262,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>月神赐福</v>
       </c>
       <c r="F262">
@@ -23350,8 +23350,8 @@
         <f t="shared" si="44"/>
         <v>4</v>
       </c>
-      <c r="E263" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C263,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E263" s="14" t="str" cm="1">
+        <f t="array" ref="E263">_xlfn.XLOOKUP(C263,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>月神赐福</v>
       </c>
       <c r="F263">
@@ -23384,8 +23384,8 @@
         <f t="shared" si="44"/>
         <v>5</v>
       </c>
-      <c r="E264" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C264,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E264" s="14" t="str" cm="1">
+        <f t="array" ref="E264">_xlfn.XLOOKUP(C264,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>月神赐福</v>
       </c>
       <c r="F264">
@@ -23418,8 +23418,8 @@
         <f t="shared" si="44"/>
         <v>6</v>
       </c>
-      <c r="E265" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C265,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E265" s="14" t="str" cm="1">
+        <f t="array" ref="E265">_xlfn.XLOOKUP(C265,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>月神赐福</v>
       </c>
       <c r="F265">
@@ -23452,8 +23452,8 @@
         <f t="shared" si="44"/>
         <v>7</v>
       </c>
-      <c r="E266" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C266,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E266" s="14" t="str" cm="1">
+        <f t="array" ref="E266">_xlfn.XLOOKUP(C266,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>月神赐福</v>
       </c>
       <c r="F266">
@@ -23486,8 +23486,8 @@
         <f t="shared" si="44"/>
         <v>8</v>
       </c>
-      <c r="E267" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C267,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E267" s="14" t="str" cm="1">
+        <f t="array" ref="E267">_xlfn.XLOOKUP(C267,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>月神赐福</v>
       </c>
       <c r="F267">
@@ -23520,8 +23520,8 @@
         <f t="shared" ref="D268:D291" si="45">D252</f>
         <v>9</v>
       </c>
-      <c r="E268" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C268,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E268" s="14" t="str" cm="1">
+        <f t="array" ref="E268">_xlfn.XLOOKUP(C268,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>月神赐福</v>
       </c>
       <c r="F268">
@@ -23554,8 +23554,8 @@
         <f t="shared" si="45"/>
         <v>10</v>
       </c>
-      <c r="E269" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C269,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E269" s="14" t="str" cm="1">
+        <f t="array" ref="E269">_xlfn.XLOOKUP(C269,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>月神赐福</v>
       </c>
       <c r="F269">
@@ -23588,8 +23588,8 @@
         <f t="shared" si="45"/>
         <v>11</v>
       </c>
-      <c r="E270" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C270,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E270" s="14" t="str" cm="1">
+        <f t="array" ref="E270">_xlfn.XLOOKUP(C270,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>月神赐福</v>
       </c>
       <c r="F270">
@@ -23622,8 +23622,8 @@
         <f t="shared" si="45"/>
         <v>12</v>
       </c>
-      <c r="E271" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C271,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E271" s="14" t="str" cm="1">
+        <f t="array" ref="E271">_xlfn.XLOOKUP(C271,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>月神赐福</v>
       </c>
       <c r="F271">
@@ -23656,8 +23656,8 @@
         <f t="shared" si="45"/>
         <v>13</v>
       </c>
-      <c r="E272" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C272,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E272" s="14" t="str" cm="1">
+        <f t="array" ref="E272">_xlfn.XLOOKUP(C272,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>月神赐福</v>
       </c>
       <c r="F272">
@@ -23690,8 +23690,8 @@
         <f t="shared" si="45"/>
         <v>14</v>
       </c>
-      <c r="E273" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C273,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E273" s="14" t="str" cm="1">
+        <f t="array" ref="E273">_xlfn.XLOOKUP(C273,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>月神赐福</v>
       </c>
       <c r="F273">
@@ -23724,8 +23724,8 @@
         <f t="shared" si="45"/>
         <v>15</v>
       </c>
-      <c r="E274" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C274,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E274" s="14" t="str" cm="1">
+        <f t="array" ref="E274">_xlfn.XLOOKUP(C274,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>月神赐福</v>
       </c>
       <c r="F274">
@@ -23758,8 +23758,8 @@
         <f t="shared" si="45"/>
         <v>16</v>
       </c>
-      <c r="E275" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C275,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E275" s="14" t="str" cm="1">
+        <f t="array" ref="E275">_xlfn.XLOOKUP(C275,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>月神赐福</v>
       </c>
       <c r="F275">
@@ -23792,8 +23792,8 @@
         <f t="shared" si="45"/>
         <v>1</v>
       </c>
-      <c r="E276" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C276,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E276" s="14" t="str" cm="1">
+        <f t="array" ref="E276">_xlfn.XLOOKUP(C276,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>回响</v>
       </c>
       <c r="F276">
@@ -23826,8 +23826,8 @@
         <f t="shared" si="45"/>
         <v>2</v>
       </c>
-      <c r="E277" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C277,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E277" s="14" t="str" cm="1">
+        <f t="array" ref="E277">_xlfn.XLOOKUP(C277,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>回响</v>
       </c>
       <c r="F277">
@@ -23860,8 +23860,8 @@
         <f t="shared" si="45"/>
         <v>3</v>
       </c>
-      <c r="E278" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C278,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E278" s="14" t="str" cm="1">
+        <f t="array" ref="E278">_xlfn.XLOOKUP(C278,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>回响</v>
       </c>
       <c r="F278">
@@ -23894,8 +23894,8 @@
         <f t="shared" si="45"/>
         <v>4</v>
       </c>
-      <c r="E279" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C279,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E279" s="14" t="str" cm="1">
+        <f t="array" ref="E279">_xlfn.XLOOKUP(C279,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>回响</v>
       </c>
       <c r="F279">
@@ -23928,8 +23928,8 @@
         <f t="shared" si="45"/>
         <v>5</v>
       </c>
-      <c r="E280" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C280,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E280" s="14" t="str" cm="1">
+        <f t="array" ref="E280">_xlfn.XLOOKUP(C280,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>回响</v>
       </c>
       <c r="F280">
@@ -23962,8 +23962,8 @@
         <f t="shared" si="45"/>
         <v>6</v>
       </c>
-      <c r="E281" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C281,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E281" s="14" t="str" cm="1">
+        <f t="array" ref="E281">_xlfn.XLOOKUP(C281,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>回响</v>
       </c>
       <c r="F281">
@@ -23996,8 +23996,8 @@
         <f t="shared" si="45"/>
         <v>7</v>
       </c>
-      <c r="E282" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C282,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E282" s="14" t="str" cm="1">
+        <f t="array" ref="E282">_xlfn.XLOOKUP(C282,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>回响</v>
       </c>
       <c r="F282">
@@ -24030,8 +24030,8 @@
         <f t="shared" si="45"/>
         <v>8</v>
       </c>
-      <c r="E283" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C283,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E283" s="14" t="str" cm="1">
+        <f t="array" ref="E283">_xlfn.XLOOKUP(C283,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>回响</v>
       </c>
       <c r="F283">
@@ -24064,8 +24064,8 @@
         <f t="shared" si="45"/>
         <v>9</v>
       </c>
-      <c r="E284" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C284,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E284" s="14" t="str" cm="1">
+        <f t="array" ref="E284">_xlfn.XLOOKUP(C284,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>回响</v>
       </c>
       <c r="F284">
@@ -24098,8 +24098,8 @@
         <f t="shared" si="45"/>
         <v>10</v>
       </c>
-      <c r="E285" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C285,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E285" s="14" t="str" cm="1">
+        <f t="array" ref="E285">_xlfn.XLOOKUP(C285,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>回响</v>
       </c>
       <c r="F285">
@@ -24132,8 +24132,8 @@
         <f t="shared" si="45"/>
         <v>11</v>
       </c>
-      <c r="E286" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C286,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E286" s="14" t="str" cm="1">
+        <f t="array" ref="E286">_xlfn.XLOOKUP(C286,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>回响</v>
       </c>
       <c r="F286">
@@ -24166,8 +24166,8 @@
         <f t="shared" si="45"/>
         <v>12</v>
       </c>
-      <c r="E287" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C287,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E287" s="14" t="str" cm="1">
+        <f t="array" ref="E287">_xlfn.XLOOKUP(C287,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>回响</v>
       </c>
       <c r="F287">
@@ -24200,8 +24200,8 @@
         <f t="shared" si="45"/>
         <v>13</v>
       </c>
-      <c r="E288" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C288,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E288" s="14" t="str" cm="1">
+        <f t="array" ref="E288">_xlfn.XLOOKUP(C288,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>回响</v>
       </c>
       <c r="F288">
@@ -24234,8 +24234,8 @@
         <f t="shared" si="45"/>
         <v>14</v>
       </c>
-      <c r="E289" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C289,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E289" s="14" t="str" cm="1">
+        <f t="array" ref="E289">_xlfn.XLOOKUP(C289,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>回响</v>
       </c>
       <c r="F289">
@@ -24268,8 +24268,8 @@
         <f t="shared" si="45"/>
         <v>15</v>
       </c>
-      <c r="E290" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C290,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E290" s="14" t="str" cm="1">
+        <f t="array" ref="E290">_xlfn.XLOOKUP(C290,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>回响</v>
       </c>
       <c r="F290">
@@ -24302,8 +24302,8 @@
         <f t="shared" si="45"/>
         <v>16</v>
       </c>
-      <c r="E291" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C291,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E291" s="14" t="str" cm="1">
+        <f t="array" ref="E291">_xlfn.XLOOKUP(C291,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>回响</v>
       </c>
       <c r="F291">
@@ -24336,8 +24336,8 @@
         <f t="shared" ref="D292:D299" si="50">D260</f>
         <v>1</v>
       </c>
-      <c r="E292" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C292,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E292" s="14" t="str" cm="1">
+        <f t="array" ref="E292">_xlfn.XLOOKUP(C292,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>极地战吼</v>
       </c>
       <c r="F292">
@@ -24370,8 +24370,8 @@
         <f t="shared" si="50"/>
         <v>2</v>
       </c>
-      <c r="E293" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C293,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E293" s="14" t="str" cm="1">
+        <f t="array" ref="E293">_xlfn.XLOOKUP(C293,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>极地战吼</v>
       </c>
       <c r="F293">
@@ -24404,8 +24404,8 @@
         <f t="shared" si="50"/>
         <v>3</v>
       </c>
-      <c r="E294" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C294,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E294" s="14" t="str" cm="1">
+        <f t="array" ref="E294">_xlfn.XLOOKUP(C294,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>极地战吼</v>
       </c>
       <c r="F294">
@@ -24438,8 +24438,8 @@
         <f t="shared" si="50"/>
         <v>4</v>
       </c>
-      <c r="E295" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C295,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E295" s="14" t="str" cm="1">
+        <f t="array" ref="E295">_xlfn.XLOOKUP(C295,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>极地战吼</v>
       </c>
       <c r="F295">
@@ -24472,8 +24472,8 @@
         <f t="shared" si="50"/>
         <v>5</v>
       </c>
-      <c r="E296" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C296,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E296" s="14" t="str" cm="1">
+        <f t="array" ref="E296">_xlfn.XLOOKUP(C296,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>极地战吼</v>
       </c>
       <c r="F296">
@@ -24506,8 +24506,8 @@
         <f t="shared" si="50"/>
         <v>6</v>
       </c>
-      <c r="E297" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C297,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E297" s="14" t="str" cm="1">
+        <f t="array" ref="E297">_xlfn.XLOOKUP(C297,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>极地战吼</v>
       </c>
       <c r="F297">
@@ -24540,8 +24540,8 @@
         <f t="shared" si="50"/>
         <v>7</v>
       </c>
-      <c r="E298" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C298,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E298" s="14" t="str" cm="1">
+        <f t="array" ref="E298">_xlfn.XLOOKUP(C298,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>极地战吼</v>
       </c>
       <c r="F298">
@@ -24574,8 +24574,8 @@
         <f t="shared" si="50"/>
         <v>8</v>
       </c>
-      <c r="E299" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C299,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E299" s="14" t="str" cm="1">
+        <f t="array" ref="E299">_xlfn.XLOOKUP(C299,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>极地战吼</v>
       </c>
       <c r="F299">
@@ -24608,8 +24608,8 @@
         <f t="shared" ref="D300:D307" si="51">D268</f>
         <v>9</v>
       </c>
-      <c r="E300" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C300,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E300" s="14" t="str" cm="1">
+        <f t="array" ref="E300">_xlfn.XLOOKUP(C300,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>极地战吼</v>
       </c>
       <c r="F300">
@@ -24642,8 +24642,8 @@
         <f t="shared" si="51"/>
         <v>10</v>
       </c>
-      <c r="E301" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C301,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E301" s="14" t="str" cm="1">
+        <f t="array" ref="E301">_xlfn.XLOOKUP(C301,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>极地战吼</v>
       </c>
       <c r="F301">
@@ -24676,8 +24676,8 @@
         <f t="shared" si="51"/>
         <v>11</v>
       </c>
-      <c r="E302" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C302,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E302" s="14" t="str" cm="1">
+        <f t="array" ref="E302">_xlfn.XLOOKUP(C302,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>极地战吼</v>
       </c>
       <c r="F302">
@@ -24710,8 +24710,8 @@
         <f t="shared" si="51"/>
         <v>12</v>
       </c>
-      <c r="E303" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C303,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E303" s="14" t="str" cm="1">
+        <f t="array" ref="E303">_xlfn.XLOOKUP(C303,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>极地战吼</v>
       </c>
       <c r="F303">
@@ -24744,8 +24744,8 @@
         <f t="shared" si="51"/>
         <v>13</v>
       </c>
-      <c r="E304" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C304,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E304" s="14" t="str" cm="1">
+        <f t="array" ref="E304">_xlfn.XLOOKUP(C304,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>极地战吼</v>
       </c>
       <c r="F304">
@@ -24778,8 +24778,8 @@
         <f t="shared" si="51"/>
         <v>14</v>
       </c>
-      <c r="E305" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C305,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E305" s="14" t="str" cm="1">
+        <f t="array" ref="E305">_xlfn.XLOOKUP(C305,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>极地战吼</v>
       </c>
       <c r="F305">
@@ -24812,8 +24812,8 @@
         <f t="shared" si="51"/>
         <v>15</v>
       </c>
-      <c r="E306" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C306,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E306" s="14" t="str" cm="1">
+        <f t="array" ref="E306">_xlfn.XLOOKUP(C306,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>极地战吼</v>
       </c>
       <c r="F306">
@@ -24846,8 +24846,8 @@
         <f t="shared" si="51"/>
         <v>16</v>
       </c>
-      <c r="E307" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C307,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E307" s="14" t="str" cm="1">
+        <f t="array" ref="E307">_xlfn.XLOOKUP(C307,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>极地战吼</v>
       </c>
       <c r="F307">
@@ -24879,8 +24879,8 @@
       <c r="D308" s="14">
         <v>1</v>
       </c>
-      <c r="E308" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C308,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E308" s="14" t="str" cm="1">
+        <f t="array" ref="E308">_xlfn.XLOOKUP(C308,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>冰霜之捷</v>
       </c>
       <c r="F308">
@@ -24912,8 +24912,8 @@
       <c r="D309" s="14">
         <v>2</v>
       </c>
-      <c r="E309" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C309,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E309" s="14" t="str" cm="1">
+        <f t="array" ref="E309">_xlfn.XLOOKUP(C309,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>冰霜之捷</v>
       </c>
       <c r="F309">
@@ -24945,8 +24945,8 @@
       <c r="D310" s="14">
         <v>3</v>
       </c>
-      <c r="E310" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C310,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E310" s="14" t="str" cm="1">
+        <f t="array" ref="E310">_xlfn.XLOOKUP(C310,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>冰霜之捷</v>
       </c>
       <c r="F310">
@@ -24978,8 +24978,8 @@
       <c r="D311" s="14">
         <v>4</v>
       </c>
-      <c r="E311" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C311,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E311" s="14" t="str" cm="1">
+        <f t="array" ref="E311">_xlfn.XLOOKUP(C311,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>冰霜之捷</v>
       </c>
       <c r="F311">
@@ -25011,8 +25011,8 @@
       <c r="D312" s="14">
         <v>5</v>
       </c>
-      <c r="E312" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C312,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E312" s="14" t="str" cm="1">
+        <f t="array" ref="E312">_xlfn.XLOOKUP(C312,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>冰霜之捷</v>
       </c>
       <c r="F312">
@@ -25044,8 +25044,8 @@
       <c r="D313" s="14">
         <v>6</v>
       </c>
-      <c r="E313" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C313,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E313" s="14" t="str" cm="1">
+        <f t="array" ref="E313">_xlfn.XLOOKUP(C313,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>冰霜之捷</v>
       </c>
       <c r="F313">
@@ -25077,8 +25077,8 @@
       <c r="D314" s="14">
         <v>7</v>
       </c>
-      <c r="E314" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C314,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E314" s="14" t="str" cm="1">
+        <f t="array" ref="E314">_xlfn.XLOOKUP(C314,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>冰霜之捷</v>
       </c>
       <c r="F314">
@@ -25110,8 +25110,8 @@
       <c r="D315" s="14">
         <v>8</v>
       </c>
-      <c r="E315" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C315,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E315" s="14" t="str" cm="1">
+        <f t="array" ref="E315">_xlfn.XLOOKUP(C315,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>冰霜之捷</v>
       </c>
       <c r="F315">
@@ -25144,8 +25144,8 @@
         <f t="shared" ref="D314:D323" si="55">D252</f>
         <v>9</v>
       </c>
-      <c r="E316" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C316,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E316" s="14" t="str" cm="1">
+        <f t="array" ref="E316">_xlfn.XLOOKUP(C316,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>冰霜之捷</v>
       </c>
       <c r="F316">
@@ -25178,8 +25178,8 @@
         <f t="shared" si="55"/>
         <v>10</v>
       </c>
-      <c r="E317" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C317,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E317" s="14" t="str" cm="1">
+        <f t="array" ref="E317">_xlfn.XLOOKUP(C317,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>冰霜之捷</v>
       </c>
       <c r="F317">
@@ -25212,8 +25212,8 @@
         <f t="shared" si="55"/>
         <v>11</v>
       </c>
-      <c r="E318" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C318,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E318" s="14" t="str" cm="1">
+        <f t="array" ref="E318">_xlfn.XLOOKUP(C318,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>冰霜之捷</v>
       </c>
       <c r="F318">
@@ -25246,8 +25246,8 @@
         <f t="shared" si="55"/>
         <v>12</v>
       </c>
-      <c r="E319" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C319,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E319" s="14" t="str" cm="1">
+        <f t="array" ref="E319">_xlfn.XLOOKUP(C319,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>冰霜之捷</v>
       </c>
       <c r="F319">
@@ -25280,8 +25280,8 @@
         <f t="shared" si="55"/>
         <v>13</v>
       </c>
-      <c r="E320" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C320,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E320" s="14" t="str" cm="1">
+        <f t="array" ref="E320">_xlfn.XLOOKUP(C320,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>冰霜之捷</v>
       </c>
       <c r="F320">
@@ -25314,8 +25314,8 @@
         <f t="shared" si="55"/>
         <v>14</v>
       </c>
-      <c r="E321" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C321,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E321" s="14" t="str" cm="1">
+        <f t="array" ref="E321">_xlfn.XLOOKUP(C321,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>冰霜之捷</v>
       </c>
       <c r="F321">
@@ -25348,8 +25348,8 @@
         <f t="shared" si="55"/>
         <v>15</v>
       </c>
-      <c r="E322" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C322,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E322" s="14" t="str" cm="1">
+        <f t="array" ref="E322">_xlfn.XLOOKUP(C322,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>冰霜之捷</v>
       </c>
       <c r="F322">
@@ -25382,8 +25382,8 @@
         <f t="shared" si="55"/>
         <v>16</v>
       </c>
-      <c r="E323" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C323,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E323" s="14" t="str" cm="1">
+        <f t="array" ref="E323">_xlfn.XLOOKUP(C323,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>冰霜之捷</v>
       </c>
       <c r="F323">
@@ -25416,8 +25416,8 @@
         <f t="shared" ref="D324:D334" si="58">D308</f>
         <v>1</v>
       </c>
-      <c r="E324" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C324,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E324" s="14" t="str" cm="1">
+        <f t="array" ref="E324">_xlfn.XLOOKUP(C324,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>冰晶术</v>
       </c>
       <c r="F324">
@@ -25450,8 +25450,8 @@
         <f t="shared" si="58"/>
         <v>2</v>
       </c>
-      <c r="E325" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C325,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E325" s="14" t="str" cm="1">
+        <f t="array" ref="E325">_xlfn.XLOOKUP(C325,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>冰晶术</v>
       </c>
       <c r="F325">
@@ -25484,8 +25484,8 @@
         <f t="shared" si="58"/>
         <v>3</v>
       </c>
-      <c r="E326" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C326,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E326" s="14" t="str" cm="1">
+        <f t="array" ref="E326">_xlfn.XLOOKUP(C326,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>冰晶术</v>
       </c>
       <c r="F326">
@@ -25518,8 +25518,8 @@
         <f t="shared" si="58"/>
         <v>4</v>
       </c>
-      <c r="E327" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C327,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E327" s="14" t="str" cm="1">
+        <f t="array" ref="E327">_xlfn.XLOOKUP(C327,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>冰晶术</v>
       </c>
       <c r="F327">
@@ -25552,8 +25552,8 @@
         <f t="shared" si="58"/>
         <v>5</v>
       </c>
-      <c r="E328" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C328,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E328" s="14" t="str" cm="1">
+        <f t="array" ref="E328">_xlfn.XLOOKUP(C328,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>冰晶术</v>
       </c>
       <c r="F328">
@@ -25586,8 +25586,8 @@
         <f t="shared" si="58"/>
         <v>6</v>
       </c>
-      <c r="E329" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C329,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E329" s="14" t="str" cm="1">
+        <f t="array" ref="E329">_xlfn.XLOOKUP(C329,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>冰晶术</v>
       </c>
       <c r="F329">
@@ -25620,8 +25620,8 @@
         <f t="shared" si="58"/>
         <v>7</v>
       </c>
-      <c r="E330" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C330,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E330" s="14" t="str" cm="1">
+        <f t="array" ref="E330">_xlfn.XLOOKUP(C330,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>冰晶术</v>
       </c>
       <c r="F330">
@@ -25654,8 +25654,8 @@
         <f t="shared" si="58"/>
         <v>8</v>
       </c>
-      <c r="E331" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C331,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E331" s="14" t="str" cm="1">
+        <f t="array" ref="E331">_xlfn.XLOOKUP(C331,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>冰晶术</v>
       </c>
       <c r="F331">
@@ -25688,8 +25688,8 @@
         <f t="shared" si="58"/>
         <v>9</v>
       </c>
-      <c r="E332" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C332,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E332" s="14" t="str" cm="1">
+        <f t="array" ref="E332">_xlfn.XLOOKUP(C332,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>冰晶术</v>
       </c>
       <c r="F332">
@@ -25722,8 +25722,8 @@
         <f t="shared" si="58"/>
         <v>10</v>
       </c>
-      <c r="E333" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C333,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E333" s="14" t="str" cm="1">
+        <f t="array" ref="E333">_xlfn.XLOOKUP(C333,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>冰晶术</v>
       </c>
       <c r="F333">
@@ -25756,8 +25756,8 @@
         <f t="shared" si="58"/>
         <v>11</v>
       </c>
-      <c r="E334" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C334,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E334" s="14" t="str" cm="1">
+        <f t="array" ref="E334">_xlfn.XLOOKUP(C334,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>冰晶术</v>
       </c>
       <c r="F334">
@@ -25790,8 +25790,8 @@
         <f t="shared" ref="D335:D345" si="60">D319</f>
         <v>12</v>
       </c>
-      <c r="E335" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C335,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E335" s="14" t="str" cm="1">
+        <f t="array" ref="E335">_xlfn.XLOOKUP(C335,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>冰晶术</v>
       </c>
       <c r="F335">
@@ -25824,8 +25824,8 @@
         <f t="shared" si="60"/>
         <v>13</v>
       </c>
-      <c r="E336" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C336,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E336" s="14" t="str" cm="1">
+        <f t="array" ref="E336">_xlfn.XLOOKUP(C336,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>冰晶术</v>
       </c>
       <c r="F336">
@@ -25858,8 +25858,8 @@
         <f t="shared" si="60"/>
         <v>14</v>
       </c>
-      <c r="E337" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C337,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E337" s="14" t="str" cm="1">
+        <f t="array" ref="E337">_xlfn.XLOOKUP(C337,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>冰晶术</v>
       </c>
       <c r="F337">
@@ -25892,8 +25892,8 @@
         <f t="shared" si="60"/>
         <v>15</v>
       </c>
-      <c r="E338" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C338,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E338" s="14" t="str" cm="1">
+        <f t="array" ref="E338">_xlfn.XLOOKUP(C338,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>冰晶术</v>
       </c>
       <c r="F338">
@@ -25926,8 +25926,8 @@
         <f t="shared" si="60"/>
         <v>16</v>
       </c>
-      <c r="E339" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C339,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E339" s="14" t="str" cm="1">
+        <f t="array" ref="E339">_xlfn.XLOOKUP(C339,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>冰晶术</v>
       </c>
       <c r="F339">
@@ -25960,8 +25960,8 @@
         <f t="shared" si="60"/>
         <v>1</v>
       </c>
-      <c r="E340" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C340,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E340" s="14" t="str" cm="1">
+        <f t="array" ref="E340">_xlfn.XLOOKUP(C340,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>元素脉冲</v>
       </c>
       <c r="F340">
@@ -25994,8 +25994,8 @@
         <f t="shared" si="60"/>
         <v>2</v>
       </c>
-      <c r="E341" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C341,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E341" s="14" t="str" cm="1">
+        <f t="array" ref="E341">_xlfn.XLOOKUP(C341,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>元素脉冲</v>
       </c>
       <c r="F341">
@@ -26028,8 +26028,8 @@
         <f t="shared" si="60"/>
         <v>3</v>
       </c>
-      <c r="E342" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C342,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E342" s="14" t="str" cm="1">
+        <f t="array" ref="E342">_xlfn.XLOOKUP(C342,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>元素脉冲</v>
       </c>
       <c r="F342">
@@ -26062,8 +26062,8 @@
         <f t="shared" si="60"/>
         <v>4</v>
       </c>
-      <c r="E343" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C343,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E343" s="14" t="str" cm="1">
+        <f t="array" ref="E343">_xlfn.XLOOKUP(C343,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>元素脉冲</v>
       </c>
       <c r="F343">
@@ -26096,8 +26096,8 @@
         <f t="shared" si="60"/>
         <v>5</v>
       </c>
-      <c r="E344" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C344,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E344" s="14" t="str" cm="1">
+        <f t="array" ref="E344">_xlfn.XLOOKUP(C344,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>元素脉冲</v>
       </c>
       <c r="F344">
@@ -26130,8 +26130,8 @@
         <f t="shared" si="60"/>
         <v>6</v>
       </c>
-      <c r="E345" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C345,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E345" s="14" t="str" cm="1">
+        <f t="array" ref="E345">_xlfn.XLOOKUP(C345,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>元素脉冲</v>
       </c>
       <c r="F345">
@@ -26164,8 +26164,8 @@
         <f t="shared" ref="D346:D371" si="62">D330</f>
         <v>7</v>
       </c>
-      <c r="E346" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C346,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E346" s="14" t="str" cm="1">
+        <f t="array" ref="E346">_xlfn.XLOOKUP(C346,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>元素脉冲</v>
       </c>
       <c r="F346">
@@ -26198,8 +26198,8 @@
         <f t="shared" si="62"/>
         <v>8</v>
       </c>
-      <c r="E347" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C347,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E347" s="14" t="str" cm="1">
+        <f t="array" ref="E347">_xlfn.XLOOKUP(C347,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>元素脉冲</v>
       </c>
       <c r="F347">
@@ -26232,8 +26232,8 @@
         <f t="shared" si="62"/>
         <v>9</v>
       </c>
-      <c r="E348" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C348,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E348" s="14" t="str" cm="1">
+        <f t="array" ref="E348">_xlfn.XLOOKUP(C348,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>元素脉冲</v>
       </c>
       <c r="F348">
@@ -26266,8 +26266,8 @@
         <f t="shared" si="62"/>
         <v>10</v>
       </c>
-      <c r="E349" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C349,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E349" s="14" t="str" cm="1">
+        <f t="array" ref="E349">_xlfn.XLOOKUP(C349,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>元素脉冲</v>
       </c>
       <c r="F349">
@@ -26300,8 +26300,8 @@
         <f t="shared" si="62"/>
         <v>11</v>
       </c>
-      <c r="E350" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C350,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E350" s="14" t="str" cm="1">
+        <f t="array" ref="E350">_xlfn.XLOOKUP(C350,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>元素脉冲</v>
       </c>
       <c r="F350">
@@ -26334,8 +26334,8 @@
         <f t="shared" si="62"/>
         <v>12</v>
       </c>
-      <c r="E351" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C351,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E351" s="14" t="str" cm="1">
+        <f t="array" ref="E351">_xlfn.XLOOKUP(C351,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>元素脉冲</v>
       </c>
       <c r="F351">
@@ -26368,8 +26368,8 @@
         <f t="shared" si="62"/>
         <v>13</v>
       </c>
-      <c r="E352" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C352,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E352" s="14" t="str" cm="1">
+        <f t="array" ref="E352">_xlfn.XLOOKUP(C352,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>元素脉冲</v>
       </c>
       <c r="F352">
@@ -26402,8 +26402,8 @@
         <f t="shared" si="62"/>
         <v>14</v>
       </c>
-      <c r="E353" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C353,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E353" s="14" t="str" cm="1">
+        <f t="array" ref="E353">_xlfn.XLOOKUP(C353,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>元素脉冲</v>
       </c>
       <c r="F353">
@@ -26436,8 +26436,8 @@
         <f t="shared" si="62"/>
         <v>15</v>
       </c>
-      <c r="E354" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C354,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E354" s="14" t="str" cm="1">
+        <f t="array" ref="E354">_xlfn.XLOOKUP(C354,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>元素脉冲</v>
       </c>
       <c r="F354">
@@ -26470,8 +26470,8 @@
         <f t="shared" si="62"/>
         <v>16</v>
       </c>
-      <c r="E355" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C355,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E355" s="14" t="str" cm="1">
+        <f t="array" ref="E355">_xlfn.XLOOKUP(C355,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>元素脉冲</v>
       </c>
       <c r="F355">
@@ -26504,8 +26504,8 @@
         <f t="shared" si="62"/>
         <v>1</v>
       </c>
-      <c r="E356" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C356,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E356" s="14" t="str" cm="1">
+        <f t="array" ref="E356">_xlfn.XLOOKUP(C356,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>毁灭意志</v>
       </c>
       <c r="F356">
@@ -26538,8 +26538,8 @@
         <f t="shared" si="62"/>
         <v>2</v>
       </c>
-      <c r="E357" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C357,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E357" s="14" t="str" cm="1">
+        <f t="array" ref="E357">_xlfn.XLOOKUP(C357,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>毁灭意志</v>
       </c>
       <c r="F357">
@@ -26572,8 +26572,8 @@
         <f t="shared" si="62"/>
         <v>3</v>
       </c>
-      <c r="E358" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C358,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E358" s="14" t="str" cm="1">
+        <f t="array" ref="E358">_xlfn.XLOOKUP(C358,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>毁灭意志</v>
       </c>
       <c r="F358">
@@ -26606,8 +26606,8 @@
         <f t="shared" si="62"/>
         <v>4</v>
       </c>
-      <c r="E359" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C359,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E359" s="14" t="str" cm="1">
+        <f t="array" ref="E359">_xlfn.XLOOKUP(C359,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>毁灭意志</v>
       </c>
       <c r="F359">
@@ -26640,8 +26640,8 @@
         <f t="shared" si="62"/>
         <v>5</v>
       </c>
-      <c r="E360" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C360,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E360" s="14" t="str" cm="1">
+        <f t="array" ref="E360">_xlfn.XLOOKUP(C360,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>毁灭意志</v>
       </c>
       <c r="F360">
@@ -26674,8 +26674,8 @@
         <f t="shared" si="62"/>
         <v>6</v>
       </c>
-      <c r="E361" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C361,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E361" s="14" t="str" cm="1">
+        <f t="array" ref="E361">_xlfn.XLOOKUP(C361,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>毁灭意志</v>
       </c>
       <c r="F361">
@@ -26708,8 +26708,8 @@
         <f t="shared" si="62"/>
         <v>7</v>
       </c>
-      <c r="E362" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C362,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E362" s="14" t="str" cm="1">
+        <f t="array" ref="E362">_xlfn.XLOOKUP(C362,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>毁灭意志</v>
       </c>
       <c r="F362">
@@ -26742,8 +26742,8 @@
         <f t="shared" si="62"/>
         <v>8</v>
       </c>
-      <c r="E363" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C363,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E363" s="14" t="str" cm="1">
+        <f t="array" ref="E363">_xlfn.XLOOKUP(C363,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>毁灭意志</v>
       </c>
       <c r="F363">
@@ -26776,8 +26776,8 @@
         <f t="shared" si="62"/>
         <v>9</v>
       </c>
-      <c r="E364" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C364,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E364" s="14" t="str" cm="1">
+        <f t="array" ref="E364">_xlfn.XLOOKUP(C364,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>毁灭意志</v>
       </c>
       <c r="F364">
@@ -26810,8 +26810,8 @@
         <f t="shared" si="62"/>
         <v>10</v>
       </c>
-      <c r="E365" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C365,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E365" s="14" t="str" cm="1">
+        <f t="array" ref="E365">_xlfn.XLOOKUP(C365,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>毁灭意志</v>
       </c>
       <c r="F365">
@@ -26844,8 +26844,8 @@
         <f t="shared" si="62"/>
         <v>11</v>
       </c>
-      <c r="E366" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C366,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E366" s="14" t="str" cm="1">
+        <f t="array" ref="E366">_xlfn.XLOOKUP(C366,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>毁灭意志</v>
       </c>
       <c r="F366">
@@ -26878,8 +26878,8 @@
         <f t="shared" si="62"/>
         <v>12</v>
       </c>
-      <c r="E367" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C367,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E367" s="14" t="str" cm="1">
+        <f t="array" ref="E367">_xlfn.XLOOKUP(C367,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>毁灭意志</v>
       </c>
       <c r="F367">
@@ -26912,8 +26912,8 @@
         <f t="shared" si="62"/>
         <v>13</v>
       </c>
-      <c r="E368" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C368,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E368" s="14" t="str" cm="1">
+        <f t="array" ref="E368">_xlfn.XLOOKUP(C368,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>毁灭意志</v>
       </c>
       <c r="F368">
@@ -26946,8 +26946,8 @@
         <f t="shared" si="62"/>
         <v>14</v>
       </c>
-      <c r="E369" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C369,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E369" s="14" t="str" cm="1">
+        <f t="array" ref="E369">_xlfn.XLOOKUP(C369,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>毁灭意志</v>
       </c>
       <c r="F369">
@@ -26980,8 +26980,8 @@
         <f t="shared" si="62"/>
         <v>15</v>
       </c>
-      <c r="E370" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C370,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E370" s="14" t="str" cm="1">
+        <f t="array" ref="E370">_xlfn.XLOOKUP(C370,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>毁灭意志</v>
       </c>
       <c r="F370">
@@ -27014,8 +27014,8 @@
         <f t="shared" si="62"/>
         <v>16</v>
       </c>
-      <c r="E371" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C371,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E371" s="14" t="str" cm="1">
+        <f t="array" ref="E371">_xlfn.XLOOKUP(C371,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>毁灭意志</v>
       </c>
       <c r="F371">
@@ -27047,8 +27047,8 @@
       <c r="D372" s="14">
         <v>1</v>
       </c>
-      <c r="E372" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C372,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E372" s="14" t="str" cm="1">
+        <f t="array" ref="E372">_xlfn.XLOOKUP(C372,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>迅捷</v>
       </c>
       <c r="F372">
@@ -27080,8 +27080,8 @@
       <c r="D373" s="14">
         <v>2</v>
       </c>
-      <c r="E373" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C373,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E373" s="14" t="str" cm="1">
+        <f t="array" ref="E373">_xlfn.XLOOKUP(C373,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>迅捷</v>
       </c>
       <c r="F373">
@@ -27113,8 +27113,8 @@
       <c r="D374" s="14">
         <v>3</v>
       </c>
-      <c r="E374" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C374,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E374" s="14" t="str" cm="1">
+        <f t="array" ref="E374">_xlfn.XLOOKUP(C374,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>迅捷</v>
       </c>
       <c r="F374">
@@ -27146,8 +27146,8 @@
       <c r="D375" s="14">
         <v>4</v>
       </c>
-      <c r="E375" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C375,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E375" s="14" t="str" cm="1">
+        <f t="array" ref="E375">_xlfn.XLOOKUP(C375,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>迅捷</v>
       </c>
       <c r="F375">
@@ -27179,8 +27179,8 @@
       <c r="D376" s="14">
         <v>5</v>
       </c>
-      <c r="E376" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C376,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E376" s="14" t="str" cm="1">
+        <f t="array" ref="E376">_xlfn.XLOOKUP(C376,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>迅捷</v>
       </c>
       <c r="F376">
@@ -27212,8 +27212,8 @@
       <c r="D377" s="14">
         <v>6</v>
       </c>
-      <c r="E377" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C377,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E377" s="14" t="str" cm="1">
+        <f t="array" ref="E377">_xlfn.XLOOKUP(C377,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>迅捷</v>
       </c>
       <c r="F377">
@@ -27245,8 +27245,8 @@
       <c r="D378" s="14">
         <v>7</v>
       </c>
-      <c r="E378" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C378,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E378" s="14" t="str" cm="1">
+        <f t="array" ref="E378">_xlfn.XLOOKUP(C378,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>迅捷</v>
       </c>
       <c r="F378">
@@ -27278,8 +27278,8 @@
       <c r="D379" s="14">
         <v>8</v>
       </c>
-      <c r="E379" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C379,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E379" s="14" t="str" cm="1">
+        <f t="array" ref="E379">_xlfn.XLOOKUP(C379,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>迅捷</v>
       </c>
       <c r="F379">
@@ -27311,8 +27311,8 @@
       <c r="D380" s="14">
         <v>9</v>
       </c>
-      <c r="E380" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C380,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E380" s="14" t="str" cm="1">
+        <f t="array" ref="E380">_xlfn.XLOOKUP(C380,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>迅捷</v>
       </c>
       <c r="F380">
@@ -27344,8 +27344,8 @@
       <c r="D381" s="14">
         <v>10</v>
       </c>
-      <c r="E381" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C381,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E381" s="14" t="str" cm="1">
+        <f t="array" ref="E381">_xlfn.XLOOKUP(C381,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>迅捷</v>
       </c>
       <c r="F381">
@@ -27377,8 +27377,8 @@
       <c r="D382" s="14">
         <v>11</v>
       </c>
-      <c r="E382" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C382,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E382" s="14" t="str" cm="1">
+        <f t="array" ref="E382">_xlfn.XLOOKUP(C382,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>迅捷</v>
       </c>
       <c r="F382">
@@ -27410,8 +27410,8 @@
       <c r="D383" s="14">
         <v>12</v>
       </c>
-      <c r="E383" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C383,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E383" s="14" t="str" cm="1">
+        <f t="array" ref="E383">_xlfn.XLOOKUP(C383,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>迅捷</v>
       </c>
       <c r="F383">
@@ -27443,8 +27443,8 @@
       <c r="D384" s="14">
         <v>13</v>
       </c>
-      <c r="E384" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C384,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E384" s="14" t="str" cm="1">
+        <f t="array" ref="E384">_xlfn.XLOOKUP(C384,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>迅捷</v>
       </c>
       <c r="F384">
@@ -27476,8 +27476,8 @@
       <c r="D385" s="14">
         <v>14</v>
       </c>
-      <c r="E385" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C385,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E385" s="14" t="str" cm="1">
+        <f t="array" ref="E385">_xlfn.XLOOKUP(C385,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>迅捷</v>
       </c>
       <c r="F385">
@@ -27509,8 +27509,8 @@
       <c r="D386" s="14">
         <v>15</v>
       </c>
-      <c r="E386" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C386,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E386" s="14" t="str" cm="1">
+        <f t="array" ref="E386">_xlfn.XLOOKUP(C386,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>迅捷</v>
       </c>
       <c r="F386">
@@ -27542,8 +27542,8 @@
       <c r="D387" s="14">
         <v>16</v>
       </c>
-      <c r="E387" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C387,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E387" s="14" t="str" cm="1">
+        <f t="array" ref="E387">_xlfn.XLOOKUP(C387,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>迅捷</v>
       </c>
       <c r="F387">
@@ -27576,8 +27576,8 @@
         <f>D372</f>
         <v>1</v>
       </c>
-      <c r="E388" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C388,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E388" s="14" t="str" cm="1">
+        <f t="array" ref="E388">_xlfn.XLOOKUP(C388,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>吞噬</v>
       </c>
       <c r="F388">
@@ -27610,8 +27610,8 @@
         <f>D373</f>
         <v>2</v>
       </c>
-      <c r="E389" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C389,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E389" s="14" t="str" cm="1">
+        <f t="array" ref="E389">_xlfn.XLOOKUP(C389,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>吞噬</v>
       </c>
       <c r="F389">
@@ -27644,8 +27644,8 @@
         <f t="shared" ref="D390:D398" si="70">D374</f>
         <v>3</v>
       </c>
-      <c r="E390" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C390,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E390" s="14" t="str" cm="1">
+        <f t="array" ref="E390">_xlfn.XLOOKUP(C390,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>吞噬</v>
       </c>
       <c r="F390">
@@ -27678,8 +27678,8 @@
         <f t="shared" si="70"/>
         <v>4</v>
       </c>
-      <c r="E391" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C391,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E391" s="14" t="str" cm="1">
+        <f t="array" ref="E391">_xlfn.XLOOKUP(C391,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>吞噬</v>
       </c>
       <c r="F391">
@@ -27712,8 +27712,8 @@
         <f t="shared" si="70"/>
         <v>5</v>
       </c>
-      <c r="E392" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C392,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E392" s="14" t="str" cm="1">
+        <f t="array" ref="E392">_xlfn.XLOOKUP(C392,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>吞噬</v>
       </c>
       <c r="F392">
@@ -27746,8 +27746,8 @@
         <f t="shared" si="70"/>
         <v>6</v>
       </c>
-      <c r="E393" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C393,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E393" s="14" t="str" cm="1">
+        <f t="array" ref="E393">_xlfn.XLOOKUP(C393,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>吞噬</v>
       </c>
       <c r="F393">
@@ -27780,8 +27780,8 @@
         <f t="shared" si="70"/>
         <v>7</v>
       </c>
-      <c r="E394" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C394,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E394" s="14" t="str" cm="1">
+        <f t="array" ref="E394">_xlfn.XLOOKUP(C394,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>吞噬</v>
       </c>
       <c r="F394">
@@ -27814,8 +27814,8 @@
         <f t="shared" si="70"/>
         <v>8</v>
       </c>
-      <c r="E395" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C395,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E395" s="14" t="str" cm="1">
+        <f t="array" ref="E395">_xlfn.XLOOKUP(C395,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>吞噬</v>
       </c>
       <c r="F395">
@@ -27848,8 +27848,8 @@
         <f t="shared" si="70"/>
         <v>9</v>
       </c>
-      <c r="E396" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C396,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E396" s="14" t="str" cm="1">
+        <f t="array" ref="E396">_xlfn.XLOOKUP(C396,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>吞噬</v>
       </c>
       <c r="F396">
@@ -27882,8 +27882,8 @@
         <f t="shared" si="70"/>
         <v>10</v>
       </c>
-      <c r="E397" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C397,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E397" s="14" t="str" cm="1">
+        <f t="array" ref="E397">_xlfn.XLOOKUP(C397,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>吞噬</v>
       </c>
       <c r="F397">
@@ -27916,8 +27916,8 @@
         <f t="shared" si="70"/>
         <v>11</v>
       </c>
-      <c r="E398" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C398,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E398" s="14" t="str" cm="1">
+        <f t="array" ref="E398">_xlfn.XLOOKUP(C398,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>吞噬</v>
       </c>
       <c r="F398">
@@ -27950,8 +27950,8 @@
         <f t="shared" ref="D399:D405" si="72">D383</f>
         <v>12</v>
       </c>
-      <c r="E399" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C399,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E399" s="14" t="str" cm="1">
+        <f t="array" ref="E399">_xlfn.XLOOKUP(C399,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>吞噬</v>
       </c>
       <c r="F399">
@@ -27984,8 +27984,8 @@
         <f t="shared" si="72"/>
         <v>13</v>
       </c>
-      <c r="E400" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C400,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E400" s="14" t="str" cm="1">
+        <f t="array" ref="E400">_xlfn.XLOOKUP(C400,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>吞噬</v>
       </c>
       <c r="F400">
@@ -28018,8 +28018,8 @@
         <f t="shared" si="72"/>
         <v>14</v>
       </c>
-      <c r="E401" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C401,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E401" s="14" t="str" cm="1">
+        <f t="array" ref="E401">_xlfn.XLOOKUP(C401,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>吞噬</v>
       </c>
       <c r="F401">
@@ -28052,8 +28052,8 @@
         <f t="shared" si="72"/>
         <v>15</v>
       </c>
-      <c r="E402" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C402,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E402" s="14" t="str" cm="1">
+        <f t="array" ref="E402">_xlfn.XLOOKUP(C402,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>吞噬</v>
       </c>
       <c r="F402">
@@ -28086,8 +28086,8 @@
         <f t="shared" si="72"/>
         <v>16</v>
       </c>
-      <c r="E403" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C403,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E403" s="14" t="str" cm="1">
+        <f t="array" ref="E403">_xlfn.XLOOKUP(C403,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>吞噬</v>
       </c>
       <c r="F403">
@@ -28120,8 +28120,8 @@
         <f t="shared" si="72"/>
         <v>1</v>
       </c>
-      <c r="E404" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C404,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E404" s="14" t="str" cm="1">
+        <f t="array" ref="E404">_xlfn.XLOOKUP(C404,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>迅捷</v>
       </c>
       <c r="F404">
@@ -28154,8 +28154,8 @@
         <f t="shared" si="72"/>
         <v>2</v>
       </c>
-      <c r="E405" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C405,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E405" s="14" t="str" cm="1">
+        <f t="array" ref="E405">_xlfn.XLOOKUP(C405,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>迅捷</v>
       </c>
       <c r="F405">
@@ -28188,8 +28188,8 @@
         <f t="shared" ref="D406:D412" si="75">D390</f>
         <v>3</v>
       </c>
-      <c r="E406" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C406,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E406" s="14" t="str" cm="1">
+        <f t="array" ref="E406">_xlfn.XLOOKUP(C406,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>迅捷</v>
       </c>
       <c r="F406">
@@ -28222,8 +28222,8 @@
         <f t="shared" si="75"/>
         <v>4</v>
       </c>
-      <c r="E407" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C407,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E407" s="14" t="str" cm="1">
+        <f t="array" ref="E407">_xlfn.XLOOKUP(C407,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>迅捷</v>
       </c>
       <c r="F407">
@@ -28256,8 +28256,8 @@
         <f t="shared" si="75"/>
         <v>5</v>
       </c>
-      <c r="E408" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C408,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E408" s="14" t="str" cm="1">
+        <f t="array" ref="E408">_xlfn.XLOOKUP(C408,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>迅捷</v>
       </c>
       <c r="F408">
@@ -28290,8 +28290,8 @@
         <f t="shared" si="75"/>
         <v>6</v>
       </c>
-      <c r="E409" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C409,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E409" s="14" t="str" cm="1">
+        <f t="array" ref="E409">_xlfn.XLOOKUP(C409,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>迅捷</v>
       </c>
       <c r="F409">
@@ -28324,8 +28324,8 @@
         <f t="shared" si="75"/>
         <v>7</v>
       </c>
-      <c r="E410" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C410,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E410" s="14" t="str" cm="1">
+        <f t="array" ref="E410">_xlfn.XLOOKUP(C410,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>迅捷</v>
       </c>
       <c r="F410">
@@ -28358,8 +28358,8 @@
         <f t="shared" si="75"/>
         <v>8</v>
       </c>
-      <c r="E411" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C411,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E411" s="14" t="str" cm="1">
+        <f t="array" ref="E411">_xlfn.XLOOKUP(C411,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>迅捷</v>
       </c>
       <c r="F411">
@@ -28392,8 +28392,8 @@
         <f t="shared" si="75"/>
         <v>9</v>
       </c>
-      <c r="E412" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C412,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E412" s="14" t="str" cm="1">
+        <f t="array" ref="E412">_xlfn.XLOOKUP(C412,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>迅捷</v>
       </c>
       <c r="F412">
@@ -28426,8 +28426,8 @@
         <f t="shared" ref="D413:D426" si="78">D397</f>
         <v>10</v>
       </c>
-      <c r="E413" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C413,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E413" s="14" t="str" cm="1">
+        <f t="array" ref="E413">_xlfn.XLOOKUP(C413,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>迅捷</v>
       </c>
       <c r="F413">
@@ -28460,8 +28460,8 @@
         <f t="shared" si="78"/>
         <v>11</v>
       </c>
-      <c r="E414" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C414,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E414" s="14" t="str" cm="1">
+        <f t="array" ref="E414">_xlfn.XLOOKUP(C414,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>迅捷</v>
       </c>
       <c r="F414">
@@ -28494,8 +28494,8 @@
         <f t="shared" si="78"/>
         <v>12</v>
       </c>
-      <c r="E415" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C415,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E415" s="14" t="str" cm="1">
+        <f t="array" ref="E415">_xlfn.XLOOKUP(C415,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>迅捷</v>
       </c>
       <c r="F415">
@@ -28528,8 +28528,8 @@
         <f t="shared" si="78"/>
         <v>13</v>
       </c>
-      <c r="E416" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C416,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E416" s="14" t="str" cm="1">
+        <f t="array" ref="E416">_xlfn.XLOOKUP(C416,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>迅捷</v>
       </c>
       <c r="F416">
@@ -28562,8 +28562,8 @@
         <f t="shared" si="78"/>
         <v>14</v>
       </c>
-      <c r="E417" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C417,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E417" s="14" t="str" cm="1">
+        <f t="array" ref="E417">_xlfn.XLOOKUP(C417,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>迅捷</v>
       </c>
       <c r="F417">
@@ -28596,8 +28596,8 @@
         <f t="shared" si="78"/>
         <v>15</v>
       </c>
-      <c r="E418" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C418,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E418" s="14" t="str" cm="1">
+        <f t="array" ref="E418">_xlfn.XLOOKUP(C418,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>迅捷</v>
       </c>
       <c r="F418">
@@ -28630,8 +28630,8 @@
         <f t="shared" si="78"/>
         <v>16</v>
       </c>
-      <c r="E419" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C419,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E419" s="14" t="str" cm="1">
+        <f t="array" ref="E419">_xlfn.XLOOKUP(C419,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>迅捷</v>
       </c>
       <c r="F419">
@@ -28664,8 +28664,8 @@
         <f t="shared" si="78"/>
         <v>1</v>
       </c>
-      <c r="E420" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C420,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E420" s="14" t="str" cm="1">
+        <f t="array" ref="E420">_xlfn.XLOOKUP(C420,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>精准投射</v>
       </c>
       <c r="F420">
@@ -28698,8 +28698,8 @@
         <f t="shared" si="78"/>
         <v>2</v>
       </c>
-      <c r="E421" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C421,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E421" s="14" t="str" cm="1">
+        <f t="array" ref="E421">_xlfn.XLOOKUP(C421,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>精准投射</v>
       </c>
       <c r="F421">
@@ -28732,8 +28732,8 @@
         <f t="shared" ref="D422:D430" si="83">D406</f>
         <v>3</v>
       </c>
-      <c r="E422" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C422,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E422" s="14" t="str" cm="1">
+        <f t="array" ref="E422">_xlfn.XLOOKUP(C422,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>精准投射</v>
       </c>
       <c r="F422">
@@ -28766,8 +28766,8 @@
         <f t="shared" si="83"/>
         <v>4</v>
       </c>
-      <c r="E423" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C423,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E423" s="14" t="str" cm="1">
+        <f t="array" ref="E423">_xlfn.XLOOKUP(C423,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>精准投射</v>
       </c>
       <c r="F423">
@@ -28800,8 +28800,8 @@
         <f t="shared" si="83"/>
         <v>5</v>
       </c>
-      <c r="E424" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C424,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E424" s="14" t="str" cm="1">
+        <f t="array" ref="E424">_xlfn.XLOOKUP(C424,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>精准投射</v>
       </c>
       <c r="F424">
@@ -28834,8 +28834,8 @@
         <f t="shared" si="83"/>
         <v>6</v>
       </c>
-      <c r="E425" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C425,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E425" s="14" t="str" cm="1">
+        <f t="array" ref="E425">_xlfn.XLOOKUP(C425,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>精准投射</v>
       </c>
       <c r="F425">
@@ -28868,8 +28868,8 @@
         <f t="shared" si="83"/>
         <v>7</v>
       </c>
-      <c r="E426" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C426,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E426" s="14" t="str" cm="1">
+        <f t="array" ref="E426">_xlfn.XLOOKUP(C426,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>精准投射</v>
       </c>
       <c r="F426">
@@ -28902,8 +28902,8 @@
         <f t="shared" si="83"/>
         <v>8</v>
       </c>
-      <c r="E427" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C427,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E427" s="14" t="str" cm="1">
+        <f t="array" ref="E427">_xlfn.XLOOKUP(C427,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>精准投射</v>
       </c>
       <c r="F427">
@@ -28936,8 +28936,8 @@
         <f t="shared" si="83"/>
         <v>9</v>
       </c>
-      <c r="E428" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C428,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E428" s="14" t="str" cm="1">
+        <f t="array" ref="E428">_xlfn.XLOOKUP(C428,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>精准投射</v>
       </c>
       <c r="F428">
@@ -28970,8 +28970,8 @@
         <f t="shared" si="83"/>
         <v>10</v>
       </c>
-      <c r="E429" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C429,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E429" s="14" t="str" cm="1">
+        <f t="array" ref="E429">_xlfn.XLOOKUP(C429,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>精准投射</v>
       </c>
       <c r="F429">
@@ -29004,8 +29004,8 @@
         <f t="shared" si="83"/>
         <v>11</v>
       </c>
-      <c r="E430" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C430,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E430" s="14" t="str" cm="1">
+        <f t="array" ref="E430">_xlfn.XLOOKUP(C430,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>精准投射</v>
       </c>
       <c r="F430">
@@ -29038,8 +29038,8 @@
         <f t="shared" ref="D431:D437" si="86">D415</f>
         <v>12</v>
       </c>
-      <c r="E431" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C431,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E431" s="14" t="str" cm="1">
+        <f t="array" ref="E431">_xlfn.XLOOKUP(C431,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>精准投射</v>
       </c>
       <c r="F431">
@@ -29072,8 +29072,8 @@
         <f t="shared" si="86"/>
         <v>13</v>
       </c>
-      <c r="E432" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C432,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E432" s="14" t="str" cm="1">
+        <f t="array" ref="E432">_xlfn.XLOOKUP(C432,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>精准投射</v>
       </c>
       <c r="F432">
@@ -29106,8 +29106,8 @@
         <f t="shared" si="86"/>
         <v>14</v>
       </c>
-      <c r="E433" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C433,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E433" s="14" t="str" cm="1">
+        <f t="array" ref="E433">_xlfn.XLOOKUP(C433,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>精准投射</v>
       </c>
       <c r="F433">
@@ -29140,8 +29140,8 @@
         <f t="shared" si="86"/>
         <v>15</v>
       </c>
-      <c r="E434" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C434,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E434" s="14" t="str" cm="1">
+        <f t="array" ref="E434">_xlfn.XLOOKUP(C434,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>精准投射</v>
       </c>
       <c r="F434">
@@ -29174,8 +29174,8 @@
         <f t="shared" si="86"/>
         <v>16</v>
       </c>
-      <c r="E435" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C435,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E435" s="14" t="str" cm="1">
+        <f t="array" ref="E435">_xlfn.XLOOKUP(C435,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>精准投射</v>
       </c>
       <c r="F435">
@@ -29208,8 +29208,8 @@
         <f t="shared" si="86"/>
         <v>1</v>
       </c>
-      <c r="E436" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C436,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E436" s="14" t="str" cm="1">
+        <f t="array" ref="E436">_xlfn.XLOOKUP(C436,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>领域扩张</v>
       </c>
       <c r="F436">
@@ -29242,8 +29242,8 @@
         <f t="shared" si="86"/>
         <v>2</v>
       </c>
-      <c r="E437" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C437,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E437" s="14" t="str" cm="1">
+        <f t="array" ref="E437">_xlfn.XLOOKUP(C437,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>领域扩张</v>
       </c>
       <c r="F437">
@@ -29276,8 +29276,8 @@
         <f t="shared" ref="D438:D444" si="89">D422</f>
         <v>3</v>
       </c>
-      <c r="E438" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C438,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E438" s="14" t="str" cm="1">
+        <f t="array" ref="E438">_xlfn.XLOOKUP(C438,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>领域扩张</v>
       </c>
       <c r="F438">
@@ -29310,8 +29310,8 @@
         <f t="shared" si="89"/>
         <v>4</v>
       </c>
-      <c r="E439" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C439,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E439" s="14" t="str" cm="1">
+        <f t="array" ref="E439">_xlfn.XLOOKUP(C439,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>领域扩张</v>
       </c>
       <c r="F439">
@@ -29344,8 +29344,8 @@
         <f t="shared" si="89"/>
         <v>5</v>
       </c>
-      <c r="E440" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C440,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E440" s="14" t="str" cm="1">
+        <f t="array" ref="E440">_xlfn.XLOOKUP(C440,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>领域扩张</v>
       </c>
       <c r="F440">
@@ -29378,8 +29378,8 @@
         <f t="shared" si="89"/>
         <v>6</v>
       </c>
-      <c r="E441" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C441,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E441" s="14" t="str" cm="1">
+        <f t="array" ref="E441">_xlfn.XLOOKUP(C441,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>领域扩张</v>
       </c>
       <c r="F441">
@@ -29412,8 +29412,8 @@
         <f t="shared" si="89"/>
         <v>7</v>
       </c>
-      <c r="E442" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C442,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E442" s="14" t="str" cm="1">
+        <f t="array" ref="E442">_xlfn.XLOOKUP(C442,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>领域扩张</v>
       </c>
       <c r="F442">
@@ -29446,8 +29446,8 @@
         <f t="shared" si="89"/>
         <v>8</v>
       </c>
-      <c r="E443" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C443,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E443" s="14" t="str" cm="1">
+        <f t="array" ref="E443">_xlfn.XLOOKUP(C443,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>领域扩张</v>
       </c>
       <c r="F443">
@@ -29480,8 +29480,8 @@
         <f t="shared" si="89"/>
         <v>9</v>
       </c>
-      <c r="E444" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C444,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E444" s="14" t="str" cm="1">
+        <f t="array" ref="E444">_xlfn.XLOOKUP(C444,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>领域扩张</v>
       </c>
       <c r="F444">
@@ -29514,8 +29514,8 @@
         <f t="shared" ref="D445:D453" si="92">D429</f>
         <v>10</v>
       </c>
-      <c r="E445" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C445,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E445" s="14" t="str" cm="1">
+        <f t="array" ref="E445">_xlfn.XLOOKUP(C445,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>领域扩张</v>
       </c>
       <c r="F445">
@@ -29548,8 +29548,8 @@
         <f t="shared" si="92"/>
         <v>11</v>
       </c>
-      <c r="E446" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C446,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E446" s="14" t="str" cm="1">
+        <f t="array" ref="E446">_xlfn.XLOOKUP(C446,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>领域扩张</v>
       </c>
       <c r="F446">
@@ -29582,8 +29582,8 @@
         <f t="shared" si="92"/>
         <v>12</v>
       </c>
-      <c r="E447" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C447,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E447" s="14" t="str" cm="1">
+        <f t="array" ref="E447">_xlfn.XLOOKUP(C447,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>领域扩张</v>
       </c>
       <c r="F447">
@@ -29616,8 +29616,8 @@
         <f t="shared" si="92"/>
         <v>13</v>
       </c>
-      <c r="E448" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C448,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E448" s="14" t="str" cm="1">
+        <f t="array" ref="E448">_xlfn.XLOOKUP(C448,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>领域扩张</v>
       </c>
       <c r="F448">
@@ -29650,8 +29650,8 @@
         <f t="shared" si="92"/>
         <v>14</v>
       </c>
-      <c r="E449" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C449,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E449" s="14" t="str" cm="1">
+        <f t="array" ref="E449">_xlfn.XLOOKUP(C449,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>领域扩张</v>
       </c>
       <c r="F449">
@@ -29684,8 +29684,8 @@
         <f t="shared" si="92"/>
         <v>15</v>
       </c>
-      <c r="E450" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C450,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E450" s="14" t="str" cm="1">
+        <f t="array" ref="E450">_xlfn.XLOOKUP(C450,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>领域扩张</v>
       </c>
       <c r="F450">
@@ -29718,8 +29718,8 @@
         <f t="shared" si="92"/>
         <v>16</v>
       </c>
-      <c r="E451" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C451,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E451" s="14" t="str" cm="1">
+        <f t="array" ref="E451">_xlfn.XLOOKUP(C451,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>领域扩张</v>
       </c>
       <c r="F451">
@@ -29752,8 +29752,8 @@
         <f t="shared" si="92"/>
         <v>1</v>
       </c>
-      <c r="E452" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C452,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E452" s="14" t="str" cm="1">
+        <f t="array" ref="E452">_xlfn.XLOOKUP(C452,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>狂暴</v>
       </c>
       <c r="F452">
@@ -29786,8 +29786,8 @@
         <f t="shared" si="92"/>
         <v>2</v>
       </c>
-      <c r="E453" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C453,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E453" s="14" t="str" cm="1">
+        <f t="array" ref="E453">_xlfn.XLOOKUP(C453,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>狂暴</v>
       </c>
       <c r="F453">
@@ -29820,8 +29820,8 @@
         <f t="shared" ref="D454:D460" si="96">D438</f>
         <v>3</v>
       </c>
-      <c r="E454" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C454,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E454" s="14" t="str" cm="1">
+        <f t="array" ref="E454">_xlfn.XLOOKUP(C454,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>狂暴</v>
       </c>
       <c r="F454">
@@ -29854,8 +29854,8 @@
         <f t="shared" si="96"/>
         <v>4</v>
       </c>
-      <c r="E455" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C455,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E455" s="14" t="str" cm="1">
+        <f t="array" ref="E455">_xlfn.XLOOKUP(C455,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>狂暴</v>
       </c>
       <c r="F455">
@@ -29888,8 +29888,8 @@
         <f t="shared" si="96"/>
         <v>5</v>
       </c>
-      <c r="E456" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C456,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E456" s="14" t="str" cm="1">
+        <f t="array" ref="E456">_xlfn.XLOOKUP(C456,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>狂暴</v>
       </c>
       <c r="F456">
@@ -29922,8 +29922,8 @@
         <f t="shared" si="96"/>
         <v>6</v>
       </c>
-      <c r="E457" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C457,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E457" s="14" t="str" cm="1">
+        <f t="array" ref="E457">_xlfn.XLOOKUP(C457,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>狂暴</v>
       </c>
       <c r="F457">
@@ -29956,8 +29956,8 @@
         <f t="shared" si="96"/>
         <v>7</v>
       </c>
-      <c r="E458" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C458,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E458" s="14" t="str" cm="1">
+        <f t="array" ref="E458">_xlfn.XLOOKUP(C458,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>狂暴</v>
       </c>
       <c r="F458">
@@ -29990,8 +29990,8 @@
         <f t="shared" si="96"/>
         <v>8</v>
       </c>
-      <c r="E459" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C459,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E459" s="14" t="str" cm="1">
+        <f t="array" ref="E459">_xlfn.XLOOKUP(C459,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>狂暴</v>
       </c>
       <c r="F459">
@@ -30024,8 +30024,8 @@
         <f t="shared" si="96"/>
         <v>9</v>
       </c>
-      <c r="E460" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C460,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E460" s="14" t="str" cm="1">
+        <f t="array" ref="E460">_xlfn.XLOOKUP(C460,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>狂暴</v>
       </c>
       <c r="F460">
@@ -30058,8 +30058,8 @@
         <f t="shared" ref="D461:D469" si="98">D445</f>
         <v>10</v>
       </c>
-      <c r="E461" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C461,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E461" s="14" t="str" cm="1">
+        <f t="array" ref="E461">_xlfn.XLOOKUP(C461,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>狂暴</v>
       </c>
       <c r="F461">
@@ -30092,8 +30092,8 @@
         <f t="shared" si="98"/>
         <v>11</v>
       </c>
-      <c r="E462" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C462,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E462" s="14" t="str" cm="1">
+        <f t="array" ref="E462">_xlfn.XLOOKUP(C462,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>狂暴</v>
       </c>
       <c r="F462">
@@ -30126,8 +30126,8 @@
         <f t="shared" si="98"/>
         <v>12</v>
       </c>
-      <c r="E463" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C463,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E463" s="14" t="str" cm="1">
+        <f t="array" ref="E463">_xlfn.XLOOKUP(C463,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>狂暴</v>
       </c>
       <c r="F463">
@@ -30160,8 +30160,8 @@
         <f t="shared" si="98"/>
         <v>13</v>
       </c>
-      <c r="E464" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C464,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E464" s="14" t="str" cm="1">
+        <f t="array" ref="E464">_xlfn.XLOOKUP(C464,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>狂暴</v>
       </c>
       <c r="F464">
@@ -30194,8 +30194,8 @@
         <f t="shared" si="98"/>
         <v>14</v>
       </c>
-      <c r="E465" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C465,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E465" s="14" t="str" cm="1">
+        <f t="array" ref="E465">_xlfn.XLOOKUP(C465,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>狂暴</v>
       </c>
       <c r="F465">
@@ -30228,8 +30228,8 @@
         <f t="shared" si="98"/>
         <v>15</v>
       </c>
-      <c r="E466" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C466,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E466" s="14" t="str" cm="1">
+        <f t="array" ref="E466">_xlfn.XLOOKUP(C466,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>狂暴</v>
       </c>
       <c r="F466">
@@ -30262,8 +30262,8 @@
         <f t="shared" si="98"/>
         <v>16</v>
       </c>
-      <c r="E467" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C467,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E467" s="14" t="str" cm="1">
+        <f t="array" ref="E467">_xlfn.XLOOKUP(C467,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>狂暴</v>
       </c>
       <c r="F467">
@@ -30296,8 +30296,8 @@
         <f t="shared" si="98"/>
         <v>1</v>
       </c>
-      <c r="E468" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C468,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E468" s="14" t="str" cm="1">
+        <f t="array" ref="E468">_xlfn.XLOOKUP(C468,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>生命再生</v>
       </c>
       <c r="F468">
@@ -30330,8 +30330,8 @@
         <f t="shared" si="98"/>
         <v>2</v>
       </c>
-      <c r="E469" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C469,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E469" s="14" t="str" cm="1">
+        <f t="array" ref="E469">_xlfn.XLOOKUP(C469,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>生命再生</v>
       </c>
       <c r="F469">
@@ -30364,8 +30364,8 @@
         <f t="shared" ref="D470:D476" si="102">D454</f>
         <v>3</v>
       </c>
-      <c r="E470" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C470,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E470" s="14" t="str" cm="1">
+        <f t="array" ref="E470">_xlfn.XLOOKUP(C470,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>生命再生</v>
       </c>
       <c r="F470">
@@ -30398,8 +30398,8 @@
         <f t="shared" si="102"/>
         <v>4</v>
       </c>
-      <c r="E471" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C471,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E471" s="14" t="str" cm="1">
+        <f t="array" ref="E471">_xlfn.XLOOKUP(C471,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>生命再生</v>
       </c>
       <c r="F471">
@@ -30432,8 +30432,8 @@
         <f t="shared" si="102"/>
         <v>5</v>
       </c>
-      <c r="E472" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C472,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E472" s="14" t="str" cm="1">
+        <f t="array" ref="E472">_xlfn.XLOOKUP(C472,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>生命再生</v>
       </c>
       <c r="F472">
@@ -30466,8 +30466,8 @@
         <f t="shared" si="102"/>
         <v>6</v>
       </c>
-      <c r="E473" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C473,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E473" s="14" t="str" cm="1">
+        <f t="array" ref="E473">_xlfn.XLOOKUP(C473,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>生命再生</v>
       </c>
       <c r="F473">
@@ -30500,8 +30500,8 @@
         <f t="shared" si="102"/>
         <v>7</v>
       </c>
-      <c r="E474" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C474,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E474" s="14" t="str" cm="1">
+        <f t="array" ref="E474">_xlfn.XLOOKUP(C474,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>生命再生</v>
       </c>
       <c r="F474">
@@ -30534,8 +30534,8 @@
         <f t="shared" si="102"/>
         <v>8</v>
       </c>
-      <c r="E475" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C475,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E475" s="14" t="str" cm="1">
+        <f t="array" ref="E475">_xlfn.XLOOKUP(C475,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>生命再生</v>
       </c>
       <c r="F475">
@@ -30568,8 +30568,8 @@
         <f t="shared" si="102"/>
         <v>9</v>
       </c>
-      <c r="E476" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C476,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E476" s="14" t="str" cm="1">
+        <f t="array" ref="E476">_xlfn.XLOOKUP(C476,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>生命再生</v>
       </c>
       <c r="F476">
@@ -30602,8 +30602,8 @@
         <f t="shared" ref="D477:D483" si="105">D461</f>
         <v>10</v>
       </c>
-      <c r="E477" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C477,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E477" s="14" t="str" cm="1">
+        <f t="array" ref="E477">_xlfn.XLOOKUP(C477,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>生命再生</v>
       </c>
       <c r="F477">
@@ -30636,8 +30636,8 @@
         <f t="shared" si="105"/>
         <v>11</v>
       </c>
-      <c r="E478" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C478,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E478" s="14" t="str" cm="1">
+        <f t="array" ref="E478">_xlfn.XLOOKUP(C478,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>生命再生</v>
       </c>
       <c r="F478">
@@ -30670,8 +30670,8 @@
         <f t="shared" si="105"/>
         <v>12</v>
       </c>
-      <c r="E479" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C479,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E479" s="14" t="str" cm="1">
+        <f t="array" ref="E479">_xlfn.XLOOKUP(C479,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>生命再生</v>
       </c>
       <c r="F479">
@@ -30704,8 +30704,8 @@
         <f t="shared" si="105"/>
         <v>13</v>
       </c>
-      <c r="E480" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C480,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E480" s="14" t="str" cm="1">
+        <f t="array" ref="E480">_xlfn.XLOOKUP(C480,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>生命再生</v>
       </c>
       <c r="F480">
@@ -30738,8 +30738,8 @@
         <f t="shared" si="105"/>
         <v>14</v>
       </c>
-      <c r="E481" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C481,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E481" s="14" t="str" cm="1">
+        <f t="array" ref="E481">_xlfn.XLOOKUP(C481,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>生命再生</v>
       </c>
       <c r="F481">
@@ -30772,8 +30772,8 @@
         <f t="shared" si="105"/>
         <v>15</v>
       </c>
-      <c r="E482" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C482,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E482" s="14" t="str" cm="1">
+        <f t="array" ref="E482">_xlfn.XLOOKUP(C482,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>生命再生</v>
       </c>
       <c r="F482">
@@ -30806,8 +30806,8 @@
         <f t="shared" si="105"/>
         <v>16</v>
       </c>
-      <c r="E483" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C483,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E483" s="14" t="str" cm="1">
+        <f t="array" ref="E483">_xlfn.XLOOKUP(C483,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>生命再生</v>
       </c>
       <c r="F483">
@@ -30839,8 +30839,8 @@
       <c r="D484" s="14">
         <v>1</v>
       </c>
-      <c r="E484" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C484,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E484" s="14" t="str" cm="1">
+        <f t="array" ref="E484">_xlfn.XLOOKUP(C484,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>鲜血之捷</v>
       </c>
       <c r="F484">
@@ -30869,8 +30869,8 @@
       <c r="D485" s="14">
         <v>2</v>
       </c>
-      <c r="E485" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C485,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E485" s="14" t="str" cm="1">
+        <f t="array" ref="E485">_xlfn.XLOOKUP(C485,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>鲜血之捷</v>
       </c>
       <c r="F485">
@@ -30899,8 +30899,8 @@
       <c r="D486" s="14">
         <v>3</v>
       </c>
-      <c r="E486" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C486,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E486" s="14" t="str" cm="1">
+        <f t="array" ref="E486">_xlfn.XLOOKUP(C486,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>鲜血之捷</v>
       </c>
       <c r="F486">
@@ -30929,8 +30929,8 @@
       <c r="D487" s="14">
         <v>4</v>
       </c>
-      <c r="E487" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C487,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E487" s="14" t="str" cm="1">
+        <f t="array" ref="E487">_xlfn.XLOOKUP(C487,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>鲜血之捷</v>
       </c>
       <c r="F487">
@@ -30959,8 +30959,8 @@
       <c r="D488" s="14">
         <v>5</v>
       </c>
-      <c r="E488" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C488,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E488" s="14" t="str" cm="1">
+        <f t="array" ref="E488">_xlfn.XLOOKUP(C488,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>鲜血之捷</v>
       </c>
       <c r="F488">
@@ -30989,8 +30989,8 @@
       <c r="D489" s="14">
         <v>6</v>
       </c>
-      <c r="E489" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C489,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E489" s="14" t="str" cm="1">
+        <f t="array" ref="E489">_xlfn.XLOOKUP(C489,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>鲜血之捷</v>
       </c>
       <c r="F489">
@@ -31019,8 +31019,8 @@
       <c r="D490" s="14">
         <v>7</v>
       </c>
-      <c r="E490" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C490,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E490" s="14" t="str" cm="1">
+        <f t="array" ref="E490">_xlfn.XLOOKUP(C490,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>鲜血之捷</v>
       </c>
       <c r="F490">
@@ -31049,8 +31049,8 @@
       <c r="D491" s="14">
         <v>8</v>
       </c>
-      <c r="E491" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C491,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E491" s="14" t="str" cm="1">
+        <f t="array" ref="E491">_xlfn.XLOOKUP(C491,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>鲜血之捷</v>
       </c>
       <c r="F491">
@@ -31079,8 +31079,8 @@
       <c r="D492" s="14">
         <v>9</v>
       </c>
-      <c r="E492" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C492,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E492" s="14" t="str" cm="1">
+        <f t="array" ref="E492">_xlfn.XLOOKUP(C492,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>鲜血之捷</v>
       </c>
       <c r="F492">
@@ -31109,8 +31109,8 @@
       <c r="D493" s="14">
         <v>10</v>
       </c>
-      <c r="E493" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C493,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E493" s="14" t="str" cm="1">
+        <f t="array" ref="E493">_xlfn.XLOOKUP(C493,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>鲜血之捷</v>
       </c>
       <c r="F493">
@@ -31139,8 +31139,8 @@
       <c r="D494" s="14">
         <v>11</v>
       </c>
-      <c r="E494" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C494,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E494" s="14" t="str" cm="1">
+        <f t="array" ref="E494">_xlfn.XLOOKUP(C494,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>鲜血之捷</v>
       </c>
       <c r="F494">
@@ -31169,8 +31169,8 @@
       <c r="D495" s="14">
         <v>12</v>
       </c>
-      <c r="E495" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C495,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E495" s="14" t="str" cm="1">
+        <f t="array" ref="E495">_xlfn.XLOOKUP(C495,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>鲜血之捷</v>
       </c>
       <c r="F495">
@@ -31199,8 +31199,8 @@
       <c r="D496" s="14">
         <v>13</v>
       </c>
-      <c r="E496" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C496,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E496" s="14" t="str" cm="1">
+        <f t="array" ref="E496">_xlfn.XLOOKUP(C496,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>鲜血之捷</v>
       </c>
       <c r="F496">
@@ -31229,8 +31229,8 @@
       <c r="D497" s="14">
         <v>14</v>
       </c>
-      <c r="E497" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C497,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E497" s="14" t="str" cm="1">
+        <f t="array" ref="E497">_xlfn.XLOOKUP(C497,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>鲜血之捷</v>
       </c>
       <c r="F497">
@@ -31259,8 +31259,8 @@
       <c r="D498" s="14">
         <v>15</v>
       </c>
-      <c r="E498" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C498,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E498" s="14" t="str" cm="1">
+        <f t="array" ref="E498">_xlfn.XLOOKUP(C498,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>鲜血之捷</v>
       </c>
       <c r="F498">
@@ -31289,8 +31289,8 @@
       <c r="D499" s="14">
         <v>16</v>
       </c>
-      <c r="E499" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C499,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E499" s="14" t="str" cm="1">
+        <f t="array" ref="E499">_xlfn.XLOOKUP(C499,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>鲜血之捷</v>
       </c>
       <c r="F499">
@@ -31319,8 +31319,8 @@
       <c r="D500" s="14">
         <v>1</v>
       </c>
-      <c r="E500" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C500,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E500" s="14" t="str" cm="1">
+        <f t="array" ref="E500">_xlfn.XLOOKUP(C500,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>瘟疫之捷</v>
       </c>
       <c r="F500">
@@ -31352,8 +31352,8 @@
       <c r="D501" s="14">
         <v>2</v>
       </c>
-      <c r="E501" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C501,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E501" s="14" t="str" cm="1">
+        <f t="array" ref="E501">_xlfn.XLOOKUP(C501,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>瘟疫之捷</v>
       </c>
       <c r="F501">
@@ -31385,8 +31385,8 @@
       <c r="D502" s="14">
         <v>3</v>
       </c>
-      <c r="E502" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C502,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E502" s="14" t="str" cm="1">
+        <f t="array" ref="E502">_xlfn.XLOOKUP(C502,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>瘟疫之捷</v>
       </c>
       <c r="F502">
@@ -31418,8 +31418,8 @@
       <c r="D503" s="14">
         <v>4</v>
       </c>
-      <c r="E503" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C503,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E503" s="14" t="str" cm="1">
+        <f t="array" ref="E503">_xlfn.XLOOKUP(C503,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>瘟疫之捷</v>
       </c>
       <c r="F503">
@@ -31451,8 +31451,8 @@
       <c r="D504" s="14">
         <v>5</v>
       </c>
-      <c r="E504" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C504,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E504" s="14" t="str" cm="1">
+        <f t="array" ref="E504">_xlfn.XLOOKUP(C504,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>瘟疫之捷</v>
       </c>
       <c r="F504">
@@ -31484,8 +31484,8 @@
       <c r="D505" s="14">
         <v>6</v>
       </c>
-      <c r="E505" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C505,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E505" s="14" t="str" cm="1">
+        <f t="array" ref="E505">_xlfn.XLOOKUP(C505,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>瘟疫之捷</v>
       </c>
       <c r="F505">
@@ -31517,8 +31517,8 @@
       <c r="D506" s="14">
         <v>7</v>
       </c>
-      <c r="E506" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C506,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E506" s="14" t="str" cm="1">
+        <f t="array" ref="E506">_xlfn.XLOOKUP(C506,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>瘟疫之捷</v>
       </c>
       <c r="F506">
@@ -31550,8 +31550,8 @@
       <c r="D507" s="14">
         <v>8</v>
       </c>
-      <c r="E507" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C507,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E507" s="14" t="str" cm="1">
+        <f t="array" ref="E507">_xlfn.XLOOKUP(C507,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>瘟疫之捷</v>
       </c>
       <c r="F507">
@@ -31583,8 +31583,8 @@
       <c r="D508" s="14">
         <v>9</v>
       </c>
-      <c r="E508" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C508,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E508" s="14" t="str" cm="1">
+        <f t="array" ref="E508">_xlfn.XLOOKUP(C508,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>瘟疫之捷</v>
       </c>
       <c r="F508">
@@ -31616,8 +31616,8 @@
       <c r="D509" s="14">
         <v>10</v>
       </c>
-      <c r="E509" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C509,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E509" s="14" t="str" cm="1">
+        <f t="array" ref="E509">_xlfn.XLOOKUP(C509,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>瘟疫之捷</v>
       </c>
       <c r="F509">
@@ -31649,8 +31649,8 @@
       <c r="D510" s="14">
         <v>11</v>
       </c>
-      <c r="E510" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C510,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E510" s="14" t="str" cm="1">
+        <f t="array" ref="E510">_xlfn.XLOOKUP(C510,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>瘟疫之捷</v>
       </c>
       <c r="F510">
@@ -31682,8 +31682,8 @@
       <c r="D511" s="14">
         <v>12</v>
       </c>
-      <c r="E511" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C511,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E511" s="14" t="str" cm="1">
+        <f t="array" ref="E511">_xlfn.XLOOKUP(C511,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>瘟疫之捷</v>
       </c>
       <c r="F511">
@@ -31715,8 +31715,8 @@
       <c r="D512" s="14">
         <v>13</v>
       </c>
-      <c r="E512" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C512,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E512" s="14" t="str" cm="1">
+        <f t="array" ref="E512">_xlfn.XLOOKUP(C512,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>瘟疫之捷</v>
       </c>
       <c r="F512">
@@ -31748,8 +31748,8 @@
       <c r="D513" s="14">
         <v>14</v>
       </c>
-      <c r="E513" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C513,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E513" s="14" t="str" cm="1">
+        <f t="array" ref="E513">_xlfn.XLOOKUP(C513,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>瘟疫之捷</v>
       </c>
       <c r="F513">
@@ -31781,8 +31781,8 @@
       <c r="D514" s="14">
         <v>15</v>
       </c>
-      <c r="E514" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C514,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E514" s="14" t="str" cm="1">
+        <f t="array" ref="E514">_xlfn.XLOOKUP(C514,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>瘟疫之捷</v>
       </c>
       <c r="F514">
@@ -31814,8 +31814,8 @@
       <c r="D515" s="14">
         <v>16</v>
       </c>
-      <c r="E515" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C515,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E515" s="14" t="str" cm="1">
+        <f t="array" ref="E515">_xlfn.XLOOKUP(C515,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>瘟疫之捷</v>
       </c>
       <c r="F515">
@@ -31847,8 +31847,8 @@
       <c r="D516" s="14">
         <v>1</v>
       </c>
-      <c r="E516" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C516,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E516" s="14" t="str" cm="1">
+        <f t="array" ref="E516">_xlfn.XLOOKUP(C516,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>物理诅咒</v>
       </c>
       <c r="F516">
@@ -31880,8 +31880,8 @@
       <c r="D517" s="14">
         <v>2</v>
       </c>
-      <c r="E517" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C517,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E517" s="14" t="str" cm="1">
+        <f t="array" ref="E517">_xlfn.XLOOKUP(C517,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>物理诅咒</v>
       </c>
       <c r="F517">
@@ -31913,8 +31913,8 @@
       <c r="D518" s="14">
         <v>3</v>
       </c>
-      <c r="E518" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C518,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E518" s="14" t="str" cm="1">
+        <f t="array" ref="E518">_xlfn.XLOOKUP(C518,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>物理诅咒</v>
       </c>
       <c r="F518">
@@ -31946,8 +31946,8 @@
       <c r="D519" s="14">
         <v>4</v>
       </c>
-      <c r="E519" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C519,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E519" s="14" t="str" cm="1">
+        <f t="array" ref="E519">_xlfn.XLOOKUP(C519,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>物理诅咒</v>
       </c>
       <c r="F519">
@@ -31979,8 +31979,8 @@
       <c r="D520" s="14">
         <v>5</v>
       </c>
-      <c r="E520" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C520,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E520" s="14" t="str" cm="1">
+        <f t="array" ref="E520">_xlfn.XLOOKUP(C520,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>物理诅咒</v>
       </c>
       <c r="F520">
@@ -32012,8 +32012,8 @@
       <c r="D521" s="14">
         <v>6</v>
       </c>
-      <c r="E521" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C521,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E521" s="14" t="str" cm="1">
+        <f t="array" ref="E521">_xlfn.XLOOKUP(C521,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>物理诅咒</v>
       </c>
       <c r="F521">
@@ -32045,8 +32045,8 @@
       <c r="D522" s="14">
         <v>7</v>
       </c>
-      <c r="E522" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C522,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E522" s="14" t="str" cm="1">
+        <f t="array" ref="E522">_xlfn.XLOOKUP(C522,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>物理诅咒</v>
       </c>
       <c r="F522">
@@ -32078,8 +32078,8 @@
       <c r="D523" s="14">
         <v>8</v>
       </c>
-      <c r="E523" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C523,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E523" s="14" t="str" cm="1">
+        <f t="array" ref="E523">_xlfn.XLOOKUP(C523,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>物理诅咒</v>
       </c>
       <c r="F523">
@@ -32111,8 +32111,8 @@
       <c r="D524" s="14">
         <v>9</v>
       </c>
-      <c r="E524" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C524,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E524" s="14" t="str" cm="1">
+        <f t="array" ref="E524">_xlfn.XLOOKUP(C524,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>物理诅咒</v>
       </c>
       <c r="F524">
@@ -32144,8 +32144,8 @@
       <c r="D525" s="14">
         <v>10</v>
       </c>
-      <c r="E525" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C525,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E525" s="14" t="str" cm="1">
+        <f t="array" ref="E525">_xlfn.XLOOKUP(C525,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>物理诅咒</v>
       </c>
       <c r="F525">
@@ -32177,8 +32177,8 @@
       <c r="D526" s="14">
         <v>11</v>
       </c>
-      <c r="E526" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C526,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E526" s="14" t="str" cm="1">
+        <f t="array" ref="E526">_xlfn.XLOOKUP(C526,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>物理诅咒</v>
       </c>
       <c r="F526">
@@ -32210,8 +32210,8 @@
       <c r="D527" s="14">
         <v>12</v>
       </c>
-      <c r="E527" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C527,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E527" s="14" t="str" cm="1">
+        <f t="array" ref="E527">_xlfn.XLOOKUP(C527,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>物理诅咒</v>
       </c>
       <c r="F527">
@@ -32243,8 +32243,8 @@
       <c r="D528" s="14">
         <v>13</v>
       </c>
-      <c r="E528" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C528,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E528" s="14" t="str" cm="1">
+        <f t="array" ref="E528">_xlfn.XLOOKUP(C528,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>物理诅咒</v>
       </c>
       <c r="F528">
@@ -32276,8 +32276,8 @@
       <c r="D529" s="14">
         <v>14</v>
       </c>
-      <c r="E529" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C529,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E529" s="14" t="str" cm="1">
+        <f t="array" ref="E529">_xlfn.XLOOKUP(C529,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>物理诅咒</v>
       </c>
       <c r="F529">
@@ -32309,8 +32309,8 @@
       <c r="D530" s="14">
         <v>15</v>
       </c>
-      <c r="E530" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C530,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E530" s="14" t="str" cm="1">
+        <f t="array" ref="E530">_xlfn.XLOOKUP(C530,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>物理诅咒</v>
       </c>
       <c r="F530">
@@ -32342,8 +32342,8 @@
       <c r="D531" s="14">
         <v>16</v>
       </c>
-      <c r="E531" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C531,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E531" s="14" t="str" cm="1">
+        <f t="array" ref="E531">_xlfn.XLOOKUP(C531,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>物理诅咒</v>
       </c>
       <c r="F531">
@@ -32375,8 +32375,8 @@
       <c r="D532" s="14">
         <v>1</v>
       </c>
-      <c r="E532" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C532,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E532" s="14" t="str" cm="1">
+        <f t="array" ref="E532">_xlfn.XLOOKUP(C532,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>火焰诅咒</v>
       </c>
       <c r="F532">
@@ -32408,8 +32408,8 @@
       <c r="D533" s="14">
         <v>2</v>
       </c>
-      <c r="E533" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C533,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E533" s="14" t="str" cm="1">
+        <f t="array" ref="E533">_xlfn.XLOOKUP(C533,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>火焰诅咒</v>
       </c>
       <c r="F533">
@@ -32441,8 +32441,8 @@
       <c r="D534" s="14">
         <v>3</v>
       </c>
-      <c r="E534" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C534,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E534" s="14" t="str" cm="1">
+        <f t="array" ref="E534">_xlfn.XLOOKUP(C534,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>火焰诅咒</v>
       </c>
       <c r="F534">
@@ -32474,8 +32474,8 @@
       <c r="D535" s="14">
         <v>4</v>
       </c>
-      <c r="E535" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C535,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E535" s="14" t="str" cm="1">
+        <f t="array" ref="E535">_xlfn.XLOOKUP(C535,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>火焰诅咒</v>
       </c>
       <c r="F535">
@@ -32507,8 +32507,8 @@
       <c r="D536" s="14">
         <v>5</v>
       </c>
-      <c r="E536" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C536,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E536" s="14" t="str" cm="1">
+        <f t="array" ref="E536">_xlfn.XLOOKUP(C536,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>火焰诅咒</v>
       </c>
       <c r="F536">
@@ -32540,8 +32540,8 @@
       <c r="D537" s="14">
         <v>6</v>
       </c>
-      <c r="E537" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C537,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E537" s="14" t="str" cm="1">
+        <f t="array" ref="E537">_xlfn.XLOOKUP(C537,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>火焰诅咒</v>
       </c>
       <c r="F537">
@@ -32573,8 +32573,8 @@
       <c r="D538" s="14">
         <v>7</v>
       </c>
-      <c r="E538" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C538,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E538" s="14" t="str" cm="1">
+        <f t="array" ref="E538">_xlfn.XLOOKUP(C538,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>火焰诅咒</v>
       </c>
       <c r="F538">
@@ -32606,8 +32606,8 @@
       <c r="D539" s="14">
         <v>8</v>
       </c>
-      <c r="E539" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C539,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E539" s="14" t="str" cm="1">
+        <f t="array" ref="E539">_xlfn.XLOOKUP(C539,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>火焰诅咒</v>
       </c>
       <c r="F539">
@@ -32639,8 +32639,8 @@
       <c r="D540" s="14">
         <v>9</v>
       </c>
-      <c r="E540" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C540,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E540" s="14" t="str" cm="1">
+        <f t="array" ref="E540">_xlfn.XLOOKUP(C540,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>火焰诅咒</v>
       </c>
       <c r="F540">
@@ -32672,8 +32672,8 @@
       <c r="D541" s="14">
         <v>10</v>
       </c>
-      <c r="E541" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C541,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E541" s="14" t="str" cm="1">
+        <f t="array" ref="E541">_xlfn.XLOOKUP(C541,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>火焰诅咒</v>
       </c>
       <c r="F541">
@@ -32705,8 +32705,8 @@
       <c r="D542" s="14">
         <v>11</v>
       </c>
-      <c r="E542" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C542,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E542" s="14" t="str" cm="1">
+        <f t="array" ref="E542">_xlfn.XLOOKUP(C542,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>火焰诅咒</v>
       </c>
       <c r="F542">
@@ -32738,8 +32738,8 @@
       <c r="D543" s="14">
         <v>12</v>
       </c>
-      <c r="E543" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C543,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E543" s="14" t="str" cm="1">
+        <f t="array" ref="E543">_xlfn.XLOOKUP(C543,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>火焰诅咒</v>
       </c>
       <c r="F543">
@@ -32771,8 +32771,8 @@
       <c r="D544" s="14">
         <v>13</v>
       </c>
-      <c r="E544" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C544,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E544" s="14" t="str" cm="1">
+        <f t="array" ref="E544">_xlfn.XLOOKUP(C544,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>火焰诅咒</v>
       </c>
       <c r="F544">
@@ -32804,8 +32804,8 @@
       <c r="D545" s="14">
         <v>14</v>
       </c>
-      <c r="E545" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C545,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E545" s="14" t="str" cm="1">
+        <f t="array" ref="E545">_xlfn.XLOOKUP(C545,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>火焰诅咒</v>
       </c>
       <c r="F545">
@@ -32837,8 +32837,8 @@
       <c r="D546" s="14">
         <v>15</v>
       </c>
-      <c r="E546" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C546,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E546" s="14" t="str" cm="1">
+        <f t="array" ref="E546">_xlfn.XLOOKUP(C546,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>火焰诅咒</v>
       </c>
       <c r="F546">
@@ -32870,8 +32870,8 @@
       <c r="D547" s="14">
         <v>16</v>
       </c>
-      <c r="E547" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C547,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E547" s="14" t="str" cm="1">
+        <f t="array" ref="E547">_xlfn.XLOOKUP(C547,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>火焰诅咒</v>
       </c>
       <c r="F547">
@@ -32903,8 +32903,8 @@
       <c r="D548" s="14">
         <v>1</v>
       </c>
-      <c r="E548" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C548,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E548" s="14" t="str" cm="1">
+        <f t="array" ref="E548">_xlfn.XLOOKUP(C548,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>寒冰诅咒</v>
       </c>
       <c r="F548">
@@ -32936,8 +32936,8 @@
       <c r="D549" s="14">
         <v>2</v>
       </c>
-      <c r="E549" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C549,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E549" s="14" t="str" cm="1">
+        <f t="array" ref="E549">_xlfn.XLOOKUP(C549,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>寒冰诅咒</v>
       </c>
       <c r="F549">
@@ -32969,8 +32969,8 @@
       <c r="D550" s="14">
         <v>3</v>
       </c>
-      <c r="E550" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C550,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E550" s="14" t="str" cm="1">
+        <f t="array" ref="E550">_xlfn.XLOOKUP(C550,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>寒冰诅咒</v>
       </c>
       <c r="F550">
@@ -33002,8 +33002,8 @@
       <c r="D551" s="14">
         <v>4</v>
       </c>
-      <c r="E551" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C551,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E551" s="14" t="str" cm="1">
+        <f t="array" ref="E551">_xlfn.XLOOKUP(C551,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>寒冰诅咒</v>
       </c>
       <c r="F551">
@@ -33035,8 +33035,8 @@
       <c r="D552" s="14">
         <v>5</v>
       </c>
-      <c r="E552" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C552,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E552" s="14" t="str" cm="1">
+        <f t="array" ref="E552">_xlfn.XLOOKUP(C552,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>寒冰诅咒</v>
       </c>
       <c r="F552">
@@ -33068,8 +33068,8 @@
       <c r="D553" s="14">
         <v>6</v>
       </c>
-      <c r="E553" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C553,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E553" s="14" t="str" cm="1">
+        <f t="array" ref="E553">_xlfn.XLOOKUP(C553,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>寒冰诅咒</v>
       </c>
       <c r="F553">
@@ -33101,8 +33101,8 @@
       <c r="D554" s="14">
         <v>7</v>
       </c>
-      <c r="E554" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C554,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E554" s="14" t="str" cm="1">
+        <f t="array" ref="E554">_xlfn.XLOOKUP(C554,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>寒冰诅咒</v>
       </c>
       <c r="F554">
@@ -33134,8 +33134,8 @@
       <c r="D555" s="14">
         <v>8</v>
       </c>
-      <c r="E555" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C555,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E555" s="14" t="str" cm="1">
+        <f t="array" ref="E555">_xlfn.XLOOKUP(C555,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>寒冰诅咒</v>
       </c>
       <c r="F555">
@@ -33167,8 +33167,8 @@
       <c r="D556" s="14">
         <v>9</v>
       </c>
-      <c r="E556" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C556,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E556" s="14" t="str" cm="1">
+        <f t="array" ref="E556">_xlfn.XLOOKUP(C556,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>寒冰诅咒</v>
       </c>
       <c r="F556">
@@ -33200,8 +33200,8 @@
       <c r="D557" s="14">
         <v>10</v>
       </c>
-      <c r="E557" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C557,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E557" s="14" t="str" cm="1">
+        <f t="array" ref="E557">_xlfn.XLOOKUP(C557,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>寒冰诅咒</v>
       </c>
       <c r="F557">
@@ -33233,8 +33233,8 @@
       <c r="D558" s="14">
         <v>11</v>
       </c>
-      <c r="E558" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C558,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E558" s="14" t="str" cm="1">
+        <f t="array" ref="E558">_xlfn.XLOOKUP(C558,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>寒冰诅咒</v>
       </c>
       <c r="F558">
@@ -33266,8 +33266,8 @@
       <c r="D559" s="14">
         <v>12</v>
       </c>
-      <c r="E559" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C559,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E559" s="14" t="str" cm="1">
+        <f t="array" ref="E559">_xlfn.XLOOKUP(C559,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>寒冰诅咒</v>
       </c>
       <c r="F559">
@@ -33299,8 +33299,8 @@
       <c r="D560" s="14">
         <v>13</v>
       </c>
-      <c r="E560" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C560,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E560" s="14" t="str" cm="1">
+        <f t="array" ref="E560">_xlfn.XLOOKUP(C560,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>寒冰诅咒</v>
       </c>
       <c r="F560">
@@ -33332,8 +33332,8 @@
       <c r="D561" s="14">
         <v>14</v>
       </c>
-      <c r="E561" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C561,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E561" s="14" t="str" cm="1">
+        <f t="array" ref="E561">_xlfn.XLOOKUP(C561,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>寒冰诅咒</v>
       </c>
       <c r="F561">
@@ -33365,8 +33365,8 @@
       <c r="D562" s="14">
         <v>15</v>
       </c>
-      <c r="E562" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C562,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E562" s="14" t="str" cm="1">
+        <f t="array" ref="E562">_xlfn.XLOOKUP(C562,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>寒冰诅咒</v>
       </c>
       <c r="F562">
@@ -33398,8 +33398,8 @@
       <c r="D563" s="14">
         <v>16</v>
       </c>
-      <c r="E563" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C563,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E563" s="14" t="str" cm="1">
+        <f t="array" ref="E563">_xlfn.XLOOKUP(C563,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>寒冰诅咒</v>
       </c>
       <c r="F563">
@@ -33431,8 +33431,8 @@
       <c r="D564" s="14">
         <v>1</v>
       </c>
-      <c r="E564" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C564,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E564" s="14" t="str" cm="1">
+        <f t="array" ref="E564">_xlfn.XLOOKUP(C564,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>闪电诅咒</v>
       </c>
       <c r="F564">
@@ -33464,8 +33464,8 @@
       <c r="D565" s="14">
         <v>2</v>
       </c>
-      <c r="E565" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C565,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E565" s="14" t="str" cm="1">
+        <f t="array" ref="E565">_xlfn.XLOOKUP(C565,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>闪电诅咒</v>
       </c>
       <c r="F565">
@@ -33497,8 +33497,8 @@
       <c r="D566" s="14">
         <v>3</v>
       </c>
-      <c r="E566" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C566,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E566" s="14" t="str" cm="1">
+        <f t="array" ref="E566">_xlfn.XLOOKUP(C566,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>闪电诅咒</v>
       </c>
       <c r="F566">
@@ -33530,8 +33530,8 @@
       <c r="D567" s="14">
         <v>4</v>
       </c>
-      <c r="E567" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C567,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E567" s="14" t="str" cm="1">
+        <f t="array" ref="E567">_xlfn.XLOOKUP(C567,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>闪电诅咒</v>
       </c>
       <c r="F567">
@@ -33563,8 +33563,8 @@
       <c r="D568" s="14">
         <v>5</v>
       </c>
-      <c r="E568" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C568,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E568" s="14" t="str" cm="1">
+        <f t="array" ref="E568">_xlfn.XLOOKUP(C568,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>闪电诅咒</v>
       </c>
       <c r="F568">
@@ -33596,8 +33596,8 @@
       <c r="D569" s="14">
         <v>6</v>
       </c>
-      <c r="E569" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C569,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E569" s="14" t="str" cm="1">
+        <f t="array" ref="E569">_xlfn.XLOOKUP(C569,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>闪电诅咒</v>
       </c>
       <c r="F569">
@@ -33629,8 +33629,8 @@
       <c r="D570" s="14">
         <v>7</v>
       </c>
-      <c r="E570" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C570,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E570" s="14" t="str" cm="1">
+        <f t="array" ref="E570">_xlfn.XLOOKUP(C570,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>闪电诅咒</v>
       </c>
       <c r="F570">
@@ -33662,8 +33662,8 @@
       <c r="D571" s="14">
         <v>8</v>
       </c>
-      <c r="E571" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C571,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E571" s="14" t="str" cm="1">
+        <f t="array" ref="E571">_xlfn.XLOOKUP(C571,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>闪电诅咒</v>
       </c>
       <c r="F571">
@@ -33695,8 +33695,8 @@
       <c r="D572" s="14">
         <v>9</v>
       </c>
-      <c r="E572" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C572,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E572" s="14" t="str" cm="1">
+        <f t="array" ref="E572">_xlfn.XLOOKUP(C572,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>闪电诅咒</v>
       </c>
       <c r="F572">
@@ -33728,8 +33728,8 @@
       <c r="D573" s="14">
         <v>10</v>
       </c>
-      <c r="E573" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C573,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E573" s="14" t="str" cm="1">
+        <f t="array" ref="E573">_xlfn.XLOOKUP(C573,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>闪电诅咒</v>
       </c>
       <c r="F573">
@@ -33761,8 +33761,8 @@
       <c r="D574" s="14">
         <v>11</v>
       </c>
-      <c r="E574" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C574,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E574" s="14" t="str" cm="1">
+        <f t="array" ref="E574">_xlfn.XLOOKUP(C574,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>闪电诅咒</v>
       </c>
       <c r="F574">
@@ -33794,8 +33794,8 @@
       <c r="D575" s="14">
         <v>12</v>
       </c>
-      <c r="E575" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C575,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E575" s="14" t="str" cm="1">
+        <f t="array" ref="E575">_xlfn.XLOOKUP(C575,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>闪电诅咒</v>
       </c>
       <c r="F575">
@@ -33827,8 +33827,8 @@
       <c r="D576" s="14">
         <v>13</v>
       </c>
-      <c r="E576" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C576,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E576" s="14" t="str" cm="1">
+        <f t="array" ref="E576">_xlfn.XLOOKUP(C576,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>闪电诅咒</v>
       </c>
       <c r="F576">
@@ -33860,8 +33860,8 @@
       <c r="D577" s="14">
         <v>14</v>
       </c>
-      <c r="E577" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C577,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E577" s="14" t="str" cm="1">
+        <f t="array" ref="E577">_xlfn.XLOOKUP(C577,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>闪电诅咒</v>
       </c>
       <c r="F577">
@@ -33893,8 +33893,8 @@
       <c r="D578" s="14">
         <v>15</v>
       </c>
-      <c r="E578" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C578,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E578" s="14" t="str" cm="1">
+        <f t="array" ref="E578">_xlfn.XLOOKUP(C578,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>闪电诅咒</v>
       </c>
       <c r="F578">
@@ -33926,8 +33926,8 @@
       <c r="D579" s="14">
         <v>16</v>
       </c>
-      <c r="E579" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C579,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E579" s="14" t="str" cm="1">
+        <f t="array" ref="E579">_xlfn.XLOOKUP(C579,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>闪电诅咒</v>
       </c>
       <c r="F579">
@@ -33959,8 +33959,8 @@
       <c r="D580" s="14">
         <v>1</v>
       </c>
-      <c r="E580" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C580,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E580" s="14" t="str" cm="1">
+        <f t="array" ref="E580">_xlfn.XLOOKUP(C580,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>混沌诅咒</v>
       </c>
       <c r="F580">
@@ -33992,8 +33992,8 @@
       <c r="D581" s="14">
         <v>2</v>
       </c>
-      <c r="E581" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C581,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E581" s="14" t="str" cm="1">
+        <f t="array" ref="E581">_xlfn.XLOOKUP(C581,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>混沌诅咒</v>
       </c>
       <c r="F581">
@@ -34025,8 +34025,8 @@
       <c r="D582" s="14">
         <v>3</v>
       </c>
-      <c r="E582" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C582,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E582" s="14" t="str" cm="1">
+        <f t="array" ref="E582">_xlfn.XLOOKUP(C582,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>混沌诅咒</v>
       </c>
       <c r="F582">
@@ -34058,8 +34058,8 @@
       <c r="D583" s="14">
         <v>4</v>
       </c>
-      <c r="E583" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C583,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E583" s="14" t="str" cm="1">
+        <f t="array" ref="E583">_xlfn.XLOOKUP(C583,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>混沌诅咒</v>
       </c>
       <c r="F583">
@@ -34091,8 +34091,8 @@
       <c r="D584" s="14">
         <v>5</v>
       </c>
-      <c r="E584" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C584,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E584" s="14" t="str" cm="1">
+        <f t="array" ref="E584">_xlfn.XLOOKUP(C584,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>混沌诅咒</v>
       </c>
       <c r="F584">
@@ -34124,8 +34124,8 @@
       <c r="D585" s="14">
         <v>6</v>
       </c>
-      <c r="E585" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C585,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E585" s="14" t="str" cm="1">
+        <f t="array" ref="E585">_xlfn.XLOOKUP(C585,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>混沌诅咒</v>
       </c>
       <c r="F585">
@@ -34157,8 +34157,8 @@
       <c r="D586" s="14">
         <v>7</v>
       </c>
-      <c r="E586" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C586,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E586" s="14" t="str" cm="1">
+        <f t="array" ref="E586">_xlfn.XLOOKUP(C586,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>混沌诅咒</v>
       </c>
       <c r="F586">
@@ -34190,8 +34190,8 @@
       <c r="D587" s="14">
         <v>8</v>
       </c>
-      <c r="E587" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C587,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E587" s="14" t="str" cm="1">
+        <f t="array" ref="E587">_xlfn.XLOOKUP(C587,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>混沌诅咒</v>
       </c>
       <c r="F587">
@@ -34223,8 +34223,8 @@
       <c r="D588" s="14">
         <v>9</v>
       </c>
-      <c r="E588" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C588,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E588" s="14" t="str" cm="1">
+        <f t="array" ref="E588">_xlfn.XLOOKUP(C588,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>混沌诅咒</v>
       </c>
       <c r="F588">
@@ -34256,8 +34256,8 @@
       <c r="D589" s="14">
         <v>10</v>
       </c>
-      <c r="E589" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C589,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E589" s="14" t="str" cm="1">
+        <f t="array" ref="E589">_xlfn.XLOOKUP(C589,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>混沌诅咒</v>
       </c>
       <c r="F589">
@@ -34289,8 +34289,8 @@
       <c r="D590" s="14">
         <v>11</v>
       </c>
-      <c r="E590" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C590,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E590" s="14" t="str" cm="1">
+        <f t="array" ref="E590">_xlfn.XLOOKUP(C590,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>混沌诅咒</v>
       </c>
       <c r="F590">
@@ -34322,8 +34322,8 @@
       <c r="D591" s="14">
         <v>12</v>
       </c>
-      <c r="E591" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C591,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E591" s="14" t="str" cm="1">
+        <f t="array" ref="E591">_xlfn.XLOOKUP(C591,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>混沌诅咒</v>
       </c>
       <c r="F591">
@@ -34355,8 +34355,8 @@
       <c r="D592" s="14">
         <v>13</v>
       </c>
-      <c r="E592" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C592,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E592" s="14" t="str" cm="1">
+        <f t="array" ref="E592">_xlfn.XLOOKUP(C592,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>混沌诅咒</v>
       </c>
       <c r="F592">
@@ -34388,8 +34388,8 @@
       <c r="D593" s="14">
         <v>14</v>
       </c>
-      <c r="E593" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C593,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E593" s="14" t="str" cm="1">
+        <f t="array" ref="E593">_xlfn.XLOOKUP(C593,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>混沌诅咒</v>
       </c>
       <c r="F593">
@@ -34421,8 +34421,8 @@
       <c r="D594" s="14">
         <v>15</v>
       </c>
-      <c r="E594" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C594,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E594" s="14" t="str" cm="1">
+        <f t="array" ref="E594">_xlfn.XLOOKUP(C594,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>混沌诅咒</v>
       </c>
       <c r="F594">
@@ -34454,8 +34454,8 @@
       <c r="D595" s="14">
         <v>16</v>
       </c>
-      <c r="E595" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C595,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E595" s="14" t="str" cm="1">
+        <f t="array" ref="E595">_xlfn.XLOOKUP(C595,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>混沌诅咒</v>
       </c>
       <c r="F595">
@@ -34486,8 +34486,8 @@
       <c r="D596" s="14">
         <v>1</v>
       </c>
-      <c r="E596" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C596,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E596" s="14" t="str" cm="1">
+        <f t="array" ref="E596">_xlfn.XLOOKUP(C596,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>附身电球</v>
       </c>
       <c r="F596">
@@ -34519,8 +34519,8 @@
       <c r="D597" s="14">
         <v>2</v>
       </c>
-      <c r="E597" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C597,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E597" s="14" t="str" cm="1">
+        <f t="array" ref="E597">_xlfn.XLOOKUP(C597,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>附身电球</v>
       </c>
       <c r="F597">
@@ -34552,8 +34552,8 @@
       <c r="D598" s="14">
         <v>3</v>
       </c>
-      <c r="E598" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C598,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E598" s="14" t="str" cm="1">
+        <f t="array" ref="E598">_xlfn.XLOOKUP(C598,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>附身电球</v>
       </c>
       <c r="F598">
@@ -34585,8 +34585,8 @@
       <c r="D599" s="14">
         <v>4</v>
       </c>
-      <c r="E599" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C599,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E599" s="14" t="str" cm="1">
+        <f t="array" ref="E599">_xlfn.XLOOKUP(C599,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>附身电球</v>
       </c>
       <c r="F599">
@@ -34618,8 +34618,8 @@
       <c r="D600" s="14">
         <v>5</v>
       </c>
-      <c r="E600" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C600,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E600" s="14" t="str" cm="1">
+        <f t="array" ref="E600">_xlfn.XLOOKUP(C600,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>附身电球</v>
       </c>
       <c r="F600">
@@ -34651,8 +34651,8 @@
       <c r="D601" s="14">
         <v>6</v>
       </c>
-      <c r="E601" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C601,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E601" s="14" t="str" cm="1">
+        <f t="array" ref="E601">_xlfn.XLOOKUP(C601,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>附身电球</v>
       </c>
       <c r="F601">
@@ -34684,8 +34684,8 @@
       <c r="D602" s="14">
         <v>7</v>
       </c>
-      <c r="E602" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C602,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E602" s="14" t="str" cm="1">
+        <f t="array" ref="E602">_xlfn.XLOOKUP(C602,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>附身电球</v>
       </c>
       <c r="F602">
@@ -34717,8 +34717,8 @@
       <c r="D603" s="14">
         <v>8</v>
       </c>
-      <c r="E603" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C603,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E603" s="14" t="str" cm="1">
+        <f t="array" ref="E603">_xlfn.XLOOKUP(C603,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>附身电球</v>
       </c>
       <c r="F603">
@@ -34750,8 +34750,8 @@
       <c r="D604" s="14">
         <v>9</v>
       </c>
-      <c r="E604" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C604,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E604" s="14" t="str" cm="1">
+        <f t="array" ref="E604">_xlfn.XLOOKUP(C604,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>附身电球</v>
       </c>
       <c r="F604">
@@ -34783,8 +34783,8 @@
       <c r="D605" s="14">
         <v>10</v>
       </c>
-      <c r="E605" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C605,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E605" s="14" t="str" cm="1">
+        <f t="array" ref="E605">_xlfn.XLOOKUP(C605,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>附身电球</v>
       </c>
       <c r="F605">
@@ -34816,8 +34816,8 @@
       <c r="D606" s="14">
         <v>11</v>
       </c>
-      <c r="E606" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C606,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E606" s="14" t="str" cm="1">
+        <f t="array" ref="E606">_xlfn.XLOOKUP(C606,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>附身电球</v>
       </c>
       <c r="F606">
@@ -34849,8 +34849,8 @@
       <c r="D607" s="14">
         <v>12</v>
       </c>
-      <c r="E607" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C607,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E607" s="14" t="str" cm="1">
+        <f t="array" ref="E607">_xlfn.XLOOKUP(C607,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>附身电球</v>
       </c>
       <c r="F607">
@@ -34882,8 +34882,8 @@
       <c r="D608" s="14">
         <v>13</v>
       </c>
-      <c r="E608" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C608,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E608" s="14" t="str" cm="1">
+        <f t="array" ref="E608">_xlfn.XLOOKUP(C608,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>附身电球</v>
       </c>
       <c r="F608">
@@ -34915,8 +34915,8 @@
       <c r="D609" s="14">
         <v>14</v>
       </c>
-      <c r="E609" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C609,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E609" s="14" t="str" cm="1">
+        <f t="array" ref="E609">_xlfn.XLOOKUP(C609,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>附身电球</v>
       </c>
       <c r="F609">
@@ -34948,8 +34948,8 @@
       <c r="D610" s="14">
         <v>15</v>
       </c>
-      <c r="E610" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C610,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E610" s="14" t="str" cm="1">
+        <f t="array" ref="E610">_xlfn.XLOOKUP(C610,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>附身电球</v>
       </c>
       <c r="F610">
@@ -34981,8 +34981,8 @@
       <c r="D611" s="14">
         <v>16</v>
       </c>
-      <c r="E611" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C611,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E611" s="14" t="str" cm="1">
+        <f t="array" ref="E611">_xlfn.XLOOKUP(C611,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>附身电球</v>
       </c>
       <c r="F611">
@@ -35013,8 +35013,8 @@
       <c r="D612" s="14">
         <v>1</v>
       </c>
-      <c r="E612" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C612,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E612" s="14" t="str" cm="1">
+        <f t="array" ref="E612">_xlfn.XLOOKUP(C612,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>火焰龙卷</v>
       </c>
       <c r="F612">
@@ -35046,8 +35046,8 @@
       <c r="D613" s="14">
         <v>2</v>
       </c>
-      <c r="E613" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C613,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E613" s="14" t="str" cm="1">
+        <f t="array" ref="E613">_xlfn.XLOOKUP(C613,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>火焰龙卷</v>
       </c>
       <c r="F613">
@@ -35079,8 +35079,8 @@
       <c r="D614" s="14">
         <v>3</v>
       </c>
-      <c r="E614" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C614,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E614" s="14" t="str" cm="1">
+        <f t="array" ref="E614">_xlfn.XLOOKUP(C614,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>火焰龙卷</v>
       </c>
       <c r="F614">
@@ -35112,8 +35112,8 @@
       <c r="D615" s="14">
         <v>4</v>
       </c>
-      <c r="E615" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C615,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E615" s="14" t="str" cm="1">
+        <f t="array" ref="E615">_xlfn.XLOOKUP(C615,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>火焰龙卷</v>
       </c>
       <c r="F615">
@@ -35145,8 +35145,8 @@
       <c r="D616" s="14">
         <v>5</v>
       </c>
-      <c r="E616" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C616,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E616" s="14" t="str" cm="1">
+        <f t="array" ref="E616">_xlfn.XLOOKUP(C616,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>火焰龙卷</v>
       </c>
       <c r="F616">
@@ -35178,8 +35178,8 @@
       <c r="D617" s="14">
         <v>6</v>
       </c>
-      <c r="E617" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C617,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E617" s="14" t="str" cm="1">
+        <f t="array" ref="E617">_xlfn.XLOOKUP(C617,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>火焰龙卷</v>
       </c>
       <c r="F617">
@@ -35211,8 +35211,8 @@
       <c r="D618" s="14">
         <v>7</v>
       </c>
-      <c r="E618" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C618,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E618" s="14" t="str" cm="1">
+        <f t="array" ref="E618">_xlfn.XLOOKUP(C618,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>火焰龙卷</v>
       </c>
       <c r="F618">
@@ -35244,8 +35244,8 @@
       <c r="D619" s="14">
         <v>8</v>
       </c>
-      <c r="E619" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C619,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E619" s="14" t="str" cm="1">
+        <f t="array" ref="E619">_xlfn.XLOOKUP(C619,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>火焰龙卷</v>
       </c>
       <c r="F619">
@@ -35277,8 +35277,8 @@
       <c r="D620" s="14">
         <v>9</v>
       </c>
-      <c r="E620" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C620,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E620" s="14" t="str" cm="1">
+        <f t="array" ref="E620">_xlfn.XLOOKUP(C620,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>火焰龙卷</v>
       </c>
       <c r="F620">
@@ -35310,8 +35310,8 @@
       <c r="D621" s="14">
         <v>10</v>
       </c>
-      <c r="E621" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C621,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E621" s="14" t="str" cm="1">
+        <f t="array" ref="E621">_xlfn.XLOOKUP(C621,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>火焰龙卷</v>
       </c>
       <c r="F621">
@@ -35343,8 +35343,8 @@
       <c r="D622" s="14">
         <v>11</v>
       </c>
-      <c r="E622" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C622,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E622" s="14" t="str" cm="1">
+        <f t="array" ref="E622">_xlfn.XLOOKUP(C622,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>火焰龙卷</v>
       </c>
       <c r="F622">
@@ -35376,8 +35376,8 @@
       <c r="D623" s="14">
         <v>12</v>
       </c>
-      <c r="E623" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C623,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E623" s="14" t="str" cm="1">
+        <f t="array" ref="E623">_xlfn.XLOOKUP(C623,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>火焰龙卷</v>
       </c>
       <c r="F623">
@@ -35409,8 +35409,8 @@
       <c r="D624" s="14">
         <v>13</v>
       </c>
-      <c r="E624" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C624,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E624" s="14" t="str" cm="1">
+        <f t="array" ref="E624">_xlfn.XLOOKUP(C624,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>火焰龙卷</v>
       </c>
       <c r="F624">
@@ -35442,8 +35442,8 @@
       <c r="D625" s="14">
         <v>14</v>
       </c>
-      <c r="E625" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C625,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E625" s="14" t="str" cm="1">
+        <f t="array" ref="E625">_xlfn.XLOOKUP(C625,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>火焰龙卷</v>
       </c>
       <c r="F625">
@@ -35475,8 +35475,8 @@
       <c r="D626" s="14">
         <v>15</v>
       </c>
-      <c r="E626" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C626,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E626" s="14" t="str" cm="1">
+        <f t="array" ref="E626">_xlfn.XLOOKUP(C626,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>火焰龙卷</v>
       </c>
       <c r="F626">
@@ -35508,8 +35508,8 @@
       <c r="D627" s="14">
         <v>16</v>
       </c>
-      <c r="E627" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C627,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E627" s="14" t="str" cm="1">
+        <f t="array" ref="E627">_xlfn.XLOOKUP(C627,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>火焰龙卷</v>
       </c>
       <c r="F627">
@@ -35541,8 +35541,9 @@
       <c r="D628" s="14">
         <v>1</v>
       </c>
-      <c r="E628" s="14" t="s">
-        <v>166</v>
+      <c r="E628" s="14" t="str" cm="1">
+        <f t="array" ref="E628">_xlfn.XLOOKUP(C628,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
+        <v>混沌剑阵</v>
       </c>
       <c r="F628">
         <f t="shared" ref="F628:F659" si="120">D628</f>
@@ -35573,8 +35574,9 @@
       <c r="D629" s="14">
         <v>2</v>
       </c>
-      <c r="E629" s="14" t="s">
-        <v>166</v>
+      <c r="E629" s="14" t="str" cm="1">
+        <f t="array" ref="E629">_xlfn.XLOOKUP(C629,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
+        <v>混沌剑阵</v>
       </c>
       <c r="F629">
         <f t="shared" si="120"/>
@@ -35605,8 +35607,9 @@
       <c r="D630" s="14">
         <v>3</v>
       </c>
-      <c r="E630" s="14" t="s">
-        <v>166</v>
+      <c r="E630" s="14" t="str" cm="1">
+        <f t="array" ref="E630">_xlfn.XLOOKUP(C630,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
+        <v>混沌剑阵</v>
       </c>
       <c r="F630">
         <f t="shared" si="120"/>
@@ -35637,8 +35640,9 @@
       <c r="D631" s="14">
         <v>4</v>
       </c>
-      <c r="E631" s="14" t="s">
-        <v>166</v>
+      <c r="E631" s="14" t="str" cm="1">
+        <f t="array" ref="E631">_xlfn.XLOOKUP(C631,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
+        <v>混沌剑阵</v>
       </c>
       <c r="F631">
         <f t="shared" si="120"/>
@@ -35669,8 +35673,9 @@
       <c r="D632" s="14">
         <v>5</v>
       </c>
-      <c r="E632" s="14" t="s">
-        <v>166</v>
+      <c r="E632" s="14" t="str" cm="1">
+        <f t="array" ref="E632">_xlfn.XLOOKUP(C632,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
+        <v>混沌剑阵</v>
       </c>
       <c r="F632">
         <f t="shared" si="120"/>
@@ -35701,8 +35706,9 @@
       <c r="D633" s="14">
         <v>6</v>
       </c>
-      <c r="E633" s="14" t="s">
-        <v>166</v>
+      <c r="E633" s="14" t="str" cm="1">
+        <f t="array" ref="E633">_xlfn.XLOOKUP(C633,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
+        <v>混沌剑阵</v>
       </c>
       <c r="F633">
         <f t="shared" si="120"/>
@@ -35733,8 +35739,9 @@
       <c r="D634" s="14">
         <v>7</v>
       </c>
-      <c r="E634" s="14" t="s">
-        <v>166</v>
+      <c r="E634" s="14" t="str" cm="1">
+        <f t="array" ref="E634">_xlfn.XLOOKUP(C634,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
+        <v>混沌剑阵</v>
       </c>
       <c r="F634">
         <f t="shared" si="120"/>
@@ -35765,8 +35772,9 @@
       <c r="D635" s="14">
         <v>8</v>
       </c>
-      <c r="E635" s="14" t="s">
-        <v>166</v>
+      <c r="E635" s="14" t="str" cm="1">
+        <f t="array" ref="E635">_xlfn.XLOOKUP(C635,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
+        <v>混沌剑阵</v>
       </c>
       <c r="F635">
         <f t="shared" si="120"/>
@@ -35797,8 +35805,9 @@
       <c r="D636" s="14">
         <v>9</v>
       </c>
-      <c r="E636" s="14" t="s">
-        <v>166</v>
+      <c r="E636" s="14" t="str" cm="1">
+        <f t="array" ref="E636">_xlfn.XLOOKUP(C636,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
+        <v>混沌剑阵</v>
       </c>
       <c r="F636">
         <f t="shared" si="120"/>
@@ -35829,8 +35838,9 @@
       <c r="D637" s="14">
         <v>10</v>
       </c>
-      <c r="E637" s="14" t="s">
-        <v>166</v>
+      <c r="E637" s="14" t="str" cm="1">
+        <f t="array" ref="E637">_xlfn.XLOOKUP(C637,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
+        <v>混沌剑阵</v>
       </c>
       <c r="F637">
         <f t="shared" si="120"/>
@@ -35861,8 +35871,9 @@
       <c r="D638" s="14">
         <v>11</v>
       </c>
-      <c r="E638" s="14" t="s">
-        <v>166</v>
+      <c r="E638" s="14" t="str" cm="1">
+        <f t="array" ref="E638">_xlfn.XLOOKUP(C638,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
+        <v>混沌剑阵</v>
       </c>
       <c r="F638">
         <f t="shared" si="120"/>
@@ -35893,8 +35904,9 @@
       <c r="D639" s="14">
         <v>12</v>
       </c>
-      <c r="E639" s="14" t="s">
-        <v>166</v>
+      <c r="E639" s="14" t="str" cm="1">
+        <f t="array" ref="E639">_xlfn.XLOOKUP(C639,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
+        <v>混沌剑阵</v>
       </c>
       <c r="F639">
         <f t="shared" si="120"/>
@@ -35925,8 +35937,9 @@
       <c r="D640" s="14">
         <v>13</v>
       </c>
-      <c r="E640" s="14" t="s">
-        <v>166</v>
+      <c r="E640" s="14" t="str" cm="1">
+        <f t="array" ref="E640">_xlfn.XLOOKUP(C640,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
+        <v>混沌剑阵</v>
       </c>
       <c r="F640">
         <f t="shared" si="120"/>
@@ -35957,8 +35970,9 @@
       <c r="D641" s="14">
         <v>14</v>
       </c>
-      <c r="E641" s="14" t="s">
-        <v>166</v>
+      <c r="E641" s="14" t="str" cm="1">
+        <f t="array" ref="E641">_xlfn.XLOOKUP(C641,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
+        <v>混沌剑阵</v>
       </c>
       <c r="F641">
         <f t="shared" si="120"/>
@@ -35989,8 +36003,9 @@
       <c r="D642" s="14">
         <v>15</v>
       </c>
-      <c r="E642" s="14" t="s">
-        <v>166</v>
+      <c r="E642" s="14" t="str" cm="1">
+        <f t="array" ref="E642">_xlfn.XLOOKUP(C642,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
+        <v>混沌剑阵</v>
       </c>
       <c r="F642">
         <f t="shared" si="120"/>
@@ -36021,8 +36036,9 @@
       <c r="D643" s="14">
         <v>16</v>
       </c>
-      <c r="E643" s="14" t="s">
-        <v>166</v>
+      <c r="E643" s="14" t="str" cm="1">
+        <f t="array" ref="E643">_xlfn.XLOOKUP(C643,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
+        <v>混沌剑阵</v>
       </c>
       <c r="F643">
         <f t="shared" si="120"/>
@@ -36053,8 +36069,8 @@
       <c r="D644" s="14">
         <v>1</v>
       </c>
-      <c r="E644" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C644,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E644" s="14" t="str" cm="1">
+        <f t="array" ref="E644">_xlfn.XLOOKUP(C644,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>我即闪电</v>
       </c>
       <c r="F644">
@@ -36086,8 +36102,8 @@
       <c r="D645" s="14">
         <v>2</v>
       </c>
-      <c r="E645" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C645,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E645" s="14" t="str" cm="1">
+        <f t="array" ref="E645">_xlfn.XLOOKUP(C645,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>我即闪电</v>
       </c>
       <c r="F645">
@@ -36119,8 +36135,8 @@
       <c r="D646" s="14">
         <v>3</v>
       </c>
-      <c r="E646" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C646,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E646" s="14" t="str" cm="1">
+        <f t="array" ref="E646">_xlfn.XLOOKUP(C646,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>我即闪电</v>
       </c>
       <c r="F646">
@@ -36152,8 +36168,8 @@
       <c r="D647" s="14">
         <v>4</v>
       </c>
-      <c r="E647" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C647,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E647" s="14" t="str" cm="1">
+        <f t="array" ref="E647">_xlfn.XLOOKUP(C647,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>我即闪电</v>
       </c>
       <c r="F647">
@@ -36185,8 +36201,8 @@
       <c r="D648" s="14">
         <v>5</v>
       </c>
-      <c r="E648" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C648,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E648" s="14" t="str" cm="1">
+        <f t="array" ref="E648">_xlfn.XLOOKUP(C648,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>我即闪电</v>
       </c>
       <c r="F648">
@@ -36218,8 +36234,8 @@
       <c r="D649" s="14">
         <v>6</v>
       </c>
-      <c r="E649" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C649,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E649" s="14" t="str" cm="1">
+        <f t="array" ref="E649">_xlfn.XLOOKUP(C649,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>我即闪电</v>
       </c>
       <c r="F649">
@@ -36251,8 +36267,8 @@
       <c r="D650" s="14">
         <v>7</v>
       </c>
-      <c r="E650" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C650,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E650" s="14" t="str" cm="1">
+        <f t="array" ref="E650">_xlfn.XLOOKUP(C650,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>我即闪电</v>
       </c>
       <c r="F650">
@@ -36284,8 +36300,8 @@
       <c r="D651" s="14">
         <v>8</v>
       </c>
-      <c r="E651" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C651,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E651" s="14" t="str" cm="1">
+        <f t="array" ref="E651">_xlfn.XLOOKUP(C651,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>我即闪电</v>
       </c>
       <c r="F651">
@@ -36317,8 +36333,8 @@
       <c r="D652" s="14">
         <v>9</v>
       </c>
-      <c r="E652" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C652,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E652" s="14" t="str" cm="1">
+        <f t="array" ref="E652">_xlfn.XLOOKUP(C652,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>我即闪电</v>
       </c>
       <c r="F652">
@@ -36350,8 +36366,8 @@
       <c r="D653" s="14">
         <v>10</v>
       </c>
-      <c r="E653" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C653,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E653" s="14" t="str" cm="1">
+        <f t="array" ref="E653">_xlfn.XLOOKUP(C653,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>我即闪电</v>
       </c>
       <c r="F653">
@@ -36383,8 +36399,8 @@
       <c r="D654" s="14">
         <v>11</v>
       </c>
-      <c r="E654" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C654,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E654" s="14" t="str" cm="1">
+        <f t="array" ref="E654">_xlfn.XLOOKUP(C654,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>我即闪电</v>
       </c>
       <c r="F654">
@@ -36416,8 +36432,8 @@
       <c r="D655" s="14">
         <v>12</v>
       </c>
-      <c r="E655" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C655,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E655" s="14" t="str" cm="1">
+        <f t="array" ref="E655">_xlfn.XLOOKUP(C655,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>我即闪电</v>
       </c>
       <c r="F655">
@@ -36449,8 +36465,8 @@
       <c r="D656" s="14">
         <v>13</v>
       </c>
-      <c r="E656" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C656,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E656" s="14" t="str" cm="1">
+        <f t="array" ref="E656">_xlfn.XLOOKUP(C656,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>我即闪电</v>
       </c>
       <c r="F656">
@@ -36482,8 +36498,8 @@
       <c r="D657" s="14">
         <v>14</v>
       </c>
-      <c r="E657" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C657,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E657" s="14" t="str" cm="1">
+        <f t="array" ref="E657">_xlfn.XLOOKUP(C657,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>我即闪电</v>
       </c>
       <c r="F657">
@@ -36515,8 +36531,8 @@
       <c r="D658" s="14">
         <v>15</v>
       </c>
-      <c r="E658" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C658,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E658" s="14" t="str" cm="1">
+        <f t="array" ref="E658">_xlfn.XLOOKUP(C658,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>我即闪电</v>
       </c>
       <c r="F658">
@@ -36548,8 +36564,8 @@
       <c r="D659" s="14">
         <v>16</v>
       </c>
-      <c r="E659" s="14" t="str">
-        <f>_xlfn.XLOOKUP(C659,SkillActive!A:A,SkillActive!B:B,,0)</f>
+      <c r="E659" s="14" t="str" cm="1">
+        <f t="array" ref="E659">_xlfn.XLOOKUP(C659,SkillActive!A:A,INDEX(SkillActive!A:AA,0,MATCH("name",SkillActive!$2:$2,0)),,0)</f>
         <v>我即闪电</v>
       </c>
       <c r="F659">

--- a/data-sources/技能养成相关.xlsx
+++ b/data-sources/技能养成相关.xlsx
@@ -5,11 +5,11 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\古荒遗迹2策划\1.表格目录\XLS表格\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\策划\1.表格目录\XLS表格\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255" activeTab="3"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="SkillActive" sheetId="1" r:id="rId1"/>
@@ -768,7 +768,7 @@
     <t>linshi/9</t>
   </si>
   <si>
-    <t>对自身一定范围内的敌人造成一次{0}</t>
+    <t>对自身一定范围内的敌人造成一次{0}\n当该技能100%物理伤害转火焰伤害时，还会释放火焰旋龙\n当该技能100%物理伤害转闪电伤害时，还会释放闪电旋龙\n当该技能100%物理伤害转冰冷伤害时，还会释放冰冷旋龙</t>
   </si>
   <si>
     <t>[[1111000040]]</t>
@@ -5381,60 +5381,60 @@
     <t>240|-250</t>
   </si>
   <si>
+    <t>偶尔漏电</t>
+  </si>
+  <si>
+    <t>攻击伤害击中时，有10%的几率触发10级[电圈]</t>
+  </si>
+  <si>
+    <t>1003002|1003010</t>
+  </si>
+  <si>
+    <t>0|-100</t>
+  </si>
+  <si>
+    <t>我麻了</t>
+  </si>
+  <si>
+    <t>对自身造成感电效果，攻击速度/施法速度提高50%</t>
+  </si>
+  <si>
+    <t>剑客1-天赋6</t>
+  </si>
+  <si>
+    <t>1003002|1003008</t>
+  </si>
+  <si>
+    <t>-240|-100</t>
+  </si>
+  <si>
+    <t>速度与激情</t>
+  </si>
+  <si>
+    <t>剑客1-天赋8</t>
+  </si>
+  <si>
+    <t>-240|150</t>
+  </si>
+  <si>
+    <t>脚底抹油</t>
+  </si>
+  <si>
+    <t>移动速度增加大于100%时，受到伤害额外减少5%</t>
+  </si>
+  <si>
+    <t>剑客1-天赋10</t>
+  </si>
+  <si>
+    <t>0|150</t>
+  </si>
+  <si>
     <t>唯快不破</t>
   </si>
   <si>
     <t>第一个技能获得攻击速度额外提高20%</t>
   </si>
   <si>
-    <t>1003002|1003010</t>
-  </si>
-  <si>
-    <t>0|-100</t>
-  </si>
-  <si>
-    <t>我麻了</t>
-  </si>
-  <si>
-    <t>对自身造成感电效果，攻击速度/施法速度提高50%</t>
-  </si>
-  <si>
-    <t>剑客1-天赋6</t>
-  </si>
-  <si>
-    <t>1003002|1003008</t>
-  </si>
-  <si>
-    <t>-240|-100</t>
-  </si>
-  <si>
-    <t>速度与激情</t>
-  </si>
-  <si>
-    <t>剑客1-天赋8</t>
-  </si>
-  <si>
-    <t>-240|150</t>
-  </si>
-  <si>
-    <t>脚底抹油</t>
-  </si>
-  <si>
-    <t>移动速度增加大于100%时，受到伤害额外减少5%</t>
-  </si>
-  <si>
-    <t>剑客1-天赋10</t>
-  </si>
-  <si>
-    <t>0|150</t>
-  </si>
-  <si>
-    <t>偶尔漏电</t>
-  </si>
-  <si>
-    <t>攻击伤害击中时，有10%的几率触发10级[电圈]</t>
-  </si>
-  <si>
     <t>剑客1-天赋12</t>
   </si>
   <si>
@@ -6509,22 +6509,22 @@
     <t>[[10033,0.06]]</t>
   </si>
   <si>
-    <t>生命恢复速度增加</t>
+    <t>生命恢复率增加</t>
   </si>
   <si>
     <t>talent/common_1/zhiliaosudu</t>
   </si>
   <si>
-    <t>生命恢复速度增加0.2%</t>
+    <t>生命恢复率增加0.2%</t>
   </si>
   <si>
     <t>[[10004,0.002]]</t>
   </si>
   <si>
-    <t>魔力恢复速度增加</t>
-  </si>
-  <si>
-    <t>魔力恢复速度增加0.2%</t>
+    <t>魔力恢复率增加</t>
+  </si>
+  <si>
+    <t>魔力恢复率增加0.2%</t>
   </si>
   <si>
     <t>[[10006,0.002]]</t>
@@ -6980,7 +6980,7 @@
     <t>抗性盘1-11</t>
   </si>
   <si>
-    <t>抗性注能持续时间提高{0}</t>
+    <t>抗性注能持续时间提高1%</t>
   </si>
   <si>
     <t>抗性盘2-1</t>
@@ -7576,14 +7576,14 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="10"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -9224,7 +9224,8 @@
       <c r="I4" s="69" t="s">
         <v>43</v>
       </c>
-      <c r="K4" s="49">
+      <c r="K4" s="49" cm="1">
+        <f t="array" ref="K4">_xlfn.SWITCH(E4,1,0,2,7,3,10,4,15,5,50)</f>
         <v>0</v>
       </c>
       <c r="L4" s="49" t="s">
@@ -9246,7 +9247,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" ht="17.25" spans="1:18">
+    <row r="5" ht="40.5" spans="1:18">
       <c r="A5" s="49">
         <v>100002</v>
       </c>
@@ -9271,7 +9272,8 @@
       <c r="I5" s="69" t="s">
         <v>43</v>
       </c>
-      <c r="K5" s="49">
+      <c r="K5" s="49" cm="1">
+        <f t="array" ref="K5">_xlfn.SWITCH(E5,1,0,2,7,3,10,4,15,5,50)</f>
         <v>0</v>
       </c>
       <c r="L5" s="49" t="s">
@@ -9318,7 +9320,8 @@
       <c r="I6" s="69" t="s">
         <v>43</v>
       </c>
-      <c r="K6" s="49">
+      <c r="K6" s="49" cm="1">
+        <f t="array" ref="K6">_xlfn.SWITCH(E6,1,0,2,7,3,10,4,15,5,50)</f>
         <v>0</v>
       </c>
       <c r="L6" s="49" t="s">
@@ -9365,7 +9368,8 @@
       <c r="I7" s="69" t="s">
         <v>58</v>
       </c>
-      <c r="K7" s="49">
+      <c r="K7" s="49" cm="1">
+        <f t="array" ref="K7">_xlfn.SWITCH(E7,1,0,2,7,3,10,4,15,5,50)</f>
         <v>0</v>
       </c>
       <c r="L7" s="49" t="s">
@@ -9414,7 +9418,7 @@
         <v>58</v>
       </c>
       <c r="K8" s="49" cm="1">
-        <f t="array" ref="K8">_xlfn.SWITCH(E8,1,0,2,7,3,15,4,25,5,50)</f>
+        <f t="array" ref="K8">_xlfn.SWITCH(E8,1,0,2,7,3,10,4,15,5,50)</f>
         <v>0</v>
       </c>
       <c r="L8" s="49" t="s">
@@ -9463,7 +9467,7 @@
         <v>58</v>
       </c>
       <c r="K9" s="49" cm="1">
-        <f t="array" ref="K9">_xlfn.SWITCH(E9,1,0,2,7,3,15,4,25,5,50)</f>
+        <f t="array" ref="K9">_xlfn.SWITCH(E9,1,0,2,7,3,10,4,15,5,50)</f>
         <v>0</v>
       </c>
       <c r="L9" s="49" t="s">
@@ -9512,7 +9516,7 @@
         <v>58</v>
       </c>
       <c r="K10" s="49" cm="1">
-        <f t="array" ref="K10">_xlfn.SWITCH(E10,1,0,2,7,3,15,4,25,5,50)</f>
+        <f t="array" ref="K10">_xlfn.SWITCH(E10,1,0,2,7,3,10,4,15,5,50)</f>
         <v>0</v>
       </c>
       <c r="L10" s="49" t="s">
@@ -9561,7 +9565,7 @@
         <v>58</v>
       </c>
       <c r="K11" s="49" cm="1">
-        <f t="array" ref="K11">_xlfn.SWITCH(E11,1,0,2,7,3,15,4,25,5,50)</f>
+        <f t="array" ref="K11">_xlfn.SWITCH(E11,1,0,2,7,3,10,4,15,5,50)</f>
         <v>0</v>
       </c>
       <c r="L11" s="49" t="s">
@@ -9610,7 +9614,7 @@
         <v>58</v>
       </c>
       <c r="K12" s="49" cm="1">
-        <f t="array" ref="K12">_xlfn.SWITCH(E12,1,0,2,7,3,15,4,25,5,50)</f>
+        <f t="array" ref="K12">_xlfn.SWITCH(E12,1,0,2,7,3,10,4,15,5,50)</f>
         <v>0</v>
       </c>
       <c r="L12" s="49" t="s">
@@ -9659,7 +9663,7 @@
         <v>58</v>
       </c>
       <c r="K13" s="49" cm="1">
-        <f t="array" ref="K13">_xlfn.SWITCH(E13,1,0,2,7,3,15,4,25,5,50)</f>
+        <f t="array" ref="K13">_xlfn.SWITCH(E13,1,0,2,7,3,10,4,15,5,50)</f>
         <v>0</v>
       </c>
       <c r="L13" s="49" t="s">
@@ -9708,7 +9712,7 @@
         <v>58</v>
       </c>
       <c r="K14" s="49" cm="1">
-        <f t="array" ref="K14">_xlfn.SWITCH(E14,1,0,2,7,3,15,4,25,5,50)</f>
+        <f t="array" ref="K14">_xlfn.SWITCH(E14,1,0,2,7,3,10,4,15,5,50)</f>
         <v>7</v>
       </c>
       <c r="L14" s="49" t="s">
@@ -9760,7 +9764,7 @@
         <v>58</v>
       </c>
       <c r="K15" s="49" cm="1">
-        <f t="array" ref="K15">_xlfn.SWITCH(E15,1,0,2,7,3,15,4,25,5,50)</f>
+        <f t="array" ref="K15">_xlfn.SWITCH(E15,1,0,2,7,3,10,4,15,5,50)</f>
         <v>7</v>
       </c>
       <c r="L15" s="49" t="s">
@@ -9812,7 +9816,7 @@
         <v>58</v>
       </c>
       <c r="K16" s="49" cm="1">
-        <f t="array" ref="K16">_xlfn.SWITCH(E16,1,0,2,7,3,15,4,25,5,50)</f>
+        <f t="array" ref="K16">_xlfn.SWITCH(E16,1,0,2,7,3,10,4,15,5,50)</f>
         <v>7</v>
       </c>
       <c r="L16" s="49" t="s">
@@ -9861,7 +9865,7 @@
         <v>58</v>
       </c>
       <c r="K17" s="49" cm="1">
-        <f t="array" ref="K17">_xlfn.SWITCH(E17,1,0,2,7,3,15,4,25,5,50)</f>
+        <f t="array" ref="K17">_xlfn.SWITCH(E17,1,0,2,7,3,10,4,15,5,50)</f>
         <v>7</v>
       </c>
       <c r="L17" s="49" t="s">
@@ -9906,8 +9910,8 @@
       <c r="I18" s="69" t="s">
         <v>58</v>
       </c>
-      <c r="K18" s="65" cm="1">
-        <f t="array" ref="K18">_xlfn.SWITCH(E18,1,0,2,7,3,15,4,25,5,50)</f>
+      <c r="K18" s="49" cm="1">
+        <f t="array" ref="K18">_xlfn.SWITCH(E18,1,0,2,7,3,10,4,15,5,50)</f>
         <v>7</v>
       </c>
       <c r="M18" s="72" t="s">
@@ -9949,7 +9953,7 @@
         <v>58</v>
       </c>
       <c r="K19" s="49" cm="1">
-        <f t="array" ref="K19">_xlfn.SWITCH(E19,1,0,2,7,3,15,4,25,5,50)</f>
+        <f t="array" ref="K19">_xlfn.SWITCH(E19,1,0,2,7,3,10,4,15,5,50)</f>
         <v>7</v>
       </c>
       <c r="L19" s="49" t="s">
@@ -9999,8 +10003,9 @@
       <c r="I20" s="69" t="s">
         <v>58</v>
       </c>
-      <c r="K20" s="49">
-        <v>15</v>
+      <c r="K20" s="49" cm="1">
+        <f t="array" ref="K20">_xlfn.SWITCH(E20,1,0,2,7,3,10,4,15,5,50)</f>
+        <v>10</v>
       </c>
       <c r="L20" s="49" t="s">
         <v>108</v>
@@ -10048,8 +10053,8 @@
         <v>58</v>
       </c>
       <c r="K21" s="49" cm="1">
-        <f t="array" ref="K21">_xlfn.SWITCH(E21,1,0,2,7,3,15,4,25,5,50)</f>
-        <v>15</v>
+        <f t="array" ref="K21">_xlfn.SWITCH(E21,1,0,2,7,3,10,4,15,5,50)</f>
+        <v>10</v>
       </c>
       <c r="L21" s="49" t="s">
         <v>112</v>
@@ -10094,8 +10099,8 @@
         <v>58</v>
       </c>
       <c r="K22" s="49" cm="1">
-        <f t="array" ref="K22">_xlfn.SWITCH(E22,1,0,2,7,3,15,4,25,5,50)</f>
-        <v>15</v>
+        <f t="array" ref="K22">_xlfn.SWITCH(E22,1,0,2,7,3,10,4,15,5,50)</f>
+        <v>10</v>
       </c>
       <c r="L22" s="49" t="s">
         <v>115</v>
@@ -10146,7 +10151,7 @@
         <v>58</v>
       </c>
       <c r="K23" s="49" cm="1">
-        <f t="array" ref="K23">_xlfn.SWITCH(E23,1,0,2,7,3,15,4,25,5,50)</f>
+        <f t="array" ref="K23">_xlfn.SWITCH(E23,1,0,2,7,3,10,4,15,5,50)</f>
         <v>7</v>
       </c>
       <c r="L23" s="49" t="s">
@@ -10198,8 +10203,8 @@
         <v>58</v>
       </c>
       <c r="K24" s="49" cm="1">
-        <f t="array" ref="K24">_xlfn.SWITCH(E24,1,0,2,7,3,15,4,25,5,50)</f>
-        <v>25</v>
+        <f t="array" ref="K24">_xlfn.SWITCH(E24,1,0,2,7,3,10,4,15,5,50)</f>
+        <v>15</v>
       </c>
       <c r="L24" s="49" t="s">
         <v>123</v>
@@ -10242,9 +10247,9 @@
       <c r="I25" s="69" t="s">
         <v>58</v>
       </c>
-      <c r="K25" s="66" cm="1">
-        <f t="array" ref="K25">_xlfn.SWITCH(E25,1,0,2,7,3,15,4,25,5,50)</f>
-        <v>25</v>
+      <c r="K25" s="49" cm="1">
+        <f t="array" ref="K25">_xlfn.SWITCH(E25,1,0,2,7,3,10,4,15,5,50)</f>
+        <v>15</v>
       </c>
       <c r="M25" s="72" t="s">
         <v>127</v>
@@ -10285,9 +10290,9 @@
       <c r="I26" s="69" t="s">
         <v>58</v>
       </c>
-      <c r="K26" s="65" cm="1">
-        <f t="array" ref="K26">_xlfn.SWITCH(E26,1,0,2,7,3,15,4,25,5,50)</f>
-        <v>25</v>
+      <c r="K26" s="49" cm="1">
+        <f t="array" ref="K26">_xlfn.SWITCH(E26,1,0,2,7,3,10,4,15,5,50)</f>
+        <v>15</v>
       </c>
       <c r="M26" s="73" t="s">
         <v>129</v>
@@ -10325,8 +10330,8 @@
       <c r="I27" s="69" t="s">
         <v>58</v>
       </c>
-      <c r="K27" s="66" cm="1">
-        <f t="array" ref="K27">_xlfn.SWITCH(E27,1,0,2,7,3,15,4,25,5,50)</f>
+      <c r="K27" s="49" cm="1">
+        <f t="array" ref="K27">_xlfn.SWITCH(E27,1,0,2,7,3,10,4,15,5,50)</f>
         <v>50</v>
       </c>
       <c r="L27" s="49" t="s">
@@ -10368,8 +10373,8 @@
       <c r="I28" s="69" t="s">
         <v>58</v>
       </c>
-      <c r="K28" s="66" cm="1">
-        <f t="array" ref="K28">_xlfn.SWITCH(E28,1,0,2,7,3,15,4,25,5,50)</f>
+      <c r="K28" s="49" cm="1">
+        <f t="array" ref="K28">_xlfn.SWITCH(E28,1,0,2,7,3,10,4,15,5,50)</f>
         <v>50</v>
       </c>
       <c r="M28" s="72" t="s">
@@ -10402,7 +10407,7 @@
         <v>0</v>
       </c>
       <c r="E29" s="49">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G29" s="49">
         <v>2114000020</v>
@@ -10415,8 +10420,8 @@
         <v>58</v>
       </c>
       <c r="K29" s="49" cm="1">
-        <f t="array" ref="K29">_xlfn.SWITCH(E29,1,0,2,7,3,15,4,25,5,50)</f>
-        <v>50</v>
+        <f t="array" ref="K29">_xlfn.SWITCH(E29,1,0,2,7,3,10,4,15,5,50)</f>
+        <v>15</v>
       </c>
       <c r="L29" s="49" t="s">
         <v>131</v>
@@ -10445,7 +10450,7 @@
         <v>0</v>
       </c>
       <c r="E30" s="49">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G30" s="49">
         <v>2140000040</v>
@@ -10458,8 +10463,8 @@
         <v>58</v>
       </c>
       <c r="K30" s="49" cm="1">
-        <f t="array" ref="K30">_xlfn.SWITCH(E30,1,0,2,7,3,15,4,25,5,50)</f>
-        <v>50</v>
+        <f t="array" ref="K30">_xlfn.SWITCH(E30,1,0,2,7,3,10,4,15,5,50)</f>
+        <v>15</v>
       </c>
       <c r="L30" s="49" t="s">
         <v>135</v>
@@ -10488,7 +10493,7 @@
         <v>0</v>
       </c>
       <c r="E31" s="49">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G31" s="49">
         <v>2140000050</v>
@@ -10501,8 +10506,8 @@
         <v>58</v>
       </c>
       <c r="K31" s="49" cm="1">
-        <f t="array" ref="K31">_xlfn.SWITCH(E31,1,0,2,7,3,15,4,25,5,50)</f>
-        <v>50</v>
+        <f t="array" ref="K31">_xlfn.SWITCH(E31,1,0,2,7,3,10,4,15,5,50)</f>
+        <v>15</v>
       </c>
       <c r="L31" s="49" t="s">
         <v>137</v>
@@ -10531,7 +10536,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="49">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G32" s="49">
         <v>2140000060</v>
@@ -10544,8 +10549,8 @@
         <v>58</v>
       </c>
       <c r="K32" s="49" cm="1">
-        <f t="array" ref="K32">_xlfn.SWITCH(E32,1,0,2,7,3,15,4,25,5,50)</f>
-        <v>50</v>
+        <f t="array" ref="K32">_xlfn.SWITCH(E32,1,0,2,7,3,10,4,15,5,50)</f>
+        <v>15</v>
       </c>
       <c r="L32" s="49" t="s">
         <v>139</v>
@@ -10574,7 +10579,7 @@
         <v>0</v>
       </c>
       <c r="E33" s="49">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G33" s="49">
         <v>2140000070</v>
@@ -10587,8 +10592,8 @@
         <v>58</v>
       </c>
       <c r="K33" s="49" cm="1">
-        <f t="array" ref="K33">_xlfn.SWITCH(E33,1,0,2,7,3,15,4,25,5,50)</f>
-        <v>50</v>
+        <f t="array" ref="K33">_xlfn.SWITCH(E33,1,0,2,7,3,10,4,15,5,50)</f>
+        <v>15</v>
       </c>
       <c r="L33" s="49" t="s">
         <v>141</v>
@@ -10630,7 +10635,7 @@
         <v>58</v>
       </c>
       <c r="K34" s="49" cm="1">
-        <f t="array" ref="K34">_xlfn.SWITCH(E34,1,0,2,7,3,15,4,25,5,50)</f>
+        <f t="array" ref="K34">_xlfn.SWITCH(E34,1,0,2,7,3,10,4,15,5,50)</f>
         <v>7</v>
       </c>
       <c r="L34" s="49" t="s">
@@ -10673,7 +10678,7 @@
         <v>58</v>
       </c>
       <c r="K35" s="49" cm="1">
-        <f t="array" ref="K35">_xlfn.SWITCH(E35,1,0,2,7,3,15,4,25,5,50)</f>
+        <f t="array" ref="K35">_xlfn.SWITCH(E35,1,0,2,7,3,10,4,15,5,50)</f>
         <v>7</v>
       </c>
       <c r="L35" s="49" t="s">
@@ -10716,8 +10721,8 @@
         <v>58</v>
       </c>
       <c r="K36" s="49" cm="1">
-        <f t="array" ref="K36">_xlfn.SWITCH(E36,1,0,2,7,3,15,4,25,5,50)</f>
-        <v>15</v>
+        <f t="array" ref="K36">_xlfn.SWITCH(E36,1,0,2,7,3,10,4,15,5,50)</f>
+        <v>10</v>
       </c>
       <c r="L36" s="49" t="s">
         <v>149</v>
@@ -10756,8 +10761,8 @@
         <v>58</v>
       </c>
       <c r="K37" s="49" cm="1">
-        <f t="array" ref="K37">_xlfn.SWITCH(E37,1,0,2,7,3,15,4,25,5,50)</f>
-        <v>15</v>
+        <f t="array" ref="K37">_xlfn.SWITCH(E37,1,0,2,7,3,10,4,15,5,50)</f>
+        <v>10</v>
       </c>
       <c r="L37" s="49" t="s">
         <v>151</v>
@@ -10796,8 +10801,8 @@
         <v>58</v>
       </c>
       <c r="K38" s="49" cm="1">
-        <f t="array" ref="K38">_xlfn.SWITCH(E38,1,0,2,7,3,15,4,25,5,50)</f>
-        <v>15</v>
+        <f t="array" ref="K38">_xlfn.SWITCH(E38,1,0,2,7,3,10,4,15,5,50)</f>
+        <v>10</v>
       </c>
       <c r="L38" s="49" t="s">
         <v>153</v>
@@ -10836,8 +10841,8 @@
         <v>58</v>
       </c>
       <c r="K39" s="49" cm="1">
-        <f t="array" ref="K39">_xlfn.SWITCH(E39,1,0,2,7,3,15,4,25,5,50)</f>
-        <v>15</v>
+        <f t="array" ref="K39">_xlfn.SWITCH(E39,1,0,2,7,3,10,4,15,5,50)</f>
+        <v>10</v>
       </c>
       <c r="L39" s="49" t="s">
         <v>155</v>
@@ -10876,8 +10881,8 @@
         <v>58</v>
       </c>
       <c r="K40" s="49" cm="1">
-        <f t="array" ref="K40">_xlfn.SWITCH(E40,1,0,2,7,3,15,4,25,5,50)</f>
-        <v>15</v>
+        <f t="array" ref="K40">_xlfn.SWITCH(E40,1,0,2,7,3,10,4,15,5,50)</f>
+        <v>10</v>
       </c>
       <c r="L40" s="49" t="s">
         <v>157</v>
@@ -10916,7 +10921,7 @@
         <v>58</v>
       </c>
       <c r="K41" s="49" cm="1">
-        <f t="array" ref="K41">_xlfn.SWITCH(E41,1,0,2,7,3,15,4,25,5,50)</f>
+        <f t="array" ref="K41">_xlfn.SWITCH(E41,1,0,2,7,3,10,4,15,5,50)</f>
         <v>7</v>
       </c>
       <c r="L41" s="49" t="s">
@@ -10965,8 +10970,8 @@
         <v>58</v>
       </c>
       <c r="K42" s="49" cm="1">
-        <f t="array" ref="K42">_xlfn.SWITCH(E42,1,0,2,7,3,15,4,25,5,50)</f>
-        <v>15</v>
+        <f t="array" ref="K42">_xlfn.SWITCH(E42,1,0,2,7,3,10,4,15,5,50)</f>
+        <v>10</v>
       </c>
       <c r="L42" s="49" t="s">
         <v>163</v>
@@ -11016,7 +11021,8 @@
       <c r="I43" s="69" t="s">
         <v>58</v>
       </c>
-      <c r="K43" s="49">
+      <c r="K43" s="49" cm="1">
+        <f t="array" ref="K43">_xlfn.SWITCH(E43,1,0,2,7,3,10,4,15,5,50)</f>
         <v>7</v>
       </c>
       <c r="L43" s="49" t="s">
@@ -11067,7 +11073,8 @@
       <c r="I44" s="69" t="s">
         <v>58</v>
       </c>
-      <c r="K44" s="49">
+      <c r="K44" s="49" cm="1">
+        <f t="array" ref="K44">_xlfn.SWITCH(E44,1,0,2,7,3,10,4,15,5,50)</f>
         <v>7</v>
       </c>
       <c r="L44" s="49" t="s">
@@ -23262,7 +23269,7 @@
       </c>
       <c r="H260">
         <f>_xlfn.XLOOKUP(E260,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="261" spans="1:8">
@@ -23296,7 +23303,7 @@
       </c>
       <c r="H261">
         <f>_xlfn.XLOOKUP(E261,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="262" spans="1:8">
@@ -23330,7 +23337,7 @@
       </c>
       <c r="H262">
         <f>_xlfn.XLOOKUP(E262,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="263" spans="1:8">
@@ -23364,7 +23371,7 @@
       </c>
       <c r="H263">
         <f>_xlfn.XLOOKUP(E263,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="264" spans="1:8">
@@ -23398,7 +23405,7 @@
       </c>
       <c r="H264">
         <f>_xlfn.XLOOKUP(E264,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="265" spans="1:8">
@@ -23432,7 +23439,7 @@
       </c>
       <c r="H265">
         <f>_xlfn.XLOOKUP(E265,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="266" spans="1:8">
@@ -23466,7 +23473,7 @@
       </c>
       <c r="H266">
         <f>_xlfn.XLOOKUP(E266,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="267" spans="1:8">
@@ -23500,7 +23507,7 @@
       </c>
       <c r="H267">
         <f>_xlfn.XLOOKUP(E267,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="268" spans="1:8">
@@ -23534,7 +23541,7 @@
       </c>
       <c r="H268">
         <f>_xlfn.XLOOKUP(E268,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="269" spans="1:8">
@@ -23568,7 +23575,7 @@
       </c>
       <c r="H269">
         <f>_xlfn.XLOOKUP(E269,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="270" spans="1:8">
@@ -23602,7 +23609,7 @@
       </c>
       <c r="H270">
         <f>_xlfn.XLOOKUP(E270,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="271" spans="1:8">
@@ -23636,7 +23643,7 @@
       </c>
       <c r="H271">
         <f>_xlfn.XLOOKUP(E271,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="272" spans="1:8">
@@ -23670,7 +23677,7 @@
       </c>
       <c r="H272">
         <f>_xlfn.XLOOKUP(E272,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="273" spans="1:8">
@@ -23704,7 +23711,7 @@
       </c>
       <c r="H273">
         <f>_xlfn.XLOOKUP(E273,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="274" spans="1:8">
@@ -23738,7 +23745,7 @@
       </c>
       <c r="H274">
         <f>_xlfn.XLOOKUP(E274,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="275" spans="1:8">
@@ -23772,7 +23779,7 @@
       </c>
       <c r="H275">
         <f>_xlfn.XLOOKUP(E275,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="276" spans="1:8">
@@ -23806,7 +23813,7 @@
       </c>
       <c r="H276">
         <f>_xlfn.XLOOKUP(E276,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="277" spans="1:8">
@@ -23840,7 +23847,7 @@
       </c>
       <c r="H277">
         <f>_xlfn.XLOOKUP(E277,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="278" spans="1:8">
@@ -23874,7 +23881,7 @@
       </c>
       <c r="H278">
         <f>_xlfn.XLOOKUP(E278,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="279" spans="1:8">
@@ -23908,7 +23915,7 @@
       </c>
       <c r="H279">
         <f>_xlfn.XLOOKUP(E279,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="280" spans="1:8">
@@ -23942,7 +23949,7 @@
       </c>
       <c r="H280">
         <f>_xlfn.XLOOKUP(E280,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="281" spans="1:8">
@@ -23976,7 +23983,7 @@
       </c>
       <c r="H281">
         <f>_xlfn.XLOOKUP(E281,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="282" spans="1:8">
@@ -24010,7 +24017,7 @@
       </c>
       <c r="H282">
         <f>_xlfn.XLOOKUP(E282,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="283" spans="1:8">
@@ -24044,7 +24051,7 @@
       </c>
       <c r="H283">
         <f>_xlfn.XLOOKUP(E283,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="284" spans="1:8">
@@ -24078,7 +24085,7 @@
       </c>
       <c r="H284">
         <f>_xlfn.XLOOKUP(E284,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="285" spans="1:8">
@@ -24112,7 +24119,7 @@
       </c>
       <c r="H285">
         <f>_xlfn.XLOOKUP(E285,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="286" spans="1:8">
@@ -24146,7 +24153,7 @@
       </c>
       <c r="H286">
         <f>_xlfn.XLOOKUP(E286,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="287" spans="1:8">
@@ -24180,7 +24187,7 @@
       </c>
       <c r="H287">
         <f>_xlfn.XLOOKUP(E287,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="288" spans="1:8">
@@ -24214,7 +24221,7 @@
       </c>
       <c r="H288">
         <f>_xlfn.XLOOKUP(E288,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="289" spans="1:8">
@@ -24248,7 +24255,7 @@
       </c>
       <c r="H289">
         <f>_xlfn.XLOOKUP(E289,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="290" spans="1:8">
@@ -24282,7 +24289,7 @@
       </c>
       <c r="H290">
         <f>_xlfn.XLOOKUP(E290,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="291" spans="1:8">
@@ -24316,7 +24323,7 @@
       </c>
       <c r="H291">
         <f>_xlfn.XLOOKUP(E291,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="292" spans="1:8">
@@ -24350,7 +24357,7 @@
       </c>
       <c r="H292">
         <f>_xlfn.XLOOKUP(E292,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="293" spans="1:8">
@@ -24384,7 +24391,7 @@
       </c>
       <c r="H293">
         <f>_xlfn.XLOOKUP(E293,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="294" spans="1:8">
@@ -24418,7 +24425,7 @@
       </c>
       <c r="H294">
         <f>_xlfn.XLOOKUP(E294,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="295" spans="1:8">
@@ -24452,7 +24459,7 @@
       </c>
       <c r="H295">
         <f>_xlfn.XLOOKUP(E295,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="296" spans="1:8">
@@ -24486,7 +24493,7 @@
       </c>
       <c r="H296">
         <f>_xlfn.XLOOKUP(E296,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="297" spans="1:8">
@@ -24520,7 +24527,7 @@
       </c>
       <c r="H297">
         <f>_xlfn.XLOOKUP(E297,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="298" spans="1:8">
@@ -24554,7 +24561,7 @@
       </c>
       <c r="H298">
         <f>_xlfn.XLOOKUP(E298,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="299" spans="1:8">
@@ -24588,7 +24595,7 @@
       </c>
       <c r="H299">
         <f>_xlfn.XLOOKUP(E299,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="300" spans="1:8">
@@ -24622,7 +24629,7 @@
       </c>
       <c r="H300">
         <f>_xlfn.XLOOKUP(E300,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="301" spans="1:8">
@@ -24656,7 +24663,7 @@
       </c>
       <c r="H301">
         <f>_xlfn.XLOOKUP(E301,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="302" spans="1:8">
@@ -24690,7 +24697,7 @@
       </c>
       <c r="H302">
         <f>_xlfn.XLOOKUP(E302,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="303" spans="1:8">
@@ -24724,7 +24731,7 @@
       </c>
       <c r="H303">
         <f>_xlfn.XLOOKUP(E303,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="304" spans="1:8">
@@ -24758,7 +24765,7 @@
       </c>
       <c r="H304">
         <f>_xlfn.XLOOKUP(E304,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="305" spans="1:8">
@@ -24792,7 +24799,7 @@
       </c>
       <c r="H305">
         <f>_xlfn.XLOOKUP(E305,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="306" spans="1:8">
@@ -24826,7 +24833,7 @@
       </c>
       <c r="H306">
         <f>_xlfn.XLOOKUP(E306,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="307" spans="1:8">
@@ -24860,7 +24867,7 @@
       </c>
       <c r="H307">
         <f>_xlfn.XLOOKUP(E307,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="308" spans="1:8">
@@ -25430,7 +25437,7 @@
       </c>
       <c r="H324">
         <f>_xlfn.XLOOKUP(E324,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="325" spans="1:8">
@@ -25464,7 +25471,7 @@
       </c>
       <c r="H325">
         <f>_xlfn.XLOOKUP(E325,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="326" spans="1:8">
@@ -25498,7 +25505,7 @@
       </c>
       <c r="H326">
         <f>_xlfn.XLOOKUP(E326,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="327" spans="1:8">
@@ -25532,7 +25539,7 @@
       </c>
       <c r="H327">
         <f>_xlfn.XLOOKUP(E327,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="328" spans="1:8">
@@ -25566,7 +25573,7 @@
       </c>
       <c r="H328">
         <f>_xlfn.XLOOKUP(E328,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="329" spans="1:8">
@@ -25600,7 +25607,7 @@
       </c>
       <c r="H329">
         <f>_xlfn.XLOOKUP(E329,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="330" spans="1:8">
@@ -25634,7 +25641,7 @@
       </c>
       <c r="H330">
         <f>_xlfn.XLOOKUP(E330,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="331" spans="1:8">
@@ -25668,7 +25675,7 @@
       </c>
       <c r="H331">
         <f>_xlfn.XLOOKUP(E331,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="332" spans="1:8">
@@ -25702,7 +25709,7 @@
       </c>
       <c r="H332">
         <f>_xlfn.XLOOKUP(E332,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="333" spans="1:8">
@@ -25736,7 +25743,7 @@
       </c>
       <c r="H333">
         <f>_xlfn.XLOOKUP(E333,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="334" spans="1:8">
@@ -25770,7 +25777,7 @@
       </c>
       <c r="H334">
         <f>_xlfn.XLOOKUP(E334,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="335" spans="1:8">
@@ -25804,7 +25811,7 @@
       </c>
       <c r="H335">
         <f>_xlfn.XLOOKUP(E335,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="336" spans="1:8">
@@ -25838,7 +25845,7 @@
       </c>
       <c r="H336">
         <f>_xlfn.XLOOKUP(E336,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="337" spans="1:8">
@@ -25872,7 +25879,7 @@
       </c>
       <c r="H337">
         <f>_xlfn.XLOOKUP(E337,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="338" spans="1:8">
@@ -25906,7 +25913,7 @@
       </c>
       <c r="H338">
         <f>_xlfn.XLOOKUP(E338,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="339" spans="1:8">
@@ -25940,7 +25947,7 @@
       </c>
       <c r="H339">
         <f>_xlfn.XLOOKUP(E339,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="340" spans="1:8">
@@ -25974,7 +25981,7 @@
       </c>
       <c r="H340">
         <f>_xlfn.XLOOKUP(E340,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="341" spans="1:8">
@@ -26008,7 +26015,7 @@
       </c>
       <c r="H341">
         <f>_xlfn.XLOOKUP(E341,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="342" spans="1:8">
@@ -26042,7 +26049,7 @@
       </c>
       <c r="H342">
         <f>_xlfn.XLOOKUP(E342,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="343" spans="1:8">
@@ -26076,7 +26083,7 @@
       </c>
       <c r="H343">
         <f>_xlfn.XLOOKUP(E343,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="344" spans="1:8">
@@ -26110,7 +26117,7 @@
       </c>
       <c r="H344">
         <f>_xlfn.XLOOKUP(E344,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="345" spans="1:8">
@@ -26144,7 +26151,7 @@
       </c>
       <c r="H345">
         <f>_xlfn.XLOOKUP(E345,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="346" spans="1:8">
@@ -26178,7 +26185,7 @@
       </c>
       <c r="H346">
         <f>_xlfn.XLOOKUP(E346,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="347" spans="1:8">
@@ -26212,7 +26219,7 @@
       </c>
       <c r="H347">
         <f>_xlfn.XLOOKUP(E347,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="348" spans="1:8">
@@ -26246,7 +26253,7 @@
       </c>
       <c r="H348">
         <f>_xlfn.XLOOKUP(E348,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="349" spans="1:8">
@@ -26280,7 +26287,7 @@
       </c>
       <c r="H349">
         <f>_xlfn.XLOOKUP(E349,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="350" spans="1:8">
@@ -26314,7 +26321,7 @@
       </c>
       <c r="H350">
         <f>_xlfn.XLOOKUP(E350,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="351" spans="1:8">
@@ -26348,7 +26355,7 @@
       </c>
       <c r="H351">
         <f>_xlfn.XLOOKUP(E351,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="352" spans="1:8">
@@ -26382,7 +26389,7 @@
       </c>
       <c r="H352">
         <f>_xlfn.XLOOKUP(E352,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="353" spans="1:8">
@@ -26416,7 +26423,7 @@
       </c>
       <c r="H353">
         <f>_xlfn.XLOOKUP(E353,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="354" spans="1:8">
@@ -26450,7 +26457,7 @@
       </c>
       <c r="H354">
         <f>_xlfn.XLOOKUP(E354,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="355" spans="1:8">
@@ -26484,7 +26491,7 @@
       </c>
       <c r="H355">
         <f>_xlfn.XLOOKUP(E355,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="356" spans="1:8">
@@ -26518,7 +26525,7 @@
       </c>
       <c r="H356">
         <f>_xlfn.XLOOKUP(E356,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="357" spans="1:8">
@@ -26552,7 +26559,7 @@
       </c>
       <c r="H357">
         <f>_xlfn.XLOOKUP(E357,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="358" spans="1:8">
@@ -26586,7 +26593,7 @@
       </c>
       <c r="H358">
         <f>_xlfn.XLOOKUP(E358,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="359" spans="1:8">
@@ -26620,7 +26627,7 @@
       </c>
       <c r="H359">
         <f>_xlfn.XLOOKUP(E359,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="360" spans="1:8">
@@ -26654,7 +26661,7 @@
       </c>
       <c r="H360">
         <f>_xlfn.XLOOKUP(E360,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="361" spans="1:8">
@@ -26688,7 +26695,7 @@
       </c>
       <c r="H361">
         <f>_xlfn.XLOOKUP(E361,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="362" spans="1:8">
@@ -26722,7 +26729,7 @@
       </c>
       <c r="H362">
         <f>_xlfn.XLOOKUP(E362,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="363" spans="1:8">
@@ -26756,7 +26763,7 @@
       </c>
       <c r="H363">
         <f>_xlfn.XLOOKUP(E363,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="364" spans="1:8">
@@ -26790,7 +26797,7 @@
       </c>
       <c r="H364">
         <f>_xlfn.XLOOKUP(E364,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="365" spans="1:8">
@@ -26824,7 +26831,7 @@
       </c>
       <c r="H365">
         <f>_xlfn.XLOOKUP(E365,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="366" spans="1:8">
@@ -26858,7 +26865,7 @@
       </c>
       <c r="H366">
         <f>_xlfn.XLOOKUP(E366,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="367" spans="1:8">
@@ -26892,7 +26899,7 @@
       </c>
       <c r="H367">
         <f>_xlfn.XLOOKUP(E367,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="368" spans="1:8">
@@ -26926,7 +26933,7 @@
       </c>
       <c r="H368">
         <f>_xlfn.XLOOKUP(E368,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="369" spans="1:8">
@@ -26960,7 +26967,7 @@
       </c>
       <c r="H369">
         <f>_xlfn.XLOOKUP(E369,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="370" spans="1:8">
@@ -26994,7 +27001,7 @@
       </c>
       <c r="H370">
         <f>_xlfn.XLOOKUP(E370,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="371" spans="1:8">
@@ -27028,7 +27035,7 @@
       </c>
       <c r="H371">
         <f>_xlfn.XLOOKUP(E371,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="372" spans="1:8">
@@ -28130,7 +28137,7 @@
       </c>
       <c r="G404">
         <f>_xlfn.XLOOKUP(C404,SkillActive!$A:$A,SkillActive!E:E,,0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H404">
         <f>_xlfn.XLOOKUP(E404,SkillActive!B:B,SkillActive!K:K,,0)</f>
@@ -28164,7 +28171,7 @@
       </c>
       <c r="G405">
         <f>_xlfn.XLOOKUP(C405,SkillActive!$A:$A,SkillActive!E:E,,0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H405">
         <f>_xlfn.XLOOKUP(E405,SkillActive!B:B,SkillActive!K:K,,0)</f>
@@ -28198,7 +28205,7 @@
       </c>
       <c r="G406">
         <f>_xlfn.XLOOKUP(C406,SkillActive!$A:$A,SkillActive!E:E,,0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H406">
         <f>_xlfn.XLOOKUP(E406,SkillActive!B:B,SkillActive!K:K,,0)</f>
@@ -28232,7 +28239,7 @@
       </c>
       <c r="G407">
         <f>_xlfn.XLOOKUP(C407,SkillActive!$A:$A,SkillActive!E:E,,0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H407">
         <f>_xlfn.XLOOKUP(E407,SkillActive!B:B,SkillActive!K:K,,0)</f>
@@ -28266,7 +28273,7 @@
       </c>
       <c r="G408">
         <f>_xlfn.XLOOKUP(C408,SkillActive!$A:$A,SkillActive!E:E,,0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H408">
         <f>_xlfn.XLOOKUP(E408,SkillActive!B:B,SkillActive!K:K,,0)</f>
@@ -28300,7 +28307,7 @@
       </c>
       <c r="G409">
         <f>_xlfn.XLOOKUP(C409,SkillActive!$A:$A,SkillActive!E:E,,0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H409">
         <f>_xlfn.XLOOKUP(E409,SkillActive!B:B,SkillActive!K:K,,0)</f>
@@ -28334,7 +28341,7 @@
       </c>
       <c r="G410">
         <f>_xlfn.XLOOKUP(C410,SkillActive!$A:$A,SkillActive!E:E,,0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H410">
         <f>_xlfn.XLOOKUP(E410,SkillActive!B:B,SkillActive!K:K,,0)</f>
@@ -28368,7 +28375,7 @@
       </c>
       <c r="G411">
         <f>_xlfn.XLOOKUP(C411,SkillActive!$A:$A,SkillActive!E:E,,0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H411">
         <f>_xlfn.XLOOKUP(E411,SkillActive!B:B,SkillActive!K:K,,0)</f>
@@ -28402,7 +28409,7 @@
       </c>
       <c r="G412">
         <f>_xlfn.XLOOKUP(C412,SkillActive!$A:$A,SkillActive!E:E,,0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H412">
         <f>_xlfn.XLOOKUP(E412,SkillActive!B:B,SkillActive!K:K,,0)</f>
@@ -28436,7 +28443,7 @@
       </c>
       <c r="G413">
         <f>_xlfn.XLOOKUP(C413,SkillActive!$A:$A,SkillActive!E:E,,0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H413">
         <f>_xlfn.XLOOKUP(E413,SkillActive!B:B,SkillActive!K:K,,0)</f>
@@ -28470,7 +28477,7 @@
       </c>
       <c r="G414">
         <f>_xlfn.XLOOKUP(C414,SkillActive!$A:$A,SkillActive!E:E,,0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H414">
         <f>_xlfn.XLOOKUP(E414,SkillActive!B:B,SkillActive!K:K,,0)</f>
@@ -28504,7 +28511,7 @@
       </c>
       <c r="G415">
         <f>_xlfn.XLOOKUP(C415,SkillActive!$A:$A,SkillActive!E:E,,0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H415">
         <f>_xlfn.XLOOKUP(E415,SkillActive!B:B,SkillActive!K:K,,0)</f>
@@ -28538,7 +28545,7 @@
       </c>
       <c r="G416">
         <f>_xlfn.XLOOKUP(C416,SkillActive!$A:$A,SkillActive!E:E,,0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H416">
         <f>_xlfn.XLOOKUP(E416,SkillActive!B:B,SkillActive!K:K,,0)</f>
@@ -28572,7 +28579,7 @@
       </c>
       <c r="G417">
         <f>_xlfn.XLOOKUP(C417,SkillActive!$A:$A,SkillActive!E:E,,0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H417">
         <f>_xlfn.XLOOKUP(E417,SkillActive!B:B,SkillActive!K:K,,0)</f>
@@ -28606,7 +28613,7 @@
       </c>
       <c r="G418">
         <f>_xlfn.XLOOKUP(C418,SkillActive!$A:$A,SkillActive!E:E,,0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H418">
         <f>_xlfn.XLOOKUP(E418,SkillActive!B:B,SkillActive!K:K,,0)</f>
@@ -28640,7 +28647,7 @@
       </c>
       <c r="G419">
         <f>_xlfn.XLOOKUP(C419,SkillActive!$A:$A,SkillActive!E:E,,0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H419">
         <f>_xlfn.XLOOKUP(E419,SkillActive!B:B,SkillActive!K:K,,0)</f>
@@ -28674,11 +28681,11 @@
       </c>
       <c r="G420">
         <f>_xlfn.XLOOKUP(C420,SkillActive!$A:$A,SkillActive!E:E,,0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H420">
         <f>_xlfn.XLOOKUP(E420,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>50</v>
+        <v>15</v>
       </c>
     </row>
     <row r="421" spans="1:8">
@@ -28708,11 +28715,11 @@
       </c>
       <c r="G421">
         <f>_xlfn.XLOOKUP(C421,SkillActive!$A:$A,SkillActive!E:E,,0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H421">
         <f>_xlfn.XLOOKUP(E421,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>50</v>
+        <v>15</v>
       </c>
     </row>
     <row r="422" spans="1:8">
@@ -28742,11 +28749,11 @@
       </c>
       <c r="G422">
         <f>_xlfn.XLOOKUP(C422,SkillActive!$A:$A,SkillActive!E:E,,0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H422">
         <f>_xlfn.XLOOKUP(E422,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>50</v>
+        <v>15</v>
       </c>
     </row>
     <row r="423" spans="1:8">
@@ -28776,11 +28783,11 @@
       </c>
       <c r="G423">
         <f>_xlfn.XLOOKUP(C423,SkillActive!$A:$A,SkillActive!E:E,,0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H423">
         <f>_xlfn.XLOOKUP(E423,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>50</v>
+        <v>15</v>
       </c>
     </row>
     <row r="424" spans="1:8">
@@ -28810,11 +28817,11 @@
       </c>
       <c r="G424">
         <f>_xlfn.XLOOKUP(C424,SkillActive!$A:$A,SkillActive!E:E,,0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H424">
         <f>_xlfn.XLOOKUP(E424,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>50</v>
+        <v>15</v>
       </c>
     </row>
     <row r="425" spans="1:8">
@@ -28844,11 +28851,11 @@
       </c>
       <c r="G425">
         <f>_xlfn.XLOOKUP(C425,SkillActive!$A:$A,SkillActive!E:E,,0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H425">
         <f>_xlfn.XLOOKUP(E425,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>50</v>
+        <v>15</v>
       </c>
     </row>
     <row r="426" spans="1:8">
@@ -28878,11 +28885,11 @@
       </c>
       <c r="G426">
         <f>_xlfn.XLOOKUP(C426,SkillActive!$A:$A,SkillActive!E:E,,0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H426">
         <f>_xlfn.XLOOKUP(E426,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>50</v>
+        <v>15</v>
       </c>
     </row>
     <row r="427" spans="1:8">
@@ -28912,11 +28919,11 @@
       </c>
       <c r="G427">
         <f>_xlfn.XLOOKUP(C427,SkillActive!$A:$A,SkillActive!E:E,,0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H427">
         <f>_xlfn.XLOOKUP(E427,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>50</v>
+        <v>15</v>
       </c>
     </row>
     <row r="428" spans="1:8">
@@ -28946,11 +28953,11 @@
       </c>
       <c r="G428">
         <f>_xlfn.XLOOKUP(C428,SkillActive!$A:$A,SkillActive!E:E,,0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H428">
         <f>_xlfn.XLOOKUP(E428,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>50</v>
+        <v>15</v>
       </c>
     </row>
     <row r="429" spans="1:8">
@@ -28980,11 +28987,11 @@
       </c>
       <c r="G429">
         <f>_xlfn.XLOOKUP(C429,SkillActive!$A:$A,SkillActive!E:E,,0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H429">
         <f>_xlfn.XLOOKUP(E429,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>50</v>
+        <v>15</v>
       </c>
     </row>
     <row r="430" spans="1:8">
@@ -29014,11 +29021,11 @@
       </c>
       <c r="G430">
         <f>_xlfn.XLOOKUP(C430,SkillActive!$A:$A,SkillActive!E:E,,0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H430">
         <f>_xlfn.XLOOKUP(E430,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>50</v>
+        <v>15</v>
       </c>
     </row>
     <row r="431" spans="1:8">
@@ -29048,11 +29055,11 @@
       </c>
       <c r="G431">
         <f>_xlfn.XLOOKUP(C431,SkillActive!$A:$A,SkillActive!E:E,,0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H431">
         <f>_xlfn.XLOOKUP(E431,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>50</v>
+        <v>15</v>
       </c>
     </row>
     <row r="432" spans="1:8">
@@ -29082,11 +29089,11 @@
       </c>
       <c r="G432">
         <f>_xlfn.XLOOKUP(C432,SkillActive!$A:$A,SkillActive!E:E,,0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H432">
         <f>_xlfn.XLOOKUP(E432,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>50</v>
+        <v>15</v>
       </c>
     </row>
     <row r="433" spans="1:8">
@@ -29116,11 +29123,11 @@
       </c>
       <c r="G433">
         <f>_xlfn.XLOOKUP(C433,SkillActive!$A:$A,SkillActive!E:E,,0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H433">
         <f>_xlfn.XLOOKUP(E433,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>50</v>
+        <v>15</v>
       </c>
     </row>
     <row r="434" spans="1:8">
@@ -29150,11 +29157,11 @@
       </c>
       <c r="G434">
         <f>_xlfn.XLOOKUP(C434,SkillActive!$A:$A,SkillActive!E:E,,0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H434">
         <f>_xlfn.XLOOKUP(E434,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>50</v>
+        <v>15</v>
       </c>
     </row>
     <row r="435" spans="1:8">
@@ -29184,11 +29191,11 @@
       </c>
       <c r="G435">
         <f>_xlfn.XLOOKUP(C435,SkillActive!$A:$A,SkillActive!E:E,,0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H435">
         <f>_xlfn.XLOOKUP(E435,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>50</v>
+        <v>15</v>
       </c>
     </row>
     <row r="436" spans="1:8">
@@ -29218,11 +29225,11 @@
       </c>
       <c r="G436">
         <f>_xlfn.XLOOKUP(C436,SkillActive!$A:$A,SkillActive!E:E,,0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H436">
         <f>_xlfn.XLOOKUP(E436,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>50</v>
+        <v>15</v>
       </c>
     </row>
     <row r="437" spans="1:8">
@@ -29252,11 +29259,11 @@
       </c>
       <c r="G437">
         <f>_xlfn.XLOOKUP(C437,SkillActive!$A:$A,SkillActive!E:E,,0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H437">
         <f>_xlfn.XLOOKUP(E437,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>50</v>
+        <v>15</v>
       </c>
     </row>
     <row r="438" spans="1:8">
@@ -29286,11 +29293,11 @@
       </c>
       <c r="G438">
         <f>_xlfn.XLOOKUP(C438,SkillActive!$A:$A,SkillActive!E:E,,0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H438">
         <f>_xlfn.XLOOKUP(E438,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>50</v>
+        <v>15</v>
       </c>
     </row>
     <row r="439" spans="1:8">
@@ -29320,11 +29327,11 @@
       </c>
       <c r="G439">
         <f>_xlfn.XLOOKUP(C439,SkillActive!$A:$A,SkillActive!E:E,,0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H439">
         <f>_xlfn.XLOOKUP(E439,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>50</v>
+        <v>15</v>
       </c>
     </row>
     <row r="440" spans="1:8">
@@ -29354,11 +29361,11 @@
       </c>
       <c r="G440">
         <f>_xlfn.XLOOKUP(C440,SkillActive!$A:$A,SkillActive!E:E,,0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H440">
         <f>_xlfn.XLOOKUP(E440,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>50</v>
+        <v>15</v>
       </c>
     </row>
     <row r="441" spans="1:8">
@@ -29388,11 +29395,11 @@
       </c>
       <c r="G441">
         <f>_xlfn.XLOOKUP(C441,SkillActive!$A:$A,SkillActive!E:E,,0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H441">
         <f>_xlfn.XLOOKUP(E441,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>50</v>
+        <v>15</v>
       </c>
     </row>
     <row r="442" spans="1:8">
@@ -29422,11 +29429,11 @@
       </c>
       <c r="G442">
         <f>_xlfn.XLOOKUP(C442,SkillActive!$A:$A,SkillActive!E:E,,0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H442">
         <f>_xlfn.XLOOKUP(E442,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>50</v>
+        <v>15</v>
       </c>
     </row>
     <row r="443" spans="1:8">
@@ -29456,11 +29463,11 @@
       </c>
       <c r="G443">
         <f>_xlfn.XLOOKUP(C443,SkillActive!$A:$A,SkillActive!E:E,,0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H443">
         <f>_xlfn.XLOOKUP(E443,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>50</v>
+        <v>15</v>
       </c>
     </row>
     <row r="444" spans="1:8">
@@ -29490,11 +29497,11 @@
       </c>
       <c r="G444">
         <f>_xlfn.XLOOKUP(C444,SkillActive!$A:$A,SkillActive!E:E,,0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H444">
         <f>_xlfn.XLOOKUP(E444,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>50</v>
+        <v>15</v>
       </c>
     </row>
     <row r="445" spans="1:8">
@@ -29524,11 +29531,11 @@
       </c>
       <c r="G445">
         <f>_xlfn.XLOOKUP(C445,SkillActive!$A:$A,SkillActive!E:E,,0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H445">
         <f>_xlfn.XLOOKUP(E445,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>50</v>
+        <v>15</v>
       </c>
     </row>
     <row r="446" spans="1:8">
@@ -29558,11 +29565,11 @@
       </c>
       <c r="G446">
         <f>_xlfn.XLOOKUP(C446,SkillActive!$A:$A,SkillActive!E:E,,0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H446">
         <f>_xlfn.XLOOKUP(E446,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>50</v>
+        <v>15</v>
       </c>
     </row>
     <row r="447" spans="1:8">
@@ -29592,11 +29599,11 @@
       </c>
       <c r="G447">
         <f>_xlfn.XLOOKUP(C447,SkillActive!$A:$A,SkillActive!E:E,,0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H447">
         <f>_xlfn.XLOOKUP(E447,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>50</v>
+        <v>15</v>
       </c>
     </row>
     <row r="448" spans="1:8">
@@ -29626,11 +29633,11 @@
       </c>
       <c r="G448">
         <f>_xlfn.XLOOKUP(C448,SkillActive!$A:$A,SkillActive!E:E,,0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H448">
         <f>_xlfn.XLOOKUP(E448,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>50</v>
+        <v>15</v>
       </c>
     </row>
     <row r="449" spans="1:8">
@@ -29660,11 +29667,11 @@
       </c>
       <c r="G449">
         <f>_xlfn.XLOOKUP(C449,SkillActive!$A:$A,SkillActive!E:E,,0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H449">
         <f>_xlfn.XLOOKUP(E449,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>50</v>
+        <v>15</v>
       </c>
     </row>
     <row r="450" spans="1:8">
@@ -29694,11 +29701,11 @@
       </c>
       <c r="G450">
         <f>_xlfn.XLOOKUP(C450,SkillActive!$A:$A,SkillActive!E:E,,0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H450">
         <f>_xlfn.XLOOKUP(E450,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>50</v>
+        <v>15</v>
       </c>
     </row>
     <row r="451" spans="1:8">
@@ -29728,11 +29735,11 @@
       </c>
       <c r="G451">
         <f>_xlfn.XLOOKUP(C451,SkillActive!$A:$A,SkillActive!E:E,,0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H451">
         <f>_xlfn.XLOOKUP(E451,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>50</v>
+        <v>15</v>
       </c>
     </row>
     <row r="452" spans="1:8">
@@ -29762,11 +29769,11 @@
       </c>
       <c r="G452">
         <f>_xlfn.XLOOKUP(C452,SkillActive!$A:$A,SkillActive!E:E,,0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H452">
         <f>_xlfn.XLOOKUP(E452,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>50</v>
+        <v>15</v>
       </c>
     </row>
     <row r="453" spans="1:8">
@@ -29796,11 +29803,11 @@
       </c>
       <c r="G453">
         <f>_xlfn.XLOOKUP(C453,SkillActive!$A:$A,SkillActive!E:E,,0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H453">
         <f>_xlfn.XLOOKUP(E453,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>50</v>
+        <v>15</v>
       </c>
     </row>
     <row r="454" spans="1:8">
@@ -29830,11 +29837,11 @@
       </c>
       <c r="G454">
         <f>_xlfn.XLOOKUP(C454,SkillActive!$A:$A,SkillActive!E:E,,0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H454">
         <f>_xlfn.XLOOKUP(E454,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>50</v>
+        <v>15</v>
       </c>
     </row>
     <row r="455" spans="1:8">
@@ -29864,11 +29871,11 @@
       </c>
       <c r="G455">
         <f>_xlfn.XLOOKUP(C455,SkillActive!$A:$A,SkillActive!E:E,,0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H455">
         <f>_xlfn.XLOOKUP(E455,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>50</v>
+        <v>15</v>
       </c>
     </row>
     <row r="456" spans="1:8">
@@ -29898,11 +29905,11 @@
       </c>
       <c r="G456">
         <f>_xlfn.XLOOKUP(C456,SkillActive!$A:$A,SkillActive!E:E,,0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H456">
         <f>_xlfn.XLOOKUP(E456,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>50</v>
+        <v>15</v>
       </c>
     </row>
     <row r="457" spans="1:8">
@@ -29932,11 +29939,11 @@
       </c>
       <c r="G457">
         <f>_xlfn.XLOOKUP(C457,SkillActive!$A:$A,SkillActive!E:E,,0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H457">
         <f>_xlfn.XLOOKUP(E457,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>50</v>
+        <v>15</v>
       </c>
     </row>
     <row r="458" spans="1:8">
@@ -29966,11 +29973,11 @@
       </c>
       <c r="G458">
         <f>_xlfn.XLOOKUP(C458,SkillActive!$A:$A,SkillActive!E:E,,0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H458">
         <f>_xlfn.XLOOKUP(E458,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>50</v>
+        <v>15</v>
       </c>
     </row>
     <row r="459" spans="1:8">
@@ -30000,11 +30007,11 @@
       </c>
       <c r="G459">
         <f>_xlfn.XLOOKUP(C459,SkillActive!$A:$A,SkillActive!E:E,,0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H459">
         <f>_xlfn.XLOOKUP(E459,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>50</v>
+        <v>15</v>
       </c>
     </row>
     <row r="460" spans="1:8">
@@ -30034,11 +30041,11 @@
       </c>
       <c r="G460">
         <f>_xlfn.XLOOKUP(C460,SkillActive!$A:$A,SkillActive!E:E,,0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H460">
         <f>_xlfn.XLOOKUP(E460,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>50</v>
+        <v>15</v>
       </c>
     </row>
     <row r="461" spans="1:8">
@@ -30068,11 +30075,11 @@
       </c>
       <c r="G461">
         <f>_xlfn.XLOOKUP(C461,SkillActive!$A:$A,SkillActive!E:E,,0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H461">
         <f>_xlfn.XLOOKUP(E461,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>50</v>
+        <v>15</v>
       </c>
     </row>
     <row r="462" spans="1:8">
@@ -30102,11 +30109,11 @@
       </c>
       <c r="G462">
         <f>_xlfn.XLOOKUP(C462,SkillActive!$A:$A,SkillActive!E:E,,0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H462">
         <f>_xlfn.XLOOKUP(E462,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>50</v>
+        <v>15</v>
       </c>
     </row>
     <row r="463" spans="1:8">
@@ -30136,11 +30143,11 @@
       </c>
       <c r="G463">
         <f>_xlfn.XLOOKUP(C463,SkillActive!$A:$A,SkillActive!E:E,,0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H463">
         <f>_xlfn.XLOOKUP(E463,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>50</v>
+        <v>15</v>
       </c>
     </row>
     <row r="464" spans="1:8">
@@ -30170,11 +30177,11 @@
       </c>
       <c r="G464">
         <f>_xlfn.XLOOKUP(C464,SkillActive!$A:$A,SkillActive!E:E,,0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H464">
         <f>_xlfn.XLOOKUP(E464,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>50</v>
+        <v>15</v>
       </c>
     </row>
     <row r="465" spans="1:8">
@@ -30204,11 +30211,11 @@
       </c>
       <c r="G465">
         <f>_xlfn.XLOOKUP(C465,SkillActive!$A:$A,SkillActive!E:E,,0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H465">
         <f>_xlfn.XLOOKUP(E465,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>50</v>
+        <v>15</v>
       </c>
     </row>
     <row r="466" spans="1:8">
@@ -30238,11 +30245,11 @@
       </c>
       <c r="G466">
         <f>_xlfn.XLOOKUP(C466,SkillActive!$A:$A,SkillActive!E:E,,0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H466">
         <f>_xlfn.XLOOKUP(E466,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>50</v>
+        <v>15</v>
       </c>
     </row>
     <row r="467" spans="1:8">
@@ -30272,11 +30279,11 @@
       </c>
       <c r="G467">
         <f>_xlfn.XLOOKUP(C467,SkillActive!$A:$A,SkillActive!E:E,,0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H467">
         <f>_xlfn.XLOOKUP(E467,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>50</v>
+        <v>15</v>
       </c>
     </row>
     <row r="468" spans="1:8">
@@ -30306,11 +30313,11 @@
       </c>
       <c r="G468">
         <f>_xlfn.XLOOKUP(C468,SkillActive!$A:$A,SkillActive!E:E,,0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H468">
         <f>_xlfn.XLOOKUP(E468,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>50</v>
+        <v>15</v>
       </c>
     </row>
     <row r="469" spans="1:8">
@@ -30340,11 +30347,11 @@
       </c>
       <c r="G469">
         <f>_xlfn.XLOOKUP(C469,SkillActive!$A:$A,SkillActive!E:E,,0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H469">
         <f>_xlfn.XLOOKUP(E469,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>50</v>
+        <v>15</v>
       </c>
     </row>
     <row r="470" spans="1:8">
@@ -30374,11 +30381,11 @@
       </c>
       <c r="G470">
         <f>_xlfn.XLOOKUP(C470,SkillActive!$A:$A,SkillActive!E:E,,0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H470">
         <f>_xlfn.XLOOKUP(E470,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>50</v>
+        <v>15</v>
       </c>
     </row>
     <row r="471" spans="1:8">
@@ -30408,11 +30415,11 @@
       </c>
       <c r="G471">
         <f>_xlfn.XLOOKUP(C471,SkillActive!$A:$A,SkillActive!E:E,,0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H471">
         <f>_xlfn.XLOOKUP(E471,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>50</v>
+        <v>15</v>
       </c>
     </row>
     <row r="472" spans="1:8">
@@ -30442,11 +30449,11 @@
       </c>
       <c r="G472">
         <f>_xlfn.XLOOKUP(C472,SkillActive!$A:$A,SkillActive!E:E,,0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H472">
         <f>_xlfn.XLOOKUP(E472,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>50</v>
+        <v>15</v>
       </c>
     </row>
     <row r="473" spans="1:8">
@@ -30476,11 +30483,11 @@
       </c>
       <c r="G473">
         <f>_xlfn.XLOOKUP(C473,SkillActive!$A:$A,SkillActive!E:E,,0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H473">
         <f>_xlfn.XLOOKUP(E473,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>50</v>
+        <v>15</v>
       </c>
     </row>
     <row r="474" spans="1:8">
@@ -30510,11 +30517,11 @@
       </c>
       <c r="G474">
         <f>_xlfn.XLOOKUP(C474,SkillActive!$A:$A,SkillActive!E:E,,0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H474">
         <f>_xlfn.XLOOKUP(E474,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>50</v>
+        <v>15</v>
       </c>
     </row>
     <row r="475" spans="1:8">
@@ -30544,11 +30551,11 @@
       </c>
       <c r="G475">
         <f>_xlfn.XLOOKUP(C475,SkillActive!$A:$A,SkillActive!E:E,,0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H475">
         <f>_xlfn.XLOOKUP(E475,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>50</v>
+        <v>15</v>
       </c>
     </row>
     <row r="476" spans="1:8">
@@ -30578,11 +30585,11 @@
       </c>
       <c r="G476">
         <f>_xlfn.XLOOKUP(C476,SkillActive!$A:$A,SkillActive!E:E,,0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H476">
         <f>_xlfn.XLOOKUP(E476,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>50</v>
+        <v>15</v>
       </c>
     </row>
     <row r="477" spans="1:8">
@@ -30612,11 +30619,11 @@
       </c>
       <c r="G477">
         <f>_xlfn.XLOOKUP(C477,SkillActive!$A:$A,SkillActive!E:E,,0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H477">
         <f>_xlfn.XLOOKUP(E477,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>50</v>
+        <v>15</v>
       </c>
     </row>
     <row r="478" spans="1:8">
@@ -30646,11 +30653,11 @@
       </c>
       <c r="G478">
         <f>_xlfn.XLOOKUP(C478,SkillActive!$A:$A,SkillActive!E:E,,0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H478">
         <f>_xlfn.XLOOKUP(E478,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>50</v>
+        <v>15</v>
       </c>
     </row>
     <row r="479" spans="1:8">
@@ -30680,11 +30687,11 @@
       </c>
       <c r="G479">
         <f>_xlfn.XLOOKUP(C479,SkillActive!$A:$A,SkillActive!E:E,,0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H479">
         <f>_xlfn.XLOOKUP(E479,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>50</v>
+        <v>15</v>
       </c>
     </row>
     <row r="480" spans="1:8">
@@ -30714,11 +30721,11 @@
       </c>
       <c r="G480">
         <f>_xlfn.XLOOKUP(C480,SkillActive!$A:$A,SkillActive!E:E,,0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H480">
         <f>_xlfn.XLOOKUP(E480,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>50</v>
+        <v>15</v>
       </c>
     </row>
     <row r="481" spans="1:8">
@@ -30748,11 +30755,11 @@
       </c>
       <c r="G481">
         <f>_xlfn.XLOOKUP(C481,SkillActive!$A:$A,SkillActive!E:E,,0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H481">
         <f>_xlfn.XLOOKUP(E481,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>50</v>
+        <v>15</v>
       </c>
     </row>
     <row r="482" spans="1:8">
@@ -30782,11 +30789,11 @@
       </c>
       <c r="G482">
         <f>_xlfn.XLOOKUP(C482,SkillActive!$A:$A,SkillActive!E:E,,0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H482">
         <f>_xlfn.XLOOKUP(E482,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>50</v>
+        <v>15</v>
       </c>
     </row>
     <row r="483" spans="1:8">
@@ -30816,11 +30823,11 @@
       </c>
       <c r="G483">
         <f>_xlfn.XLOOKUP(C483,SkillActive!$A:$A,SkillActive!E:E,,0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H483">
         <f>_xlfn.XLOOKUP(E483,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>50</v>
+        <v>15</v>
       </c>
     </row>
     <row r="484" spans="1:8">
@@ -31861,7 +31868,7 @@
       </c>
       <c r="H516">
         <f>_xlfn.XLOOKUP(E516,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="517" spans="1:8">
@@ -31894,7 +31901,7 @@
       </c>
       <c r="H517">
         <f>_xlfn.XLOOKUP(E517,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="518" spans="1:8">
@@ -31927,7 +31934,7 @@
       </c>
       <c r="H518">
         <f>_xlfn.XLOOKUP(E518,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="519" spans="1:8">
@@ -31960,7 +31967,7 @@
       </c>
       <c r="H519">
         <f>_xlfn.XLOOKUP(E519,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="520" spans="1:8">
@@ -31993,7 +32000,7 @@
       </c>
       <c r="H520">
         <f>_xlfn.XLOOKUP(E520,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="521" spans="1:8">
@@ -32026,7 +32033,7 @@
       </c>
       <c r="H521">
         <f>_xlfn.XLOOKUP(E521,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="522" spans="1:8">
@@ -32059,7 +32066,7 @@
       </c>
       <c r="H522">
         <f>_xlfn.XLOOKUP(E522,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="523" spans="1:8">
@@ -32092,7 +32099,7 @@
       </c>
       <c r="H523">
         <f>_xlfn.XLOOKUP(E523,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="524" spans="1:8">
@@ -32125,7 +32132,7 @@
       </c>
       <c r="H524">
         <f>_xlfn.XLOOKUP(E524,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="525" spans="1:8">
@@ -32158,7 +32165,7 @@
       </c>
       <c r="H525">
         <f>_xlfn.XLOOKUP(E525,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="526" spans="1:8">
@@ -32191,7 +32198,7 @@
       </c>
       <c r="H526">
         <f>_xlfn.XLOOKUP(E526,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="527" spans="1:8">
@@ -32224,7 +32231,7 @@
       </c>
       <c r="H527">
         <f>_xlfn.XLOOKUP(E527,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="528" spans="1:8">
@@ -32257,7 +32264,7 @@
       </c>
       <c r="H528">
         <f>_xlfn.XLOOKUP(E528,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="529" spans="1:8">
@@ -32290,7 +32297,7 @@
       </c>
       <c r="H529">
         <f>_xlfn.XLOOKUP(E529,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="530" spans="1:8">
@@ -32323,7 +32330,7 @@
       </c>
       <c r="H530">
         <f>_xlfn.XLOOKUP(E530,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="531" spans="1:8">
@@ -32356,7 +32363,7 @@
       </c>
       <c r="H531">
         <f>_xlfn.XLOOKUP(E531,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="532" spans="1:8">
@@ -32389,7 +32396,7 @@
       </c>
       <c r="H532">
         <f>_xlfn.XLOOKUP(E532,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="533" spans="1:8">
@@ -32422,7 +32429,7 @@
       </c>
       <c r="H533">
         <f>_xlfn.XLOOKUP(E533,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="534" spans="1:8">
@@ -32455,7 +32462,7 @@
       </c>
       <c r="H534">
         <f>_xlfn.XLOOKUP(E534,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="535" spans="1:8">
@@ -32488,7 +32495,7 @@
       </c>
       <c r="H535">
         <f>_xlfn.XLOOKUP(E535,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="536" spans="1:8">
@@ -32521,7 +32528,7 @@
       </c>
       <c r="H536">
         <f>_xlfn.XLOOKUP(E536,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="537" spans="1:8">
@@ -32554,7 +32561,7 @@
       </c>
       <c r="H537">
         <f>_xlfn.XLOOKUP(E537,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="538" spans="1:8">
@@ -32587,7 +32594,7 @@
       </c>
       <c r="H538">
         <f>_xlfn.XLOOKUP(E538,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="539" spans="1:8">
@@ -32620,7 +32627,7 @@
       </c>
       <c r="H539">
         <f>_xlfn.XLOOKUP(E539,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="540" spans="1:8">
@@ -32653,7 +32660,7 @@
       </c>
       <c r="H540">
         <f>_xlfn.XLOOKUP(E540,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="541" spans="1:8">
@@ -32686,7 +32693,7 @@
       </c>
       <c r="H541">
         <f>_xlfn.XLOOKUP(E541,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="542" spans="1:8">
@@ -32719,7 +32726,7 @@
       </c>
       <c r="H542">
         <f>_xlfn.XLOOKUP(E542,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="543" spans="1:8">
@@ -32752,7 +32759,7 @@
       </c>
       <c r="H543">
         <f>_xlfn.XLOOKUP(E543,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="544" spans="1:8">
@@ -32785,7 +32792,7 @@
       </c>
       <c r="H544">
         <f>_xlfn.XLOOKUP(E544,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="545" spans="1:8">
@@ -32818,7 +32825,7 @@
       </c>
       <c r="H545">
         <f>_xlfn.XLOOKUP(E545,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="546" spans="1:8">
@@ -32851,7 +32858,7 @@
       </c>
       <c r="H546">
         <f>_xlfn.XLOOKUP(E546,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="547" spans="1:8">
@@ -32884,7 +32891,7 @@
       </c>
       <c r="H547">
         <f>_xlfn.XLOOKUP(E547,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="548" spans="1:8">
@@ -32917,7 +32924,7 @@
       </c>
       <c r="H548">
         <f>_xlfn.XLOOKUP(E548,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="549" spans="1:8">
@@ -32950,7 +32957,7 @@
       </c>
       <c r="H549">
         <f>_xlfn.XLOOKUP(E549,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="550" spans="1:8">
@@ -32983,7 +32990,7 @@
       </c>
       <c r="H550">
         <f>_xlfn.XLOOKUP(E550,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="551" spans="1:8">
@@ -33016,7 +33023,7 @@
       </c>
       <c r="H551">
         <f>_xlfn.XLOOKUP(E551,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="552" spans="1:8">
@@ -33049,7 +33056,7 @@
       </c>
       <c r="H552">
         <f>_xlfn.XLOOKUP(E552,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="553" spans="1:8">
@@ -33082,7 +33089,7 @@
       </c>
       <c r="H553">
         <f>_xlfn.XLOOKUP(E553,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="554" spans="1:8">
@@ -33115,7 +33122,7 @@
       </c>
       <c r="H554">
         <f>_xlfn.XLOOKUP(E554,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="555" spans="1:8">
@@ -33148,7 +33155,7 @@
       </c>
       <c r="H555">
         <f>_xlfn.XLOOKUP(E555,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="556" spans="1:8">
@@ -33181,7 +33188,7 @@
       </c>
       <c r="H556">
         <f>_xlfn.XLOOKUP(E556,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="557" spans="1:8">
@@ -33214,7 +33221,7 @@
       </c>
       <c r="H557">
         <f>_xlfn.XLOOKUP(E557,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="558" spans="1:8">
@@ -33247,7 +33254,7 @@
       </c>
       <c r="H558">
         <f>_xlfn.XLOOKUP(E558,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="559" spans="1:8">
@@ -33280,7 +33287,7 @@
       </c>
       <c r="H559">
         <f>_xlfn.XLOOKUP(E559,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="560" spans="1:8">
@@ -33313,7 +33320,7 @@
       </c>
       <c r="H560">
         <f>_xlfn.XLOOKUP(E560,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="561" spans="1:8">
@@ -33346,7 +33353,7 @@
       </c>
       <c r="H561">
         <f>_xlfn.XLOOKUP(E561,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="562" spans="1:8">
@@ -33379,7 +33386,7 @@
       </c>
       <c r="H562">
         <f>_xlfn.XLOOKUP(E562,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="563" spans="1:8">
@@ -33412,7 +33419,7 @@
       </c>
       <c r="H563">
         <f>_xlfn.XLOOKUP(E563,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="564" spans="1:8">
@@ -33445,7 +33452,7 @@
       </c>
       <c r="H564">
         <f>_xlfn.XLOOKUP(E564,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="565" spans="1:8">
@@ -33478,7 +33485,7 @@
       </c>
       <c r="H565">
         <f>_xlfn.XLOOKUP(E565,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="566" spans="1:8">
@@ -33511,7 +33518,7 @@
       </c>
       <c r="H566">
         <f>_xlfn.XLOOKUP(E566,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="567" spans="1:8">
@@ -33544,7 +33551,7 @@
       </c>
       <c r="H567">
         <f>_xlfn.XLOOKUP(E567,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="568" spans="1:8">
@@ -33577,7 +33584,7 @@
       </c>
       <c r="H568">
         <f>_xlfn.XLOOKUP(E568,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="569" spans="1:8">
@@ -33610,7 +33617,7 @@
       </c>
       <c r="H569">
         <f>_xlfn.XLOOKUP(E569,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="570" spans="1:8">
@@ -33643,7 +33650,7 @@
       </c>
       <c r="H570">
         <f>_xlfn.XLOOKUP(E570,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="571" spans="1:8">
@@ -33676,7 +33683,7 @@
       </c>
       <c r="H571">
         <f>_xlfn.XLOOKUP(E571,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="572" spans="1:8">
@@ -33709,7 +33716,7 @@
       </c>
       <c r="H572">
         <f>_xlfn.XLOOKUP(E572,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="573" spans="1:8">
@@ -33742,7 +33749,7 @@
       </c>
       <c r="H573">
         <f>_xlfn.XLOOKUP(E573,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="574" spans="1:8">
@@ -33775,7 +33782,7 @@
       </c>
       <c r="H574">
         <f>_xlfn.XLOOKUP(E574,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="575" spans="1:8">
@@ -33808,7 +33815,7 @@
       </c>
       <c r="H575">
         <f>_xlfn.XLOOKUP(E575,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="576" spans="1:8">
@@ -33841,7 +33848,7 @@
       </c>
       <c r="H576">
         <f>_xlfn.XLOOKUP(E576,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="577" spans="1:8">
@@ -33874,7 +33881,7 @@
       </c>
       <c r="H577">
         <f>_xlfn.XLOOKUP(E577,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="578" spans="1:8">
@@ -33907,7 +33914,7 @@
       </c>
       <c r="H578">
         <f>_xlfn.XLOOKUP(E578,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="579" spans="1:8">
@@ -33940,7 +33947,7 @@
       </c>
       <c r="H579">
         <f>_xlfn.XLOOKUP(E579,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="580" spans="1:8">
@@ -33973,7 +33980,7 @@
       </c>
       <c r="H580">
         <f>_xlfn.XLOOKUP(E580,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="581" spans="1:8">
@@ -34006,7 +34013,7 @@
       </c>
       <c r="H581">
         <f>_xlfn.XLOOKUP(E581,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="582" spans="1:8">
@@ -34039,7 +34046,7 @@
       </c>
       <c r="H582">
         <f>_xlfn.XLOOKUP(E582,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="583" spans="1:8">
@@ -34072,7 +34079,7 @@
       </c>
       <c r="H583">
         <f>_xlfn.XLOOKUP(E583,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="584" spans="1:8">
@@ -34105,7 +34112,7 @@
       </c>
       <c r="H584">
         <f>_xlfn.XLOOKUP(E584,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="585" spans="1:8">
@@ -34138,7 +34145,7 @@
       </c>
       <c r="H585">
         <f>_xlfn.XLOOKUP(E585,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="586" spans="1:8">
@@ -34171,7 +34178,7 @@
       </c>
       <c r="H586">
         <f>_xlfn.XLOOKUP(E586,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="587" spans="1:8">
@@ -34204,7 +34211,7 @@
       </c>
       <c r="H587">
         <f>_xlfn.XLOOKUP(E587,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="588" spans="1:8">
@@ -34237,7 +34244,7 @@
       </c>
       <c r="H588">
         <f>_xlfn.XLOOKUP(E588,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="589" spans="1:8">
@@ -34270,7 +34277,7 @@
       </c>
       <c r="H589">
         <f>_xlfn.XLOOKUP(E589,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="590" spans="1:8">
@@ -34303,7 +34310,7 @@
       </c>
       <c r="H590">
         <f>_xlfn.XLOOKUP(E590,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="591" spans="1:8">
@@ -34336,7 +34343,7 @@
       </c>
       <c r="H591">
         <f>_xlfn.XLOOKUP(E591,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="592" spans="1:8">
@@ -34369,7 +34376,7 @@
       </c>
       <c r="H592">
         <f>_xlfn.XLOOKUP(E592,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="593" spans="1:8">
@@ -34402,7 +34409,7 @@
       </c>
       <c r="H593">
         <f>_xlfn.XLOOKUP(E593,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="594" spans="1:8">
@@ -34435,7 +34442,7 @@
       </c>
       <c r="H594">
         <f>_xlfn.XLOOKUP(E594,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="595" spans="1:8">
@@ -34468,7 +34475,7 @@
       </c>
       <c r="H595">
         <f>_xlfn.XLOOKUP(E595,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="596" spans="1:8">
@@ -35027,7 +35034,7 @@
       </c>
       <c r="H612">
         <f>_xlfn.XLOOKUP(E612,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="613" spans="1:8">
@@ -35060,7 +35067,7 @@
       </c>
       <c r="H613">
         <f>_xlfn.XLOOKUP(E613,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="614" spans="1:8">
@@ -35093,7 +35100,7 @@
       </c>
       <c r="H614">
         <f>_xlfn.XLOOKUP(E614,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="615" spans="1:8">
@@ -35126,7 +35133,7 @@
       </c>
       <c r="H615">
         <f>_xlfn.XLOOKUP(E615,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="616" spans="1:8">
@@ -35159,7 +35166,7 @@
       </c>
       <c r="H616">
         <f>_xlfn.XLOOKUP(E616,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="617" spans="1:8">
@@ -35192,7 +35199,7 @@
       </c>
       <c r="H617">
         <f>_xlfn.XLOOKUP(E617,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="618" spans="1:8">
@@ -35225,7 +35232,7 @@
       </c>
       <c r="H618">
         <f>_xlfn.XLOOKUP(E618,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="619" spans="1:8">
@@ -35258,7 +35265,7 @@
       </c>
       <c r="H619">
         <f>_xlfn.XLOOKUP(E619,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="620" spans="1:8">
@@ -35291,7 +35298,7 @@
       </c>
       <c r="H620">
         <f>_xlfn.XLOOKUP(E620,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="621" spans="1:8">
@@ -35324,7 +35331,7 @@
       </c>
       <c r="H621">
         <f>_xlfn.XLOOKUP(E621,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="622" spans="1:8">
@@ -35357,7 +35364,7 @@
       </c>
       <c r="H622">
         <f>_xlfn.XLOOKUP(E622,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="623" spans="1:8">
@@ -35390,7 +35397,7 @@
       </c>
       <c r="H623">
         <f>_xlfn.XLOOKUP(E623,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="624" spans="1:8">
@@ -35423,7 +35430,7 @@
       </c>
       <c r="H624">
         <f>_xlfn.XLOOKUP(E624,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="625" spans="1:8">
@@ -35456,7 +35463,7 @@
       </c>
       <c r="H625">
         <f>_xlfn.XLOOKUP(E625,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="626" spans="1:8">
@@ -35489,7 +35496,7 @@
       </c>
       <c r="H626">
         <f>_xlfn.XLOOKUP(E626,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="627" spans="1:8">
@@ -35522,7 +35529,7 @@
       </c>
       <c r="H627">
         <f>_xlfn.XLOOKUP(E627,SkillActive!B:B,SkillActive!K:K,,0)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="628" spans="1:8">
@@ -53940,7 +53947,7 @@
         <v>2</v>
       </c>
       <c r="H110" s="7" t="s">
-        <v>419</v>
+        <v>429</v>
       </c>
       <c r="I110" s="7" t="s">
         <v>1583</v>
@@ -53951,11 +53958,10 @@
       <c r="K110" s="7">
         <v>1</v>
       </c>
-      <c r="L110" s="7">
-        <v>10085</v>
-      </c>
-      <c r="M110" s="7" t="s">
-        <v>234</v>
+      <c r="L110" s="7"/>
+      <c r="M110" s="7"/>
+      <c r="N110" s="7">
+        <v>2150000440</v>
       </c>
     </row>
     <row r="111" s="7" customFormat="1" ht="15.95" customHeight="1" spans="1:15">
@@ -54090,7 +54096,7 @@
         <v>2</v>
       </c>
       <c r="H114" s="7" t="s">
-        <v>429</v>
+        <v>419</v>
       </c>
       <c r="I114" s="7" t="s">
         <v>1599</v>
@@ -54101,8 +54107,11 @@
       <c r="K114" s="7">
         <v>1</v>
       </c>
-      <c r="N114" s="7">
-        <v>2150000440</v>
+      <c r="L114" s="7">
+        <v>10085</v>
+      </c>
+      <c r="M114" s="7" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="115" s="7" customFormat="1" ht="15.95" customHeight="1" spans="1:15">
@@ -58405,7 +58414,7 @@
         <v>7</v>
       </c>
       <c r="L233" s="5">
-        <v>10194</v>
+        <v>10140</v>
       </c>
       <c r="M233" s="13" t="s">
         <v>1828</v>
@@ -59902,6 +59911,9 @@
       <c r="L276" s="5">
         <v>10225</v>
       </c>
+      <c r="M276" s="5" t="s">
+        <v>329</v>
+      </c>
     </row>
     <row r="277" s="5" customFormat="1" spans="1:14">
       <c r="A277" s="4">
@@ -59971,7 +59983,7 @@
         <v>1</v>
       </c>
       <c r="L278" s="31">
-        <v>10236</v>
+        <v>10237</v>
       </c>
       <c r="M278" s="5" t="s">
         <v>329</v>
@@ -60008,10 +60020,7 @@
         <v>1</v>
       </c>
       <c r="L279" s="31">
-        <v>10237</v>
-      </c>
-      <c r="M279" s="5" t="s">
-        <v>329</v>
+        <v>10238</v>
       </c>
     </row>
     <row r="280" s="5" customFormat="1" spans="1:14">
